--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B169634-40B4-4579-9043-0A1B00EACD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69840F2B-C8D5-4A30-90BE-96265BC6271A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="10" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -23,9 +23,10 @@
     <sheet name="ExtTest10mm_8" sheetId="18" r:id="rId8"/>
     <sheet name="ExtTest10mm_9" sheetId="19" r:id="rId9"/>
     <sheet name="ExtTest10mm_10" sheetId="20" r:id="rId10"/>
-    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId11"/>
-    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId12"/>
-    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId13"/>
+    <sheet name="ExtTest10mm_11" sheetId="21" r:id="rId11"/>
+    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId12"/>
+    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId13"/>
+    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -128,8 +129,62 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={7429FFDB-7320-40ED-9095-CADFEE0453D3}</author>
+    <author>tc={56BB9B1E-AE6F-4367-98DA-1738BC17BA33}</author>
+    <author>tc={181A90AF-6CB1-444A-AC50-05218AF784A8}</author>
+    <author>tc={E9CB4941-5049-48DD-9386-0FE986486E00}</author>
+    <author>tc={4B24DE55-490A-4648-B1F6-ECBEA4FEDB7F}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{7429FFDB-7320-40ED-9095-CADFEE0453D3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{56BB9B1E-AE6F-4367-98DA-1738BC17BA33}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{181A90AF-6CB1-444A-AC50-05218AF784A8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Max contracted length normalized by resting length</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{E9CB4941-5049-48DD-9386-0FE986486E00}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kmax</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{4B24DE55-490A-4648-B1F6-ECBEA4FEDB7F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    So it can reach -114 degrees</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="68">
   <si>
     <t>Test #</t>
   </si>
@@ -304,6 +359,36 @@
   <si>
     <t xml:space="preserve">***tendon 45 mm and </t>
   </si>
+  <si>
+    <t>^Collected by Ben</t>
+  </si>
+  <si>
+    <t>Batch D21</t>
+  </si>
+  <si>
+    <t>Batch E31</t>
+  </si>
+  <si>
+    <t>Ext Test 11</t>
+  </si>
+  <si>
+    <t>Ext Test 10</t>
+  </si>
+  <si>
+    <t>Ext Test 9</t>
+  </si>
+  <si>
+    <t>Ext Test 8</t>
+  </si>
+  <si>
+    <t>Ext Test 7</t>
+  </si>
+  <si>
+    <t>Ext Test 6</t>
+  </si>
+  <si>
+    <t>Encoder magnet fell off and I took measurements by hand</t>
+  </si>
 </sst>
 </file>
 
@@ -359,7 +444,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -374,6 +459,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,7 +614,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -546,14 +637,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1697,36 +1789,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Flexor 10mm</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Knee Torque</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1758,17 +1820,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.4158344861650378E-2"/>
-          <c:y val="0.17072497123130037"/>
-          <c:w val="0.91627572927286405"/>
-          <c:h val="0.77864211737629463"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -1807,98 +1859,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="log"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.60346456692913386"/>
-                  <c:y val="-0.28313193524076818"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="log"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="poly"/>
             <c:order val="3"/>
             <c:dispRSqr val="1"/>
@@ -1906,8 +1866,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.27899278215223094"/>
-                  <c:y val="0.3201971535736251"/>
+                  <c:x val="-0.30954483814523187"/>
+                  <c:y val="-2.5762248468941384E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -1942,200 +1902,146 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
+              <c:f>ExtTest10mm_11!$C$7:$AE$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>-5.5</c:v>
+                  <c:v>-101</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10.5</c:v>
+                  <c:v>-84.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-25.5</c:v>
+                  <c:v>-61</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.5</c:v>
+                  <c:v>-25</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>-14.5</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>-20</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-33</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>-39.5</c:v>
+                  <c:v>-30</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-43</c:v>
+                  <c:v>-40</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-50</c:v>
+                  <c:v>-53.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-62.5</c:v>
+                  <c:v>-63</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-60</c:v>
+                  <c:v>-85</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-55</c:v>
+                  <c:v>-96</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-53.5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>-46</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>-40</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-36.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-33.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-29.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-24.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-17.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-14.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-5.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>-0.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>11.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>19.5</c:v>
+                  <c:v>-106.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
+              <c:f>ExtTest10mm_11!$C$16:$AE$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>-13.550199438030189</c:v>
+                  <c:v>4.1076941173321835</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.715746326203965</c:v>
+                  <c:v>3.2488282465245577</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-12.227450296743585</c:v>
+                  <c:v>2.6482887751287043</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-13.574295183417183</c:v>
+                  <c:v>1.9985703282089087</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-12.617833179689791</c:v>
+                  <c:v>0.74522863715796217</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11.427173303326315</c:v>
+                  <c:v>0.24940114058390522</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-7.8289359826583684</c:v>
+                  <c:v>2.3747517585233231</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-6.4962395866945686</c:v>
+                  <c:v>3.2569294237478505</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-4.9404873370427511</c:v>
+                  <c:v>2.7371491864067816</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.8261340010696823</c:v>
+                  <c:v>3.2973182203532829</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.2108000422274927</c:v>
+                  <c:v>3.6031513786602369</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.11021594724709009</c:v>
+                  <c:v>3.8046722299114375</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.5137448723481624</c:v>
+                  <c:v>4.3479101475855275</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-3.1927408242720881</c:v>
+                  <c:v>5.0687639409674814</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-4.8615958230354943</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-6.8694525901110115</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-8.5997889837959107</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-10.35823139969961</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-11.863637901467659</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-13.477555041999489</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-13.77813076308844</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-14.884597105183458</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-14.534539473342328</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-14.338144060893327</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-14.021223986689929</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-12.539046654783448</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-11.167854768300959</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-8.2836070695559112</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2144,7 +2050,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
+              <c16:uniqueId val="{00000001-C7E4-4688-8087-06DE23804B3C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2156,11 +2062,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1394438799"/>
-        <c:axId val="1190584639"/>
+        <c:axId val="495425744"/>
+        <c:axId val="495426728"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1394438799"/>
+        <c:axId val="495425744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2217,12 +2123,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1190584639"/>
+        <c:crossAx val="495426728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1190584639"/>
+        <c:axId val="495426728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2279,7 +2185,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1394438799"/>
+        <c:crossAx val="495425744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2559,6 +2465,659 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
+                  <c:x val="-0.27899278215223094"/>
+                  <c:y val="0.3201971535736251"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-10.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-25.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-14.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-33</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-39.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-43</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-50</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-62.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-60</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-55</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-53.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-46</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-40</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-36.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-33.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-29.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-17.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-14.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>19.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>-13.550199438030189</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-12.715746326203965</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-12.227450296743585</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-13.574295183417183</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-12.617833179689791</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-11.427173303326315</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.8289359826583684</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-6.4962395866945686</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.9404873370427511</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.8261340010696823</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.2108000422274927</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.11021594724709009</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.5137448723481624</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-3.1927408242720881</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-4.8615958230354943</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-6.8694525901110115</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-8.5997889837959107</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-10.35823139969961</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-11.863637901467659</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-13.477555041999489</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-13.77813076308844</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-14.884597105183458</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-14.534539473342328</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-14.338144060893327</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-14.021223986689929</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-12.539046654783448</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-11.167854768300959</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-8.2836070695559112</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1394438799"/>
+        <c:axId val="1190584639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1394438799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1190584639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1190584639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1394438799"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Flexor 10mm</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Knee Torque</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.4158344861650378E-2"/>
+          <c:y val="0.17072497123130037"/>
+          <c:w val="0.91627572927286405"/>
+          <c:h val="0.77864211737629463"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="power"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.60346456692913386"/>
+                  <c:y val="-0.28313193524076818"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
                   <c:x val="-0.40762374401637524"/>
                   <c:y val="4.5584595515824444E-2"/>
                 </c:manualLayout>
@@ -2964,7 +3523,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7661,6 +8220,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -10561,6 +11160,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -14779,6 +15894,49 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>338137</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D30F6C69-70C1-4E7A-A4D9-2CB56DCB4150}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>740833</xdr:colOff>
       <xdr:row>20</xdr:row>
@@ -14818,7 +15976,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -14861,7 +16019,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -15574,6 +16732,26 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{7429FFDB-7320-40ED-9095-CADFEE0453D3}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{56BB9B1E-AE6F-4367-98DA-1738BC17BA33}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{181A90AF-6CB1-444A-AC50-05218AF784A8}">
+    <text>Max contracted length normalized by resting length</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{E9CB4941-5049-48DD-9386-0FE986486E00}">
+    <text>Kmax</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{4B24DE55-490A-4648-B1F6-ECBEA4FEDB7F}">
+    <text>So it can reach -114 degrees</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C83896A-0586-4C90-B5FD-474633C66A37}">
   <dimension ref="A1:AJ27"/>
@@ -16548,7 +17726,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
@@ -16559,7 +17737,7 @@
         <v>400</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
@@ -16584,6 +17762,9 @@
       </c>
       <c r="C4">
         <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
       </c>
       <c r="L4" t="s">
         <v>16</v>
@@ -16874,40 +18055,40 @@
       <c r="C10" s="16">
         <v>337</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10">
         <v>348</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10">
         <v>345</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10">
         <v>343</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10">
         <v>346</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10">
         <v>351</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10">
         <v>359</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10">
         <v>364</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10">
         <v>370</v>
       </c>
-      <c r="L10" s="22">
+      <c r="L10">
         <v>369</v>
       </c>
-      <c r="M10" s="22">
+      <c r="M10">
         <v>374</v>
       </c>
-      <c r="N10" s="22">
+      <c r="N10">
         <v>382</v>
       </c>
-      <c r="O10" s="22">
+      <c r="O10">
         <v>382</v>
       </c>
     </row>
@@ -17218,6 +18399,706 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9CE551-57A5-4045-B5A9-E0D9326386C2}">
+  <dimension ref="A1:AE27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>432</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3">
+        <v>367</v>
+      </c>
+      <c r="D3">
+        <f>(C3/C2)</f>
+        <v>0.84953703703703709</v>
+      </c>
+      <c r="E3">
+        <f>1-D3</f>
+        <v>0.15046296296296291</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D6">
+        <v>13.4</v>
+      </c>
+      <c r="E6">
+        <v>10.9</v>
+      </c>
+      <c r="F6">
+        <v>8.1</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>9.6</v>
+      </c>
+      <c r="J6">
+        <v>13.2</v>
+      </c>
+      <c r="K6">
+        <v>11.2</v>
+      </c>
+      <c r="L6">
+        <v>13.6</v>
+      </c>
+      <c r="M6">
+        <v>14.8</v>
+      </c>
+      <c r="N6">
+        <v>15.8</v>
+      </c>
+      <c r="O6">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="P6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16">
+        <v>-101</v>
+      </c>
+      <c r="D7">
+        <v>-84.5</v>
+      </c>
+      <c r="E7">
+        <v>-61</v>
+      </c>
+      <c r="F7">
+        <v>-25</v>
+      </c>
+      <c r="G7">
+        <v>-2.5</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>-14.5</v>
+      </c>
+      <c r="J7">
+        <v>-30</v>
+      </c>
+      <c r="K7">
+        <v>-40</v>
+      </c>
+      <c r="L7">
+        <v>-53.5</v>
+      </c>
+      <c r="M7">
+        <v>-63</v>
+      </c>
+      <c r="N7">
+        <v>-85</v>
+      </c>
+      <c r="O7">
+        <v>-96</v>
+      </c>
+      <c r="P7">
+        <v>-106.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16">
+        <v>624</v>
+      </c>
+      <c r="D8">
+        <v>622</v>
+      </c>
+      <c r="E8">
+        <v>622</v>
+      </c>
+      <c r="F8">
+        <v>624</v>
+      </c>
+      <c r="G8">
+        <v>623</v>
+      </c>
+      <c r="H8">
+        <v>623</v>
+      </c>
+      <c r="I8">
+        <v>622</v>
+      </c>
+      <c r="J8">
+        <v>622</v>
+      </c>
+      <c r="K8">
+        <v>622</v>
+      </c>
+      <c r="L8">
+        <v>625</v>
+      </c>
+      <c r="M8">
+        <v>624</v>
+      </c>
+      <c r="N8">
+        <v>623</v>
+      </c>
+      <c r="O8">
+        <v>623</v>
+      </c>
+      <c r="P8">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="15">
+        <v>69</v>
+      </c>
+      <c r="D9" s="1">
+        <v>71</v>
+      </c>
+      <c r="E9" s="1">
+        <v>71.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>76</v>
+      </c>
+      <c r="G9" s="1">
+        <v>79</v>
+      </c>
+      <c r="H9" s="1">
+        <v>82</v>
+      </c>
+      <c r="I9" s="1">
+        <v>77</v>
+      </c>
+      <c r="J9" s="1">
+        <v>76</v>
+      </c>
+      <c r="K9" s="1">
+        <v>73</v>
+      </c>
+      <c r="L9" s="1">
+        <v>71</v>
+      </c>
+      <c r="M9" s="1">
+        <v>72</v>
+      </c>
+      <c r="N9" s="1">
+        <v>69.5</v>
+      </c>
+      <c r="O9" s="1">
+        <v>69</v>
+      </c>
+      <c r="P9" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16">
+        <v>405</v>
+      </c>
+      <c r="D10">
+        <v>395</v>
+      </c>
+      <c r="E10" s="30">
+        <v>387</v>
+      </c>
+      <c r="F10">
+        <v>375</v>
+      </c>
+      <c r="G10">
+        <v>363</v>
+      </c>
+      <c r="H10" s="30">
+        <v>356</v>
+      </c>
+      <c r="I10" s="30">
+        <v>370</v>
+      </c>
+      <c r="J10" s="30">
+        <v>375</v>
+      </c>
+      <c r="K10" s="30">
+        <v>381</v>
+      </c>
+      <c r="L10" s="30">
+        <v>388</v>
+      </c>
+      <c r="M10" s="30">
+        <v>390</v>
+      </c>
+      <c r="N10" s="30">
+        <v>396</v>
+      </c>
+      <c r="O10" s="30">
+        <v>401</v>
+      </c>
+      <c r="P10" s="30">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="15"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="16">
+        <v>249.71</v>
+      </c>
+      <c r="D13">
+        <v>249.71</v>
+      </c>
+      <c r="E13">
+        <v>249.71</v>
+      </c>
+      <c r="F13">
+        <v>249.71</v>
+      </c>
+      <c r="G13">
+        <v>249.71</v>
+      </c>
+      <c r="H13">
+        <v>249.71</v>
+      </c>
+      <c r="I13">
+        <v>249.71</v>
+      </c>
+      <c r="J13">
+        <v>249.71</v>
+      </c>
+      <c r="K13">
+        <v>249.71</v>
+      </c>
+      <c r="L13">
+        <v>249.71</v>
+      </c>
+      <c r="M13">
+        <v>249.71</v>
+      </c>
+      <c r="N13">
+        <v>249.71</v>
+      </c>
+      <c r="O13">
+        <v>249.71</v>
+      </c>
+      <c r="P13">
+        <v>249.71</v>
+      </c>
+      <c r="Q13">
+        <v>249.71</v>
+      </c>
+      <c r="R13">
+        <v>249.71</v>
+      </c>
+      <c r="S13">
+        <v>249.71</v>
+      </c>
+      <c r="T13">
+        <v>249.71</v>
+      </c>
+      <c r="U13">
+        <v>249.71</v>
+      </c>
+      <c r="V13">
+        <v>249.71</v>
+      </c>
+      <c r="W13">
+        <v>249.71</v>
+      </c>
+      <c r="X13">
+        <v>249.71</v>
+      </c>
+      <c r="Y13">
+        <v>249.71</v>
+      </c>
+      <c r="Z13">
+        <v>249.71</v>
+      </c>
+      <c r="AA13">
+        <v>249.71</v>
+      </c>
+      <c r="AB13">
+        <v>249.71</v>
+      </c>
+      <c r="AC13">
+        <v>249.71</v>
+      </c>
+      <c r="AD13">
+        <v>249.71</v>
+      </c>
+      <c r="AE13">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>30</v>
+      </c>
+      <c r="F14">
+        <v>43</v>
+      </c>
+      <c r="G14">
+        <v>55</v>
+      </c>
+      <c r="H14">
+        <v>60</v>
+      </c>
+      <c r="I14">
+        <v>45</v>
+      </c>
+      <c r="J14">
+        <v>40</v>
+      </c>
+      <c r="K14">
+        <v>42</v>
+      </c>
+      <c r="L14">
+        <v>30</v>
+      </c>
+      <c r="M14">
+        <v>30</v>
+      </c>
+      <c r="N14">
+        <v>30</v>
+      </c>
+      <c r="O14">
+        <v>30</v>
+      </c>
+      <c r="P14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="14"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="16">
+        <f>C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
+        <v>4.1076941173321835</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:AE16" si="0">D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
+        <v>3.2488282465245577</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>2.6482887751287043</v>
+      </c>
+      <c r="F16" s="16">
+        <f>F6*SIN(RADIANS(F9+5.15))*F13/1000</f>
+        <v>1.9985703282089087</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>0.74522863715796217</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>0.24940114058390522</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>2.3747517585233231</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>3.2569294237478505</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="0"/>
+        <v>2.7371491864067816</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="0"/>
+        <v>3.2973182203532829</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>3.6031513786602369</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="0"/>
+        <v>3.8046722299114375</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="0"/>
+        <v>4.3479101475855275</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="0"/>
+        <v>5.0687639409674814</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B21" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B27" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
   <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -18116,7 +19997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
   <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -18935,7 +20816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
   <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -22583,7 +24464,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
@@ -23249,7 +25130,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
@@ -23286,7 +25167,7 @@
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="22">
         <v>1</v>
       </c>
       <c r="D5" s="10">
@@ -23378,7 +25259,7 @@
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>2.2372000000000001</v>
       </c>
       <c r="D6">
@@ -23401,7 +25282,7 @@
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="23">
         <v>1.5</v>
       </c>
       <c r="D7">
@@ -23421,7 +25302,7 @@
       <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="23">
         <v>620</v>
       </c>
       <c r="D8">
@@ -23444,7 +25325,7 @@
       <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <v>82.8</v>
       </c>
       <c r="D9" s="1">
@@ -23465,7 +25346,7 @@
       <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="23">
         <v>340</v>
       </c>
       <c r="D10">
@@ -23489,21 +25370,21 @@
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="25"/>
+      <c r="C11" s="24"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="24"/>
+      <c r="C12" s="23"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="23">
         <v>249.71</v>
       </c>
       <c r="D13">
@@ -23575,7 +25456,7 @@
       <c r="B14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="D14">
         <v>70</v>
       </c>
@@ -23594,114 +25475,114 @@
       <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="26"/>
+      <c r="C15" s="25"/>
     </row>
-    <row r="16" spans="1:31" s="29" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28" t="s">
+    <row r="16" spans="1:31" s="28" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="23">
         <f>C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
         <v>0.55829367015563802</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <f t="shared" ref="D16:W16" si="0">D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
         <v>0.39904182493424839</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="23">
         <f t="shared" si="0"/>
         <v>6.6697068808236901</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="23">
         <f t="shared" si="0"/>
         <v>6.8734537902217339</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="23">
         <f t="shared" si="0"/>
         <v>5.4126384787884589</v>
       </c>
-      <c r="H16" s="24" t="e">
+      <c r="H16" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="24">
+      <c r="J16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="24">
+      <c r="K16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L16" s="24">
+      <c r="L16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M16" s="24">
+      <c r="M16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N16" s="24">
+      <c r="N16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O16" s="24">
+      <c r="O16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P16" s="24">
+      <c r="P16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="24">
+      <c r="Q16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R16" s="24">
+      <c r="R16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S16" s="24">
+      <c r="S16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T16" s="24">
+      <c r="T16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U16" s="24">
+      <c r="U16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V16" s="24">
+      <c r="V16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W16" s="24">
+      <c r="W16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="29">
+      <c r="AA16" s="28">
         <f t="shared" ref="AA16:AE16" si="1">AA6*SIN(RADIANS(AA9))*AA13/1000</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="29">
+      <c r="AB16" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC16" s="29">
+      <c r="AC16" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD16" s="29">
+      <c r="AD16" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="29">
+      <c r="AE16" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23732,7 +25613,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
@@ -24383,7 +26264,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
@@ -24419,6 +26300,9 @@
       </c>
       <c r="C4">
         <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
       </c>
       <c r="L4" t="s">
         <v>53</v>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69840F2B-C8D5-4A30-90BE-96265BC6271A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A61D5E-CF01-454E-842A-CF85E4BA88EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="10" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="26685" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="9" activeTab="11" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -24,9 +24,10 @@
     <sheet name="ExtTest10mm_9" sheetId="19" r:id="rId9"/>
     <sheet name="ExtTest10mm_10" sheetId="20" r:id="rId10"/>
     <sheet name="ExtTest10mm_11" sheetId="21" r:id="rId11"/>
-    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId12"/>
-    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId13"/>
-    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId14"/>
+    <sheet name="ExtTest10mm_12" sheetId="22" r:id="rId12"/>
+    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId13"/>
+    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId14"/>
+    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -183,8 +184,62 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={F99A6D76-844F-423C-8E72-632020492202}</author>
+    <author>tc={57404540-41ED-4CFC-A34A-B0C06D36E435}</author>
+    <author>tc={FD23BCFD-5D0D-499D-B1BC-4D31A4174384}</author>
+    <author>tc={34C2BEB3-8987-42FD-9240-D19AB0F3395E}</author>
+    <author>tc={619279C5-5896-4658-A891-94E7656E0604}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{F99A6D76-844F-423C-8E72-632020492202}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{57404540-41ED-4CFC-A34A-B0C06D36E435}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{FD23BCFD-5D0D-499D-B1BC-4D31A4174384}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Max contracted length normalized by resting length</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{34C2BEB3-8987-42FD-9240-D19AB0F3395E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kmax</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{619279C5-5896-4658-A891-94E7656E0604}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    So it can reach -114 degrees</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="79">
   <si>
     <t>Test #</t>
   </si>
@@ -389,6 +444,39 @@
   <si>
     <t>Encoder magnet fell off and I took measurements by hand</t>
   </si>
+  <si>
+    <t>^Collected by Moe</t>
+  </si>
+  <si>
+    <t>I found the encoder magnets and recalibrated</t>
+  </si>
+  <si>
+    <t>Max contraction length (mm)</t>
+  </si>
+  <si>
+    <t>Resting muscle length (mm)</t>
+  </si>
+  <si>
+    <t>*start from the second readings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* preloaded 2.08N </t>
+  </si>
+  <si>
+    <t>*preloaded 3.35N</t>
+  </si>
+  <si>
+    <t>*preloaded 4.56</t>
+  </si>
+  <si>
+    <t>* preloaded 5.8 N</t>
+  </si>
+  <si>
+    <t>*preloaded 9.5N</t>
+  </si>
+  <si>
+    <t>*preloaded 1.5N</t>
+  </si>
 </sst>
 </file>
 
@@ -425,12 +513,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -443,8 +525,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,6 +553,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,7 +708,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -637,14 +731,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -2256,36 +2353,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Flexor 10mm</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Knee Torque</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2317,25 +2384,18 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.4158344861650378E-2"/>
-          <c:y val="0.17072497123130037"/>
-          <c:w val="0.91627572927286405"/>
-          <c:h val="0.77864211737629463"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>result</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:noFill/>
               <a:round/>
             </a:ln>
@@ -2366,44 +2426,10 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="log"/>
             <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.60346456692913386"/>
-                  <c:y val="-0.28313193524076818"/>
-                </c:manualLayout>
-              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -2444,31 +2470,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="log"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="poly"/>
             <c:order val="3"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.27899278215223094"/>
-                  <c:y val="0.3201971535736251"/>
-                </c:manualLayout>
-              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -2501,200 +2507,140 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
+              <c:f>ExtTest10mm_12!$D$7:$S$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>-5.5</c:v>
+                  <c:v>28.29</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10.5</c:v>
+                  <c:v>18.149999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-25.5</c:v>
+                  <c:v>1.29</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.5</c:v>
+                  <c:v>-14.86</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-14.5</c:v>
+                  <c:v>-25.64</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-20</c:v>
+                  <c:v>-36.76</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-33</c:v>
+                  <c:v>-42.87</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-39.5</c:v>
+                  <c:v>-49.33</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-43</c:v>
+                  <c:v>-56.87</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-50</c:v>
+                  <c:v>-68.36</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-62.5</c:v>
+                  <c:v>-77.69</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-60</c:v>
+                  <c:v>-84.16</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-55</c:v>
+                  <c:v>-90.1</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-53.5</c:v>
+                  <c:v>-99.233999999999995</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-46</c:v>
+                  <c:v>-82</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-40</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-36.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-33.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-29.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-24.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-17.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-14.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-5.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>-0.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>11.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>19.5</c:v>
+                  <c:v>-65.48</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
+              <c:f>ExtTest10mm_12!$D$16:$AB$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-13.550199438030189</c:v>
+                  <c:v>0.38934455560856757</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.715746326203965</c:v>
+                  <c:v>1.8112948210918218</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-12.227450296743585</c:v>
+                  <c:v>4.4750917512529496</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-13.574295183417183</c:v>
+                  <c:v>5.4446222516176634</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-12.617833179689791</c:v>
+                  <c:v>5.9469453841091626</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11.427173303326315</c:v>
+                  <c:v>5.6590559428960212</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-7.8289359826583684</c:v>
+                  <c:v>6.0927652115792634</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-6.4962395866945686</c:v>
+                  <c:v>6.0976142089621366</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-4.9404873370427511</c:v>
+                  <c:v>6.3279415846485803</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.8261340010696823</c:v>
+                  <c:v>7.0095037627925798</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.2108000422274927</c:v>
+                  <c:v>7.5711771242618884</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.11021594724709009</c:v>
+                  <c:v>7.937808715762241</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.5137448723481624</c:v>
+                  <c:v>8.3306919291859725</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-3.1927408242720881</c:v>
+                  <c:v>9.369972199445602</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-4.8615958230354943</c:v>
+                  <c:v>7.0892341737595572</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-6.8694525901110115</c:v>
+                  <c:v>5.4793670426458965</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-8.5997889837959107</c:v>
+                  <c:v>4.957246848957868</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-10.35823139969961</c:v>
+                  <c:v>4.8935172428682936</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-11.863637901467659</c:v>
+                  <c:v>4.5504713609212226</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-13.477555041999489</c:v>
+                  <c:v>0.10037237370560359</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-13.77813076308844</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-14.884597105183458</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-14.534539473342328</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-14.338144060893327</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-14.021223986689929</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>-12.539046654783448</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>-11.167854768300959</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>-8.2836070695559112</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2703,7 +2649,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
+              <c16:uniqueId val="{00000000-FC5D-4D76-8301-4B545B22878D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2715,11 +2661,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1394438799"/>
-        <c:axId val="1190584639"/>
+        <c:axId val="1567646591"/>
+        <c:axId val="1566330175"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1394438799"/>
+        <c:axId val="1567646591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2776,12 +2722,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1190584639"/>
+        <c:crossAx val="1566330175"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1190584639"/>
+        <c:axId val="1566330175"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2838,7 +2784,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1394438799"/>
+        <c:crossAx val="1567646591"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3118,6 +3064,659 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
+                  <c:x val="-0.27899278215223094"/>
+                  <c:y val="0.3201971535736251"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-10.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-25.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-14.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-33</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-39.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-43</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-50</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-62.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-60</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-55</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-53.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-46</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-40</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-36.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-33.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-29.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-17.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-14.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>19.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>-13.550199438030189</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-12.715746326203965</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-12.227450296743585</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-13.574295183417183</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-12.617833179689791</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-11.427173303326315</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.8289359826583684</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-6.4962395866945686</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.9404873370427511</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.8261340010696823</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.2108000422274927</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.11021594724709009</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.5137448723481624</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-3.1927408242720881</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-4.8615958230354943</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-6.8694525901110115</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-8.5997889837959107</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-10.35823139969961</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-11.863637901467659</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-13.477555041999489</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-13.77813076308844</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-14.884597105183458</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-14.534539473342328</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-14.338144060893327</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-14.021223986689929</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-12.539046654783448</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-11.167854768300959</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-8.2836070695559112</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1394438799"/>
+        <c:axId val="1190584639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1394438799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1190584639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1190584639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1394438799"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Flexor 10mm</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Knee Torque</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.4158344861650378E-2"/>
+          <c:y val="0.17072497123130037"/>
+          <c:w val="0.91627572927286405"/>
+          <c:h val="0.77864211737629463"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="power"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.60346456692913386"/>
+                  <c:y val="-0.28313193524076818"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
                   <c:x val="-0.40762374401637524"/>
                   <c:y val="4.5584595515824444E-2"/>
                 </c:manualLayout>
@@ -3523,7 +4122,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8260,6 +8859,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -11676,6 +12315,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -15937,6 +17092,47 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>329710</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>108439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1340825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>41276</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34D96D25-D710-62E5-8544-989B5550AA53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>740833</xdr:colOff>
       <xdr:row>20</xdr:row>
@@ -15976,7 +17172,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -16019,7 +17215,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -16752,27 +17948,47 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{F99A6D76-844F-423C-8E72-632020492202}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{57404540-41ED-4CFC-A34A-B0C06D36E435}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{FD23BCFD-5D0D-499D-B1BC-4D31A4174384}">
+    <text>Max contracted length normalized by resting length</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{34C2BEB3-8987-42FD-9240-D19AB0F3395E}">
+    <text>Kmax</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{619279C5-5896-4658-A891-94E7656E0604}">
+    <text>So it can reach -114 degrees</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C83896A-0586-4C90-B5FD-474633C66A37}">
   <dimension ref="A1:AJ27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -16783,7 +17999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -16792,7 +18008,7 @@
         <v>403.38</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -16800,7 +18016,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -16923,7 +18139,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -16988,7 +18204,7 @@
         <v>23.167999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -17053,7 +18269,7 @@
         <v>-123</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -17121,13 +18337,13 @@
         <v>84.4</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -17207,7 +18423,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -17233,7 +18449,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -17308,7 +18524,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -17374,13 +18590,13 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -17517,12 +18733,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C18">
         <f>C6+4.6262</f>
         <v>5.6261999999999999</v>
@@ -17560,7 +18776,7 @@
         <v>6.3061999999999996</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C19">
         <v>22.176200000000001</v>
       </c>
@@ -17589,12 +18805,12 @@
         <v>6.3061999999999996</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C21">
         <v>17.55</v>
       </c>
@@ -17623,7 +18839,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
       <c r="T22">
         <v>480</v>
       </c>
@@ -17640,7 +18856,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
       <c r="S23" t="s">
         <v>30</v>
       </c>
@@ -17665,7 +18881,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
       <c r="S24" t="s">
         <v>31</v>
       </c>
@@ -17690,7 +18906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
       <c r="S27" t="s">
         <v>32</v>
       </c>
@@ -17709,27 +18925,27 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA3ACFF-8EC2-4AAF-BDC7-460D102A0BEE}">
   <dimension ref="A1:AE21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -17740,7 +18956,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -17756,7 +18972,7 @@
         <v>0.14749999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -17776,7 +18992,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -17868,7 +19084,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -17912,7 +19128,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -17956,7 +19172,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -18000,7 +19216,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -18047,7 +19263,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -18092,7 +19308,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -18101,14 +19317,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -18201,7 +19417,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -18246,14 +19462,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -18374,7 +19590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="L17" t="s">
         <v>55</v>
       </c>
@@ -18385,7 +19601,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
@@ -18401,27 +19617,27 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9CE551-57A5-4045-B5A9-E0D9326386C2}">
   <dimension ref="A1:AE27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -18432,7 +19648,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -18448,7 +19664,7 @@
         <v>0.15046296296296291</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -18460,7 +19676,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -18552,7 +19768,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -18599,7 +19815,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -18646,7 +19862,7 @@
         <v>-106.5</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -18693,7 +19909,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -18743,7 +19959,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -18754,7 +19970,7 @@
       <c r="D10">
         <v>395</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10">
         <v>387</v>
       </c>
       <c r="F10">
@@ -18763,35 +19979,35 @@
       <c r="G10">
         <v>363</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10">
         <v>356</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10">
         <v>370</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10">
         <v>375</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10">
         <v>381</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10">
         <v>388</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M10">
         <v>390</v>
       </c>
-      <c r="N10" s="30">
+      <c r="N10">
         <v>396</v>
       </c>
-      <c r="O10" s="30">
+      <c r="O10">
         <v>401</v>
       </c>
-      <c r="P10" s="30">
+      <c r="P10">
         <v>403</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -18800,14 +20016,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -18900,7 +20116,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -18948,14 +20164,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -19076,16 +20292,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
         <v>67</v>
       </c>
@@ -19099,26 +20315,1021 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605CE535-3534-4BC1-886C-868F03FBDC68}">
+  <dimension ref="A1:AK36"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2">
+        <v>436</v>
+      </c>
+      <c r="E2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3">
+        <v>371</v>
+      </c>
+      <c r="D3">
+        <f>(C3/C2)</f>
+        <v>0.8509174311926605</v>
+      </c>
+      <c r="E3">
+        <f>1-D3</f>
+        <v>0.1490825688073395</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N4" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A5" s="10"/>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6">
+        <v>1.56</v>
+      </c>
+      <c r="E6">
+        <v>7.27</v>
+      </c>
+      <c r="F6">
+        <v>18.05</v>
+      </c>
+      <c r="G6">
+        <v>22.13</v>
+      </c>
+      <c r="H6">
+        <v>24.334</v>
+      </c>
+      <c r="I6">
+        <v>23.155999999999999</v>
+      </c>
+      <c r="J6">
+        <v>25.13</v>
+      </c>
+      <c r="K6">
+        <v>25.15</v>
+      </c>
+      <c r="L6">
+        <v>26.1</v>
+      </c>
+      <c r="M6">
+        <v>29.18</v>
+      </c>
+      <c r="N6">
+        <v>31.68</v>
+      </c>
+      <c r="O6">
+        <v>32.74</v>
+      </c>
+      <c r="P6">
+        <v>34.68</v>
+      </c>
+      <c r="Q6">
+        <v>38.82</v>
+      </c>
+      <c r="R6">
+        <v>29.24</v>
+      </c>
+      <c r="S6">
+        <v>22.6</v>
+      </c>
+      <c r="T6">
+        <v>20.248000000000001</v>
+      </c>
+      <c r="U6">
+        <v>19.89</v>
+      </c>
+      <c r="V6">
+        <v>18.373999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.40200000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7">
+        <v>28.29</v>
+      </c>
+      <c r="E7">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="F7">
+        <v>1.29</v>
+      </c>
+      <c r="G7">
+        <v>-14.86</v>
+      </c>
+      <c r="H7">
+        <v>-25.64</v>
+      </c>
+      <c r="I7">
+        <v>-36.76</v>
+      </c>
+      <c r="J7">
+        <v>-42.87</v>
+      </c>
+      <c r="K7">
+        <v>-49.33</v>
+      </c>
+      <c r="L7">
+        <v>-56.87</v>
+      </c>
+      <c r="M7">
+        <v>-68.36</v>
+      </c>
+      <c r="N7">
+        <v>-77.69</v>
+      </c>
+      <c r="O7">
+        <v>-84.16</v>
+      </c>
+      <c r="P7">
+        <v>-90.1</v>
+      </c>
+      <c r="Q7">
+        <v>-99.233999999999995</v>
+      </c>
+      <c r="R7">
+        <v>-82</v>
+      </c>
+      <c r="S7">
+        <v>-65.48</v>
+      </c>
+      <c r="T7">
+        <v>-47.537999999999997</v>
+      </c>
+      <c r="U7">
+        <v>-26.72</v>
+      </c>
+      <c r="V7">
+        <v>-6.2530000000000001</v>
+      </c>
+      <c r="W7">
+        <v>31.442</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8">
+        <v>622.09299999999996</v>
+      </c>
+      <c r="E8">
+        <v>620.57899999999995</v>
+      </c>
+      <c r="F8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="G8">
+        <v>621.34</v>
+      </c>
+      <c r="H8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="I8">
+        <v>620.58000000000004</v>
+      </c>
+      <c r="J8">
+        <v>622.85</v>
+      </c>
+      <c r="K8">
+        <v>622.09299999999996</v>
+      </c>
+      <c r="L8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="M8">
+        <v>623.04999999999995</v>
+      </c>
+      <c r="N8">
+        <v>623.33600000000001</v>
+      </c>
+      <c r="O8">
+        <v>620.57899999999995</v>
+      </c>
+      <c r="P8">
+        <v>622.85</v>
+      </c>
+      <c r="Q8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="R8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="S8">
+        <v>622.09</v>
+      </c>
+      <c r="T8">
+        <v>622.6</v>
+      </c>
+      <c r="U8">
+        <v>622.85</v>
+      </c>
+      <c r="V8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="W8">
+        <v>620.57899999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="31"/>
+      <c r="D9" s="1">
+        <v>83</v>
+      </c>
+      <c r="E9" s="1">
+        <v>81</v>
+      </c>
+      <c r="F9" s="1">
+        <v>78</v>
+      </c>
+      <c r="G9" s="1">
+        <v>75</v>
+      </c>
+      <c r="H9" s="1">
+        <v>73</v>
+      </c>
+      <c r="I9" s="1">
+        <v>73</v>
+      </c>
+      <c r="J9" s="1">
+        <v>71</v>
+      </c>
+      <c r="K9" s="1">
+        <v>71</v>
+      </c>
+      <c r="L9" s="1">
+        <v>71</v>
+      </c>
+      <c r="M9" s="1">
+        <v>69</v>
+      </c>
+      <c r="N9" s="1">
+        <v>68</v>
+      </c>
+      <c r="O9" s="1">
+        <v>71</v>
+      </c>
+      <c r="P9" s="1">
+        <v>69</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>70</v>
+      </c>
+      <c r="R9" s="1">
+        <v>71</v>
+      </c>
+      <c r="S9" s="1">
+        <v>71</v>
+      </c>
+      <c r="T9" s="1">
+        <v>73.5</v>
+      </c>
+      <c r="U9" s="1">
+        <v>75</v>
+      </c>
+      <c r="V9" s="1">
+        <v>77.5</v>
+      </c>
+      <c r="W9" s="1">
+        <v>84</v>
+      </c>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="33">
+        <v>367</v>
+      </c>
+      <c r="E10" s="33">
+        <v>367</v>
+      </c>
+      <c r="F10" s="33">
+        <v>382</v>
+      </c>
+      <c r="G10" s="33">
+        <v>398</v>
+      </c>
+      <c r="H10" s="33">
+        <v>397</v>
+      </c>
+      <c r="I10" s="33">
+        <v>403</v>
+      </c>
+      <c r="J10" s="33">
+        <v>407</v>
+      </c>
+      <c r="K10" s="33">
+        <v>411</v>
+      </c>
+      <c r="L10" s="33">
+        <v>416</v>
+      </c>
+      <c r="M10" s="33">
+        <v>422</v>
+      </c>
+      <c r="N10" s="33">
+        <v>428</v>
+      </c>
+      <c r="O10" s="33">
+        <v>428</v>
+      </c>
+      <c r="P10" s="33">
+        <v>434</v>
+      </c>
+      <c r="Q10" s="33">
+        <v>434</v>
+      </c>
+      <c r="R10" s="33">
+        <v>425</v>
+      </c>
+      <c r="S10" s="33">
+        <v>420</v>
+      </c>
+      <c r="T10" s="33">
+        <v>398</v>
+      </c>
+      <c r="U10" s="33">
+        <v>396</v>
+      </c>
+      <c r="V10" s="33">
+        <v>386</v>
+      </c>
+      <c r="W10" s="33">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="31"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="30"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="30">
+        <v>249.71</v>
+      </c>
+      <c r="D13">
+        <v>249.71</v>
+      </c>
+      <c r="E13">
+        <v>249.71</v>
+      </c>
+      <c r="F13">
+        <v>249.71</v>
+      </c>
+      <c r="G13">
+        <v>249.71</v>
+      </c>
+      <c r="H13">
+        <v>249.71</v>
+      </c>
+      <c r="I13">
+        <v>249.71</v>
+      </c>
+      <c r="J13">
+        <v>249.71</v>
+      </c>
+      <c r="K13">
+        <v>249.71</v>
+      </c>
+      <c r="L13">
+        <v>249.71</v>
+      </c>
+      <c r="M13">
+        <v>249.71</v>
+      </c>
+      <c r="N13">
+        <v>249.71</v>
+      </c>
+      <c r="O13">
+        <v>249.71</v>
+      </c>
+      <c r="P13">
+        <v>249.71</v>
+      </c>
+      <c r="Q13">
+        <v>249.71</v>
+      </c>
+      <c r="R13">
+        <v>249.71</v>
+      </c>
+      <c r="S13">
+        <v>249.71</v>
+      </c>
+      <c r="T13">
+        <v>249.71</v>
+      </c>
+      <c r="U13">
+        <v>249.71</v>
+      </c>
+      <c r="V13">
+        <v>249.71</v>
+      </c>
+      <c r="W13">
+        <v>249.71</v>
+      </c>
+      <c r="X13">
+        <v>249.71</v>
+      </c>
+      <c r="Y13">
+        <v>249.71</v>
+      </c>
+      <c r="Z13">
+        <v>249.71</v>
+      </c>
+      <c r="AA13">
+        <v>249.71</v>
+      </c>
+      <c r="AB13">
+        <v>249.71</v>
+      </c>
+      <c r="AC13">
+        <v>249.71</v>
+      </c>
+      <c r="AD13">
+        <v>249.71</v>
+      </c>
+      <c r="AE13">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="30"/>
+      <c r="D14">
+        <v>78</v>
+      </c>
+      <c r="E14">
+        <v>61</v>
+      </c>
+      <c r="F14">
+        <v>55</v>
+      </c>
+      <c r="G14">
+        <v>48</v>
+      </c>
+      <c r="H14">
+        <v>38</v>
+      </c>
+      <c r="I14">
+        <v>32</v>
+      </c>
+      <c r="J14">
+        <v>30</v>
+      </c>
+      <c r="K14">
+        <v>30</v>
+      </c>
+      <c r="L14">
+        <v>30</v>
+      </c>
+      <c r="M14">
+        <v>29</v>
+      </c>
+      <c r="N14">
+        <v>28</v>
+      </c>
+      <c r="O14">
+        <v>26</v>
+      </c>
+      <c r="P14">
+        <v>23</v>
+      </c>
+      <c r="Q14">
+        <v>23</v>
+      </c>
+      <c r="R14">
+        <v>24</v>
+      </c>
+      <c r="S14">
+        <v>29</v>
+      </c>
+      <c r="T14">
+        <v>31</v>
+      </c>
+      <c r="U14">
+        <v>35</v>
+      </c>
+      <c r="V14">
+        <v>50</v>
+      </c>
+      <c r="W14">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="30">
+        <f>C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:AE16" si="0">D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
+        <v>0.38934455560856757</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>1.8112948210918218</v>
+      </c>
+      <c r="F16" s="16">
+        <f>F6*SIN(RADIANS(F9+5.15))*F13/1000</f>
+        <v>4.4750917512529496</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>5.4446222516176634</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>5.9469453841091626</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>5.6590559428960212</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>6.0927652115792634</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="0"/>
+        <v>6.0976142089621366</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="0"/>
+        <v>6.3279415846485803</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>7.0095037627925798</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5711771242618884</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="0"/>
+        <v>7.937808715762241</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="0"/>
+        <v>8.3306919291859725</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>9.369972199445602</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>7.0892341737595572</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>5.4793670426458965</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>4.957246848957868</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>4.8935172428682936</v>
+      </c>
+      <c r="V16" s="16">
+        <f t="shared" si="0"/>
+        <v>4.5504713609212226</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>0.10037237370560359</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -19129,7 +21340,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -19138,7 +21349,7 @@
         <v>402.55</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -19146,7 +21357,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -19269,7 +21480,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -19358,7 +21569,7 @@
         <v>30.405999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -19447,7 +21658,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -19539,13 +21750,13 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -19641,7 +21852,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -19667,7 +21878,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -19757,7 +21968,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -19847,13 +22058,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -19997,27 +22208,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
   <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -20028,7 +22239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -20040,7 +22251,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -20051,7 +22262,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -20174,7 +22385,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -20239,7 +22450,7 @@
         <v>48.012999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -20304,7 +22515,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -20372,13 +22583,13 @@
         <v>95.1</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -20458,7 +22669,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -20484,7 +22695,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -20589,7 +22800,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -20655,13 +22866,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -20798,12 +23009,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="L16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
       <c r="R29">
         <f>485*1.03</f>
         <v>499.55</v>
@@ -20816,27 +23027,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
   <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -20847,7 +23058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -20856,7 +23067,7 @@
         <v>379.31</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -20864,7 +23075,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -20987,7 +23198,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -21022,7 +23233,7 @@
         <v>2.0994000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -21057,7 +23268,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -21095,13 +23306,13 @@
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -21161,7 +23372,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -21187,7 +23398,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -21292,7 +23503,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -21328,13 +23539,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -21471,13 +23682,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="10:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="10:18" x14ac:dyDescent="0.35">
       <c r="J18">
         <f>1-348/457</f>
         <v>0.23851203501094087</v>
       </c>
     </row>
-    <row r="29" spans="10:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="10:18" x14ac:dyDescent="0.35">
       <c r="R29">
         <f>485*1.03</f>
         <v>499.55</v>
@@ -21493,24 +23704,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D1208C-7CDD-421F-9FF0-096EE144B4F3}">
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -21521,7 +23732,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -21530,7 +23741,7 @@
         <v>379.31</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -21542,7 +23753,7 @@
         <v>0.16849015317286653</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -21665,7 +23876,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -21757,7 +23968,7 @@
         <v>24.667000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -21849,7 +24060,7 @@
         <v>-123</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -21944,13 +24155,13 @@
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -22048,7 +24259,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -22074,7 +24285,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -22179,7 +24390,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -22272,13 +24483,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -22425,24 +24636,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CB8201-A5D3-4826-B613-98BAA3DB341B}">
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -22453,7 +24664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -22462,7 +24673,7 @@
         <v>403.38</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -22474,7 +24685,7 @@
         <v>0.18106995884773658</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -22597,7 +24808,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -22614,7 +24825,7 @@
         <v>13.111000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -22631,7 +24842,7 @@
         <v>-92</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -22651,13 +24862,13 @@
         <v>80.7</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -22705,7 +24916,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -22731,7 +24942,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -22836,7 +25047,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -22854,13 +25065,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -23007,24 +25218,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D539E524-5F19-4B4B-B21A-C95F2596B6A0}">
   <dimension ref="A1:AJ27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -23035,7 +25246,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -23047,7 +25258,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -23068,7 +25279,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -23191,7 +25402,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -23277,7 +25488,7 @@
         <v>33.061999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -23360,7 +25571,7 @@
         <v>-66</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -23446,13 +25657,13 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -23544,7 +25755,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -23570,7 +25781,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -23675,7 +25886,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -23759,13 +25970,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -23902,7 +26113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="U16" t="s">
         <v>23</v>
       </c>
@@ -23910,22 +26121,22 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="17:29" x14ac:dyDescent="0.35">
       <c r="AB17">
         <v>2.2241</v>
       </c>
     </row>
-    <row r="18" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="17:29" x14ac:dyDescent="0.35">
       <c r="AC18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q25" t="s">
         <v>42</v>
       </c>
@@ -23936,7 +26147,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q26" t="s">
         <v>43</v>
       </c>
@@ -23947,7 +26158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="17:29" x14ac:dyDescent="0.35">
       <c r="R27">
         <v>505</v>
       </c>
@@ -23962,24 +26173,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E6C766-4925-4D35-B304-44784D2D9843}">
   <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -23990,7 +26201,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -23998,7 +26209,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -24009,7 +26220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -24059,7 +26270,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -24106,7 +26317,7 @@
         <v>6.2092000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -24153,7 +26364,7 @@
         <v>-18.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -24203,7 +26414,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>3</v>
@@ -24251,7 +26462,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
@@ -24259,13 +26470,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -24316,7 +26527,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -24364,13 +26575,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -24435,7 +26646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="L16" t="s">
         <v>39</v>
       </c>
@@ -24450,24 +26661,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B944D1C8-56B8-47D8-90D4-245D22EBCA01}">
   <dimension ref="A1:AE15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -24478,7 +26689,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -24486,7 +26697,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -24494,7 +26705,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -24586,7 +26797,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -24642,7 +26853,7 @@
         <v>17.72</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -24698,7 +26909,7 @@
         <v>-119.5</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -24757,7 +26968,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>3</v>
@@ -24814,7 +27025,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
@@ -24822,13 +27033,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -24921,7 +27132,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -24978,13 +27189,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -25115,25 +27326,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07511B1B-CFA9-4E3E-A27D-F86FFAE12463}">
   <dimension ref="A1:AE16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -25144,7 +27355,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -25152,7 +27363,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -25163,7 +27374,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -25255,7 +27466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -25278,7 +27489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -25298,7 +27509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
@@ -25318,7 +27529,7 @@
         <v>628.9</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -25341,7 +27552,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -25363,7 +27574,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -25372,14 +27583,14 @@
       </c>
       <c r="C11" s="24"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="23"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -25451,7 +27662,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -25470,14 +27681,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="25"/>
     </row>
-    <row r="16" spans="1:31" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
       <c r="B16" s="27" t="s">
         <v>6</v>
@@ -25597,26 +27808,26 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC7A6C4B-FDDD-4D0B-90C8-5B01A1705645}">
   <dimension ref="A1:AE17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -25627,7 +27838,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -25635,7 +27846,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -25652,7 +27863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -25744,7 +27955,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -25788,7 +27999,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -25832,7 +28043,7 @@
         <v>-73</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
@@ -25876,7 +28087,7 @@
         <v>629.71799999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -25923,7 +28134,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -25968,7 +28179,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -25977,14 +28188,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -26056,7 +28267,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -26101,14 +28312,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -26229,7 +28440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N17" s="3" t="s">
         <v>50</v>
       </c>
@@ -26247,27 +28458,27 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4D735A-7F76-4974-8609-056275EBAB78}">
   <dimension ref="A1:AE21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -26278,7 +28489,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -26294,7 +28505,7 @@
         <v>0.14749999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -26312,7 +28523,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -26404,7 +28615,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -26442,7 +28653,7 @@
         <v>45.42</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -26480,7 +28691,7 @@
         <v>-52.89</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -26518,7 +28729,7 @@
         <v>623.61</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -26565,7 +28776,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -26610,7 +28821,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -26619,14 +28830,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -26719,7 +28930,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -26758,14 +28969,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -26886,11 +29097,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A61D5E-CF01-454E-842A-CF85E4BA88EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD150D4-4730-494D-96AC-EE7AD0BAEDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26685" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="9" activeTab="11" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="26685" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="13" activeTab="15" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId13"/>
     <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId14"/>
     <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId15"/>
+    <sheet name="FlxTest10mm_4" sheetId="23" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -238,8 +239,62 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={B3DD3E36-DE23-4526-822F-7544076C12AF}</author>
+    <author>tc={44F69930-AA26-4737-9556-6F232E8AC193}</author>
+    <author>tc={6E9C7D1B-6D13-4A15-A63C-B49E3DDDDD72}</author>
+    <author>tc={A117DFD4-25AF-41A6-9D26-99F7C9197E59}</author>
+    <author>tc={70F2E1CB-BEA3-46AD-8012-48E9D04ADA3E}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{B3DD3E36-DE23-4526-822F-7544076C12AF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{44F69930-AA26-4737-9556-6F232E8AC193}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{6E9C7D1B-6D13-4A15-A63C-B49E3DDDDD72}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Max contracted length normalized by resting length</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{A117DFD4-25AF-41A6-9D26-99F7C9197E59}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kmax</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{70F2E1CB-BEA3-46AD-8012-48E9D04ADA3E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    So it can reach -114 degrees</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="81">
   <si>
     <t>Test #</t>
   </si>
@@ -476,6 +531,12 @@
   </si>
   <si>
     <t>*preloaded 1.5N</t>
+  </si>
+  <si>
+    <t>Flex test 4</t>
+  </si>
+  <si>
+    <t>^Collected by Moe &amp; Ben</t>
   </si>
 </sst>
 </file>
@@ -4570,6 +4631,456 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_4!$C$7:$AE$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>-68.718999999999994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.898000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-54.359000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-46.460999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-38.204000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-32.100999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-27.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-24.202999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_4!$C$16:$X$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>-1.9089163300292105</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.0809375058192954</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-7.0574220518637798</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-10.09453321766197</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-13.401234911810583</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-14.847761858930939</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-15.781617917093591</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-16.386164614410578</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CE28-4152-9B9D-F4BE9A57F41C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1604021071"/>
+        <c:axId val="1604018671"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1604021071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604018671"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1604018671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604021071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -8899,6 +9410,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -12831,6 +13382,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -17236,6 +18303,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87F016FD-8475-49B9-BE00-EEAE24A59AD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>55562</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>96837</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B83CC11-D790-13A2-4619-F46E06DD1000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17968,6 +19076,26 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{B3DD3E36-DE23-4526-822F-7544076C12AF}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{44F69930-AA26-4737-9556-6F232E8AC193}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{6E9C7D1B-6D13-4A15-A63C-B49E3DDDDD72}">
+    <text>Max contracted length normalized by resting length</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{A117DFD4-25AF-41A6-9D26-99F7C9197E59}">
+    <text>Kmax</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{70F2E1CB-BEA3-46AD-8012-48E9D04ADA3E}">
+    <text>So it can reach -114 degrees</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C83896A-0586-4C90-B5FD-474633C66A37}">
   <dimension ref="A1:AJ27"/>
@@ -23701,6 +24829,805 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B26E4-CFF3-41E2-8721-B0918FFC9B0E}">
+  <dimension ref="A1:AK36"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2">
+        <v>479</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3">
+        <v>413</v>
+      </c>
+      <c r="D3">
+        <f>(C3/C2)</f>
+        <v>0.86221294363256784</v>
+      </c>
+      <c r="E3">
+        <f>1-D3</f>
+        <v>0.13778705636743216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N4" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A5" s="10"/>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>7.6539999999999999</v>
+      </c>
+      <c r="D6">
+        <v>16.346</v>
+      </c>
+      <c r="E6">
+        <v>28.263000000000002</v>
+      </c>
+      <c r="F6">
+        <v>41.6</v>
+      </c>
+      <c r="G6">
+        <v>53.704999999999998</v>
+      </c>
+      <c r="H6">
+        <v>59.472000000000001</v>
+      </c>
+      <c r="I6">
+        <v>63.2</v>
+      </c>
+      <c r="J6">
+        <v>65.655000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16">
+        <v>-68.718999999999994</v>
+      </c>
+      <c r="D7">
+        <v>-61.898000000000003</v>
+      </c>
+      <c r="E7">
+        <v>-54.359000000000002</v>
+      </c>
+      <c r="F7">
+        <v>-46.460999999999999</v>
+      </c>
+      <c r="G7">
+        <v>-38.204000000000001</v>
+      </c>
+      <c r="H7">
+        <v>-32.100999999999999</v>
+      </c>
+      <c r="I7">
+        <v>-27.8</v>
+      </c>
+      <c r="J7">
+        <v>-24.202999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="D8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="E8">
+        <v>622.85</v>
+      </c>
+      <c r="F8">
+        <v>622.85</v>
+      </c>
+      <c r="G8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="H8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="I8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="J8">
+        <v>622.85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="15">
+        <v>82</v>
+      </c>
+      <c r="D9" s="1">
+        <v>86</v>
+      </c>
+      <c r="E9" s="1">
+        <v>84.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>98.5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>87</v>
+      </c>
+      <c r="H9" s="1">
+        <v>86</v>
+      </c>
+      <c r="I9" s="1">
+        <v>85</v>
+      </c>
+      <c r="J9" s="1">
+        <v>83</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16">
+        <v>408</v>
+      </c>
+      <c r="D10" s="33">
+        <v>410</v>
+      </c>
+      <c r="E10" s="33">
+        <v>421</v>
+      </c>
+      <c r="F10" s="33">
+        <v>427</v>
+      </c>
+      <c r="G10" s="33">
+        <v>437</v>
+      </c>
+      <c r="H10" s="33">
+        <v>441</v>
+      </c>
+      <c r="I10" s="33">
+        <v>444</v>
+      </c>
+      <c r="J10" s="33">
+        <v>447</v>
+      </c>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="33"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="16">
+        <v>249.71</v>
+      </c>
+      <c r="D13">
+        <v>249.71</v>
+      </c>
+      <c r="E13">
+        <v>249.71</v>
+      </c>
+      <c r="F13">
+        <v>249.71</v>
+      </c>
+      <c r="G13">
+        <v>249.71</v>
+      </c>
+      <c r="H13">
+        <v>249.71</v>
+      </c>
+      <c r="I13">
+        <v>249.71</v>
+      </c>
+      <c r="J13">
+        <v>249.71</v>
+      </c>
+      <c r="K13">
+        <v>249.71</v>
+      </c>
+      <c r="L13">
+        <v>249.71</v>
+      </c>
+      <c r="M13">
+        <v>249.71</v>
+      </c>
+      <c r="N13">
+        <v>249.71</v>
+      </c>
+      <c r="O13">
+        <v>249.71</v>
+      </c>
+      <c r="P13">
+        <v>249.71</v>
+      </c>
+      <c r="Q13">
+        <v>249.71</v>
+      </c>
+      <c r="R13">
+        <v>249.71</v>
+      </c>
+      <c r="S13">
+        <v>249.71</v>
+      </c>
+      <c r="T13">
+        <v>249.71</v>
+      </c>
+      <c r="U13">
+        <v>249.71</v>
+      </c>
+      <c r="V13">
+        <v>249.71</v>
+      </c>
+      <c r="W13">
+        <v>249.71</v>
+      </c>
+      <c r="X13">
+        <v>249.71</v>
+      </c>
+      <c r="Y13">
+        <v>249.71</v>
+      </c>
+      <c r="Z13">
+        <v>249.71</v>
+      </c>
+      <c r="AA13">
+        <v>249.71</v>
+      </c>
+      <c r="AB13">
+        <v>249.71</v>
+      </c>
+      <c r="AC13">
+        <v>249.71</v>
+      </c>
+      <c r="AD13">
+        <v>249.71</v>
+      </c>
+      <c r="AE13">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16">
+        <v>62</v>
+      </c>
+      <c r="D14">
+        <v>71</v>
+      </c>
+      <c r="E14">
+        <v>72</v>
+      </c>
+      <c r="F14">
+        <v>82</v>
+      </c>
+      <c r="G14">
+        <v>82</v>
+      </c>
+      <c r="H14">
+        <v>80</v>
+      </c>
+      <c r="I14">
+        <v>79</v>
+      </c>
+      <c r="J14">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="16">
+        <f>-C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
+        <v>-1.9089163300292105</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:AE16" si="0">-D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
+        <v>-4.0809375058192954</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>-7.0574220518637798</v>
+      </c>
+      <c r="F16" s="16">
+        <f t="shared" si="0"/>
+        <v>-10.09453321766197</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>-13.401234911810583</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>-14.847761858930939</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>-15.781617917093591</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>-16.386164614410578</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D1208C-7CDD-421F-9FF0-096EE144B4F3}">
   <dimension ref="A1:AJ15"/>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD150D4-4730-494D-96AC-EE7AD0BAEDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F416346-DDA5-482A-BBD3-70514486EDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26685" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="13" activeTab="15" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="15" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="82">
   <si>
     <t>Test #</t>
   </si>
@@ -538,12 +538,15 @@
   <si>
     <t>^Collected by Moe &amp; Ben</t>
   </si>
+  <si>
+    <t>oooooo</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -585,12 +588,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4716,42 +4713,100 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="poly"/>
             <c:order val="3"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.5337707786526634E-2"/>
+                  <c:y val="-0.46240994367386146"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>y = 0.0001x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="30000">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>3</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t> + 0.024x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="30000">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>2</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t> + 0.9144x - 5.9593</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>R² = 0.9885</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </c:rich>
+              </c:tx>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:noFill/>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
                 <a:ln>
                   <a:noFill/>
                 </a:ln>
@@ -4764,10 +4819,7 @@
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
+                        <a:schemeClr val="bg1"/>
                       </a:solidFill>
                       <a:latin typeface="+mn-lt"/>
                       <a:ea typeface="+mn-ea"/>
@@ -4809,6 +4861,36 @@
                 <c:pt idx="7">
                   <c:v>-24.202999999999999</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>-25.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-20.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-70.81</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-53.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-39.280999999999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-29.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-16.3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-10.199999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4819,58 +4901,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>-1.9089163300292105</c:v>
+                  <c:v>-1.9888446022622024</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-4.0809375058192954</c:v>
+                  <c:v>-4.2527956349925518</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-7.0574220518637798</c:v>
+                  <c:v>-7.3539886035989408</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-10.09453321766197</c:v>
+                  <c:v>-10.527409285407064</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-13.401234911810583</c:v>
+                  <c:v>-13.966402193997661</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-14.847761858930939</c:v>
+                  <c:v>-15.473036951197667</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-15.781617917093591</c:v>
+                  <c:v>-16.445267992387105</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-16.386164614410578</c:v>
+                  <c:v>-17.07325998043143</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>-14.697192119709124</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>-15.358895091501429</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>-15.042937875530633</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>-0.56433407059449248</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>-2.4445410159422072</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>-5.2402184740344895</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>-10.95843156495609</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>-13.902438921694182</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>-16.846155017276384</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>-9.9320795468220986</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -19099,24 +19181,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C83896A-0586-4C90-B5FD-474633C66A37}">
   <dimension ref="A1:AJ27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -19127,7 +19209,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -19136,7 +19218,7 @@
         <v>403.38</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -19144,7 +19226,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -19267,7 +19349,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -19332,7 +19414,7 @@
         <v>23.167999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -19397,7 +19479,7 @@
         <v>-123</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -19465,13 +19547,13 @@
         <v>84.4</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -19551,7 +19633,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -19577,7 +19659,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -19652,7 +19734,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -19718,13 +19800,13 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -19861,12 +19943,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C18">
         <f>C6+4.6262</f>
         <v>5.6261999999999999</v>
@@ -19904,7 +19986,7 @@
         <v>6.3061999999999996</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C19">
         <v>22.176200000000001</v>
       </c>
@@ -19933,12 +20015,12 @@
         <v>6.3061999999999996</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C21">
         <v>17.55</v>
       </c>
@@ -19967,7 +20049,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.3">
       <c r="T22">
         <v>480</v>
       </c>
@@ -19984,7 +20066,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.3">
       <c r="S23" t="s">
         <v>30</v>
       </c>
@@ -20009,7 +20091,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.3">
       <c r="S24" t="s">
         <v>31</v>
       </c>
@@ -20034,7 +20116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.3">
       <c r="S27" t="s">
         <v>32</v>
       </c>
@@ -20053,27 +20135,27 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA3ACFF-8EC2-4AAF-BDC7-460D102A0BEE}">
   <dimension ref="A1:AE21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -20084,7 +20166,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -20100,7 +20182,7 @@
         <v>0.14749999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -20120,7 +20202,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -20212,7 +20294,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -20256,7 +20338,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -20300,7 +20382,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -20344,7 +20426,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -20391,7 +20473,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -20436,7 +20518,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -20445,14 +20527,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -20545,7 +20627,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -20590,14 +20672,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -20718,7 +20800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="L17" t="s">
         <v>55</v>
       </c>
@@ -20729,7 +20811,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
@@ -20745,27 +20827,27 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9CE551-57A5-4045-B5A9-E0D9326386C2}">
   <dimension ref="A1:AE27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -20776,7 +20858,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -20792,7 +20874,7 @@
         <v>0.15046296296296291</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -20804,7 +20886,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -20896,7 +20978,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -20943,7 +21025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -20990,7 +21072,7 @@
         <v>-106.5</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -21037,7 +21119,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -21087,7 +21169,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -21135,7 +21217,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -21144,14 +21226,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -21244,7 +21326,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -21292,14 +21374,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -21420,16 +21502,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="29" t="s">
         <v>67</v>
       </c>
@@ -21445,22 +21527,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605CE535-3534-4BC1-886C-868F03FBDC68}">
   <dimension ref="A1:AK36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>71</v>
       </c>
@@ -21472,7 +21554,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
@@ -21489,7 +21571,7 @@
         <v>0.1490825688073395</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -21519,7 +21601,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="4" t="s">
         <v>0</v>
@@ -21618,7 +21700,7 @@
       <c r="AJ5" s="10"/>
       <c r="AK5" s="10"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
         <v>1</v>
@@ -21685,7 +21767,7 @@
         <v>0.40200000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="6" t="s">
         <v>2</v>
@@ -21752,7 +21834,7 @@
         <v>31.442</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
         <v>47</v>
@@ -21819,7 +21901,7 @@
         <v>620.57899999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -21902,74 +21984,74 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="30"/>
-      <c r="D10" s="33">
+      <c r="D10">
         <v>367</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10">
         <v>367</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10">
         <v>382</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10">
         <v>398</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10">
         <v>397</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10">
         <v>403</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10">
         <v>407</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10">
         <v>411</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10">
         <v>416</v>
       </c>
-      <c r="M10" s="33">
+      <c r="M10">
         <v>422</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10">
         <v>428</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10">
         <v>428</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10">
         <v>434</v>
       </c>
-      <c r="Q10" s="33">
+      <c r="Q10">
         <v>434</v>
       </c>
-      <c r="R10" s="33">
+      <c r="R10">
         <v>425</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10">
         <v>420</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10">
         <v>398</v>
       </c>
-      <c r="U10" s="33">
+      <c r="U10">
         <v>396</v>
       </c>
-      <c r="V10" s="33">
+      <c r="V10">
         <v>386</v>
       </c>
-      <c r="W10" s="33">
+      <c r="W10">
         <v>366</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -22012,14 +22094,14 @@
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="30"/>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -22112,7 +22194,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -22179,7 +22261,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
@@ -22220,7 +22302,7 @@
       <c r="AJ15" s="2"/>
       <c r="AK15" s="2"/>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
         <v>6</v>
@@ -22342,91 +22424,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="29" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
     </row>
@@ -22440,24 +22522,24 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -22468,7 +22550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -22477,7 +22559,7 @@
         <v>402.55</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -22485,7 +22567,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -22608,7 +22690,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -22697,7 +22779,7 @@
         <v>30.405999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -22786,7 +22868,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -22878,13 +22960,13 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -22980,7 +23062,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -23006,7 +23088,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -23096,7 +23178,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -23186,13 +23268,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -23339,24 +23421,24 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
   <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -23367,7 +23449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -23379,7 +23461,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -23390,7 +23472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -23513,7 +23595,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -23578,7 +23660,7 @@
         <v>48.012999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -23643,7 +23725,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -23711,13 +23793,13 @@
         <v>95.1</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -23797,7 +23879,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -23823,7 +23905,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -23928,7 +24010,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -23994,13 +24076,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -24137,12 +24219,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="L16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="18:18" x14ac:dyDescent="0.3">
       <c r="R29">
         <f>485*1.03</f>
         <v>499.55</v>
@@ -24158,24 +24240,24 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
   <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -24186,7 +24268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -24195,7 +24277,7 @@
         <v>379.31</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -24203,7 +24285,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -24326,7 +24408,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -24361,7 +24443,7 @@
         <v>2.0994000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -24396,7 +24478,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -24434,13 +24516,13 @@
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -24500,7 +24582,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -24526,7 +24608,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -24631,7 +24713,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -24667,13 +24749,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -24810,13 +24892,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="10:18" x14ac:dyDescent="0.3">
       <c r="J18">
         <f>1-348/457</f>
         <v>0.23851203501094087</v>
       </c>
     </row>
-    <row r="29" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="10:18" x14ac:dyDescent="0.3">
       <c r="R29">
         <f>485*1.03</f>
         <v>499.55</v>
@@ -24832,22 +24914,22 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B26E4-CFF3-41E2-8721-B0918FFC9B0E}">
   <dimension ref="A1:AK36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>71</v>
       </c>
@@ -24859,7 +24941,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
@@ -24876,7 +24958,7 @@
         <v>0.13778705636743216</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -24885,28 +24967,11 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>77</v>
-      </c>
-      <c r="R4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="4" t="s">
         <v>0</v>
@@ -25005,7 +25070,7 @@
       <c r="AJ5" s="10"/>
       <c r="AK5" s="10"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
         <v>1</v>
@@ -25034,8 +25099,38 @@
       <c r="J6">
         <v>65.655000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="K6">
+        <v>63.7</v>
+      </c>
+      <c r="L6">
+        <v>61.6</v>
+      </c>
+      <c r="M6">
+        <v>60.4</v>
+      </c>
+      <c r="N6">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="O6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="P6">
+        <v>21</v>
+      </c>
+      <c r="Q6">
+        <v>44</v>
+      </c>
+      <c r="R6">
+        <v>55.9</v>
+      </c>
+      <c r="S6">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="T6">
+        <v>75.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="6" t="s">
         <v>2</v>
@@ -25064,8 +25159,38 @@
       <c r="J7">
         <v>-24.202999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="K7">
+        <v>-25.6</v>
+      </c>
+      <c r="L7">
+        <v>-16</v>
+      </c>
+      <c r="M7">
+        <v>-20.6</v>
+      </c>
+      <c r="N7">
+        <v>-70.81</v>
+      </c>
+      <c r="O7">
+        <v>-63</v>
+      </c>
+      <c r="P7">
+        <v>-53.6</v>
+      </c>
+      <c r="Q7">
+        <v>-39.280999999999999</v>
+      </c>
+      <c r="R7">
+        <v>-29.6</v>
+      </c>
+      <c r="S7">
+        <v>-16.3</v>
+      </c>
+      <c r="T7">
+        <v>-10.199999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
         <v>47</v>
@@ -25094,8 +25219,38 @@
       <c r="J8">
         <v>622.85</v>
       </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="K8">
+        <v>622.79999999999995</v>
+      </c>
+      <c r="L8">
+        <v>623.6</v>
+      </c>
+      <c r="M8">
+        <v>622</v>
+      </c>
+      <c r="N8">
+        <v>626</v>
+      </c>
+      <c r="O8">
+        <v>624</v>
+      </c>
+      <c r="P8">
+        <v>622</v>
+      </c>
+      <c r="Q8">
+        <v>625.1</v>
+      </c>
+      <c r="R8">
+        <v>625.1</v>
+      </c>
+      <c r="S8">
+        <v>623.6</v>
+      </c>
+      <c r="T8">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -25126,16 +25281,36 @@
       <c r="J9" s="1">
         <v>83</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
+      <c r="K9" s="1">
+        <v>57.5</v>
+      </c>
+      <c r="L9" s="1">
+        <v>88</v>
+      </c>
+      <c r="M9" s="1">
+        <v>89</v>
+      </c>
+      <c r="N9" s="1">
+        <v>84.5</v>
+      </c>
+      <c r="O9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="P9" s="1">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>89</v>
+      </c>
+      <c r="R9" s="1">
+        <v>90</v>
+      </c>
+      <c r="S9" s="1">
+        <v>88.5</v>
+      </c>
+      <c r="T9" s="1">
+        <v>26.5</v>
+      </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
@@ -25154,7 +25329,7 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -25162,42 +25337,59 @@
       <c r="C10" s="16">
         <v>408</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10">
         <v>410</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10">
         <v>421</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10">
         <v>427</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10">
         <v>437</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10">
         <v>441</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10">
         <v>444</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10">
         <v>447</v>
       </c>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="K10" s="33">
+        <v>445</v>
+      </c>
+      <c r="L10" s="33">
+        <v>452</v>
+      </c>
+      <c r="M10" s="33">
+        <v>449</v>
+      </c>
+      <c r="N10" s="33">
+        <v>403</v>
+      </c>
+      <c r="O10" s="33">
+        <v>407</v>
+      </c>
+      <c r="P10" s="33">
+        <v>415</v>
+      </c>
+      <c r="Q10" s="33">
+        <v>430</v>
+      </c>
+      <c r="R10" s="33">
+        <v>438</v>
+      </c>
+      <c r="S10" s="33">
+        <v>450</v>
+      </c>
+      <c r="T10" s="33">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -25240,44 +25432,44 @@
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="16">
-        <v>249.71</v>
-      </c>
-      <c r="D13">
-        <v>249.71</v>
-      </c>
-      <c r="E13">
-        <v>249.71</v>
-      </c>
-      <c r="F13">
-        <v>249.71</v>
-      </c>
-      <c r="G13">
-        <v>249.71</v>
-      </c>
-      <c r="H13">
-        <v>249.71</v>
-      </c>
-      <c r="I13">
-        <v>249.71</v>
-      </c>
-      <c r="J13">
-        <v>249.71</v>
-      </c>
-      <c r="K13">
-        <v>249.71</v>
+        <v>260.20999999999998</v>
+      </c>
+      <c r="D13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="E13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="F13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="G13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="H13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="I13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="J13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="K13" s="16">
+        <v>260.20999999999998</v>
       </c>
       <c r="L13">
         <v>249.71</v>
@@ -25340,7 +25532,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -25369,8 +25561,38 @@
       <c r="J14">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="K14">
+        <v>75</v>
+      </c>
+      <c r="L14">
+        <v>74</v>
+      </c>
+      <c r="M14">
+        <v>75</v>
+      </c>
+      <c r="N14">
+        <v>55</v>
+      </c>
+      <c r="O14">
+        <v>65</v>
+      </c>
+      <c r="P14">
+        <v>75</v>
+      </c>
+      <c r="Q14">
+        <v>76</v>
+      </c>
+      <c r="R14">
+        <v>75</v>
+      </c>
+      <c r="S14">
+        <v>75</v>
+      </c>
+      <c r="T14">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
@@ -25392,7 +25614,9 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
+      <c r="T15" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
@@ -25411,213 +25635,213 @@
       <c r="AJ15" s="2"/>
       <c r="AK15" s="2"/>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="16">
-        <f>-C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
-        <v>-1.9089163300292105</v>
+        <f>-C6*SIN(RADIANS(C9+4.96))*C13/1000</f>
+        <v>-1.9888446022622024</v>
       </c>
       <c r="D16" s="16">
-        <f t="shared" ref="D16:AE16" si="0">-D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
-        <v>-4.0809375058192954</v>
+        <f t="shared" ref="D16:K16" si="0">-D6*SIN(RADIANS(D9+4.96))*D13/1000</f>
+        <v>-4.2527956349925518</v>
       </c>
       <c r="E16" s="16">
         <f t="shared" si="0"/>
-        <v>-7.0574220518637798</v>
+        <v>-7.3539886035989408</v>
       </c>
       <c r="F16" s="16">
         <f t="shared" si="0"/>
-        <v>-10.09453321766197</v>
+        <v>-10.527409285407064</v>
       </c>
       <c r="G16" s="16">
         <f t="shared" si="0"/>
-        <v>-13.401234911810583</v>
+        <v>-13.966402193997661</v>
       </c>
       <c r="H16" s="16">
         <f t="shared" si="0"/>
-        <v>-14.847761858930939</v>
+        <v>-15.473036951197667</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="0"/>
-        <v>-15.781617917093591</v>
+        <v>-16.445267992387105</v>
       </c>
       <c r="J16" s="16">
         <f t="shared" si="0"/>
-        <v>-16.386164614410578</v>
+        <v>-17.07325998043143</v>
       </c>
       <c r="K16" s="16">
         <f t="shared" si="0"/>
+        <v>-14.697192119709124</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" ref="D16:AE16" si="1">-L6*SIN(RADIANS(L9+5.15))*L13/1000</f>
+        <v>-15.358895091501429</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="1"/>
+        <v>-15.042937875530633</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="1"/>
+        <v>-0.56433407059449248</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="1"/>
+        <v>-2.4445410159422072</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="1"/>
+        <v>-5.2402184740344895</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="1"/>
+        <v>-10.95843156495609</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="1"/>
+        <v>-13.902438921694182</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="1"/>
+        <v>-16.846155017276384</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="1"/>
+        <v>-9.9320795468220986</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L16" s="16">
-        <f t="shared" si="0"/>
+      <c r="V16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M16" s="16">
-        <f t="shared" si="0"/>
+      <c r="W16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N16" s="16">
-        <f t="shared" si="0"/>
+      <c r="X16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O16" s="16">
-        <f t="shared" si="0"/>
+      <c r="Y16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P16" s="16">
-        <f t="shared" si="0"/>
+      <c r="Z16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AA16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AB16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AC16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AD16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AE16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="29" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
     </row>
@@ -25631,24 +25855,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D1208C-7CDD-421F-9FF0-096EE144B4F3}">
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -25659,7 +25883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -25668,7 +25892,7 @@
         <v>379.31</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -25680,7 +25904,7 @@
         <v>0.16849015317286653</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -25803,7 +26027,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -25895,7 +26119,7 @@
         <v>24.667000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -25987,7 +26211,7 @@
         <v>-123</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -26082,13 +26306,13 @@
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -26186,7 +26410,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -26212,7 +26436,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -26317,7 +26541,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -26410,13 +26634,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -26563,24 +26787,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CB8201-A5D3-4826-B613-98BAA3DB341B}">
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -26591,7 +26815,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -26600,7 +26824,7 @@
         <v>403.38</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -26612,7 +26836,7 @@
         <v>0.18106995884773658</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -26735,7 +26959,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -26752,7 +26976,7 @@
         <v>13.111000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -26769,7 +26993,7 @@
         <v>-92</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -26789,13 +27013,13 @@
         <v>80.7</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -26843,7 +27067,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -26869,7 +27093,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -26974,7 +27198,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -26992,13 +27216,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -27145,24 +27369,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D539E524-5F19-4B4B-B21A-C95F2596B6A0}">
   <dimension ref="A1:AJ27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -27173,7 +27397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -27185,7 +27409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -27206,7 +27430,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -27329,7 +27553,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -27415,7 +27639,7 @@
         <v>33.061999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -27498,7 +27722,7 @@
         <v>-66</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -27584,13 +27808,13 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -27682,7 +27906,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -27708,7 +27932,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -27813,7 +28037,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -27897,13 +28121,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -28040,7 +28264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="U16" t="s">
         <v>23</v>
       </c>
@@ -28048,22 +28272,22 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="17" spans="17:29" x14ac:dyDescent="0.3">
       <c r="AB17">
         <v>2.2241</v>
       </c>
     </row>
-    <row r="18" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="18" spans="17:29" x14ac:dyDescent="0.3">
       <c r="AC18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="24" spans="17:29" x14ac:dyDescent="0.3">
       <c r="Q24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="25" spans="17:29" x14ac:dyDescent="0.3">
       <c r="Q25" t="s">
         <v>42</v>
       </c>
@@ -28074,7 +28298,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="26" spans="17:29" x14ac:dyDescent="0.3">
       <c r="Q26" t="s">
         <v>43</v>
       </c>
@@ -28085,7 +28309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="27" spans="17:29" x14ac:dyDescent="0.3">
       <c r="R27">
         <v>505</v>
       </c>
@@ -28100,24 +28324,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E6C766-4925-4D35-B304-44784D2D9843}">
   <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -28128,7 +28352,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -28136,7 +28360,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -28147,7 +28371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -28197,7 +28421,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -28244,7 +28468,7 @@
         <v>6.2092000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -28291,7 +28515,7 @@
         <v>-18.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -28341,7 +28565,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>3</v>
@@ -28389,7 +28613,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
@@ -28397,13 +28621,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -28454,7 +28678,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -28502,13 +28726,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -28573,7 +28797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="L16" t="s">
         <v>39</v>
       </c>
@@ -28588,24 +28812,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B944D1C8-56B8-47D8-90D4-245D22EBCA01}">
   <dimension ref="A1:AE15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -28616,7 +28840,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -28624,7 +28848,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -28632,7 +28856,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -28724,7 +28948,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -28780,7 +29004,7 @@
         <v>17.72</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -28836,7 +29060,7 @@
         <v>-119.5</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -28895,7 +29119,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>3</v>
@@ -28952,7 +29176,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
@@ -28960,13 +29184,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -29059,7 +29283,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -29116,13 +29340,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -29253,25 +29477,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07511B1B-CFA9-4E3E-A27D-F86FFAE12463}">
   <dimension ref="A1:AE16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -29282,7 +29506,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -29290,7 +29514,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -29301,7 +29525,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -29393,7 +29617,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -29416,7 +29640,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -29436,7 +29660,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
@@ -29456,7 +29680,7 @@
         <v>628.9</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -29479,7 +29703,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -29501,7 +29725,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -29510,14 +29734,14 @@
       </c>
       <c r="C11" s="24"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="23"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -29589,7 +29813,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -29608,14 +29832,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="25"/>
     </row>
-    <row r="16" spans="1:31" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
       <c r="B16" s="27" t="s">
         <v>6</v>
@@ -29735,26 +29959,26 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC7A6C4B-FDDD-4D0B-90C8-5B01A1705645}">
   <dimension ref="A1:AE17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -29765,7 +29989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -29773,7 +29997,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -29790,7 +30014,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -29882,7 +30106,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -29926,7 +30150,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -29970,7 +30194,7 @@
         <v>-73</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
@@ -30014,7 +30238,7 @@
         <v>629.71799999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -30061,7 +30285,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -30106,7 +30330,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -30115,14 +30339,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -30194,7 +30418,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -30239,14 +30463,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -30367,7 +30591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="14:15" x14ac:dyDescent="0.3">
       <c r="N17" s="3" t="s">
         <v>50</v>
       </c>
@@ -30385,27 +30609,27 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4D735A-7F76-4974-8609-056275EBAB78}">
   <dimension ref="A1:AE21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -30416,7 +30640,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -30432,7 +30656,7 @@
         <v>0.14749999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -30450,7 +30674,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -30542,7 +30766,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -30580,7 +30804,7 @@
         <v>45.42</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -30618,7 +30842,7 @@
         <v>-52.89</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -30656,7 +30880,7 @@
         <v>623.61</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -30703,7 +30927,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -30748,7 +30972,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -30757,14 +30981,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -30857,7 +31081,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -30896,14 +31120,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -31024,11 +31248,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F416346-DDA5-482A-BBD3-70514486EDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7F1798-1087-4F15-A16B-810D4A81F2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="15" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="14" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId14"/>
     <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId15"/>
     <sheet name="FlxTest10mm_4" sheetId="23" r:id="rId16"/>
+    <sheet name="FlxTest10mm_5" sheetId="24" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -293,8 +294,62 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={1412A674-61A3-4D66-9D3E-5374366576D7}</author>
+    <author>tc={7BAEFA08-D790-466D-A190-320CBA26570E}</author>
+    <author>tc={E1852E19-B84C-463E-A0CB-BF0ADA1DC1BE}</author>
+    <author>tc={13B25287-2F50-4E04-AC48-02AB262B1DE9}</author>
+    <author>tc={50243B4E-1A69-4602-BC70-D861CF3BE17E}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{1412A674-61A3-4D66-9D3E-5374366576D7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{7BAEFA08-D790-466D-A190-320CBA26570E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{E1852E19-B84C-463E-A0CB-BF0ADA1DC1BE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Max contracted length normalized by resting length</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{13B25287-2F50-4E04-AC48-02AB262B1DE9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kmax</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{50243B4E-1A69-4602-BC70-D861CF3BE17E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="94">
   <si>
     <t>Test #</t>
   </si>
@@ -541,12 +596,48 @@
   <si>
     <t>oooooo</t>
   </si>
+  <si>
+    <t>Flex test 5</t>
+  </si>
+  <si>
+    <t>*4 N pretension</t>
+  </si>
+  <si>
+    <t>*/**</t>
+  </si>
+  <si>
+    <t>**noticed tendon is actually 35 mm. Possible plastic deformation or incorrect initial measurement.</t>
+  </si>
+  <si>
+    <t>tendon 37 mm under load</t>
+  </si>
+  <si>
+    <t>****</t>
+  </si>
+  <si>
+    <t>5 N pretension, Lm = 406</t>
+  </si>
+  <si>
+    <t>11.43N pretension</t>
+  </si>
+  <si>
+    <t>tendon 38mm</t>
+  </si>
+  <si>
+    <t>18.7 N pretension</t>
+  </si>
+  <si>
+    <t>tendon 39mm</t>
+  </si>
+  <si>
+    <t>23.5 N pretension</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,6 +679,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -766,7 +863,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -801,6 +898,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -4973,6 +5071,480 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-CE28-4152-9B9D-F4BE9A57F41C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1604021071"/>
+        <c:axId val="1604018671"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1604021071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604018671"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1604018671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604021071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.21909860469440826"/>
+                  <c:y val="1.901586316257094E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_5!$C$7:$AE$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>-113.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-102</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-94.207999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-87.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-80.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-112.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-102.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-92</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-86</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-77.694000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-70.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-65.129000000000005</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-60.462000000000003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-50.768999999999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-45.74</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-40.716999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-34.972999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-29.228999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_5!$C$16:$X$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>-4.9109379769919088E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.83403244093913598</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.7200073984477242</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.900103689581238</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.5474653742290858</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-18.319240363209158</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.14749659592534689</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.77675624770615737</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1.8437074490668364</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.9228908759206247</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-5.0559532620861303</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-7.5053908133297975</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-10.014296277159817</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-12.137120802638771</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-16.328074980556799</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-18.009994411252876</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-19.562355739823911</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-20.200690671447745</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-19.951096115672847</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8ECD-4C0F-A506-F9E8935F6B6D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9532,6 +10104,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors17.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -13465,6 +14077,522 @@
 </file>
 
 <file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -18430,6 +19558,49 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>410920</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>46935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>1130338</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>78684</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58E722E8-FDD3-4A7B-AD3B-C615A565B17C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -19178,6 +20349,26 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{1412A674-61A3-4D66-9D3E-5374366576D7}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{7BAEFA08-D790-466D-A190-320CBA26570E}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{E1852E19-B84C-463E-A0CB-BF0ADA1DC1BE}">
+    <text>Max contracted length normalized by resting length</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{13B25287-2F50-4E04-AC48-02AB262B1DE9}">
+    <text>Kmax</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{50243B4E-1A69-4602-BC70-D861CF3BE17E}">
+    <text>Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C83896A-0586-4C90-B5FD-474633C66A37}">
   <dimension ref="A1:AJ27"/>
@@ -25852,6 +27043,998 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4491407B-6063-4D38-82E5-CAFE7B595AB6}">
+  <dimension ref="A1:AK36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2">
+        <v>406</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3">
+        <v>338</v>
+      </c>
+      <c r="D3">
+        <f>(C3/C2)</f>
+        <v>0.83251231527093594</v>
+      </c>
+      <c r="E3">
+        <f>1-D3</f>
+        <v>0.16748768472906406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" t="s">
+        <v>84</v>
+      </c>
+      <c r="O4" s="3"/>
+      <c r="Q4" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="D6">
+        <v>3.4</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>11.8</v>
+      </c>
+      <c r="G6">
+        <v>18.5</v>
+      </c>
+      <c r="H6">
+        <v>74.64</v>
+      </c>
+      <c r="I6">
+        <v>0.6</v>
+      </c>
+      <c r="J6">
+        <v>3.16</v>
+      </c>
+      <c r="K6">
+        <v>7.5</v>
+      </c>
+      <c r="L6">
+        <v>11.89</v>
+      </c>
+      <c r="M6">
+        <v>20.6</v>
+      </c>
+      <c r="N6">
+        <v>30.58</v>
+      </c>
+      <c r="O6">
+        <v>40.848999999999997</v>
+      </c>
+      <c r="P6">
+        <v>49.58</v>
+      </c>
+      <c r="Q6">
+        <v>66.7</v>
+      </c>
+      <c r="R6">
+        <v>73.463999999999999</v>
+      </c>
+      <c r="S6">
+        <v>79.912000000000006</v>
+      </c>
+      <c r="T6">
+        <v>82.4</v>
+      </c>
+      <c r="U6">
+        <v>81.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16">
+        <v>-113.5</v>
+      </c>
+      <c r="D7">
+        <v>-102</v>
+      </c>
+      <c r="E7">
+        <v>-94.207999999999998</v>
+      </c>
+      <c r="F7">
+        <v>-87.7</v>
+      </c>
+      <c r="G7">
+        <v>-80.5</v>
+      </c>
+      <c r="H7">
+        <v>-45</v>
+      </c>
+      <c r="I7">
+        <v>-112.5</v>
+      </c>
+      <c r="J7">
+        <v>-102.4</v>
+      </c>
+      <c r="K7">
+        <v>-92</v>
+      </c>
+      <c r="L7">
+        <v>-86</v>
+      </c>
+      <c r="M7">
+        <v>-77.694000000000003</v>
+      </c>
+      <c r="N7">
+        <v>-70.8</v>
+      </c>
+      <c r="O7">
+        <v>-65.129000000000005</v>
+      </c>
+      <c r="P7">
+        <v>-60.462000000000003</v>
+      </c>
+      <c r="Q7">
+        <v>-50.768999999999998</v>
+      </c>
+      <c r="R7">
+        <v>-45.74</v>
+      </c>
+      <c r="S7">
+        <v>-40.716999999999999</v>
+      </c>
+      <c r="T7">
+        <v>-34.972999999999999</v>
+      </c>
+      <c r="U7">
+        <v>-29.228999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16">
+        <v>624</v>
+      </c>
+      <c r="D8">
+        <v>623</v>
+      </c>
+      <c r="E8">
+        <v>624.36500000000001</v>
+      </c>
+      <c r="F8">
+        <v>624</v>
+      </c>
+      <c r="G8">
+        <v>623</v>
+      </c>
+      <c r="H8">
+        <v>622.79999999999995</v>
+      </c>
+      <c r="I8">
+        <v>625</v>
+      </c>
+      <c r="J8">
+        <v>624.5</v>
+      </c>
+      <c r="K8">
+        <v>624</v>
+      </c>
+      <c r="L8">
+        <v>622</v>
+      </c>
+      <c r="M8">
+        <v>622</v>
+      </c>
+      <c r="N8">
+        <v>625</v>
+      </c>
+      <c r="O8">
+        <v>624.36500000000001</v>
+      </c>
+      <c r="P8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="Q8">
+        <v>622.85</v>
+      </c>
+      <c r="R8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="S8">
+        <v>622.85</v>
+      </c>
+      <c r="T8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="U8">
+        <v>622.79999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="15">
+        <v>82</v>
+      </c>
+      <c r="D9" s="1">
+        <v>81</v>
+      </c>
+      <c r="E9" s="1">
+        <v>83</v>
+      </c>
+      <c r="F9" s="1">
+        <v>86</v>
+      </c>
+      <c r="G9" s="1">
+        <v>84</v>
+      </c>
+      <c r="H9" s="1">
+        <v>88</v>
+      </c>
+      <c r="I9" s="1">
+        <v>85</v>
+      </c>
+      <c r="J9" s="1">
+        <v>85.5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>85</v>
+      </c>
+      <c r="L9" s="1">
+        <v>85</v>
+      </c>
+      <c r="M9" s="1">
+        <v>88</v>
+      </c>
+      <c r="N9" s="1">
+        <v>88</v>
+      </c>
+      <c r="O9" s="1">
+        <v>89</v>
+      </c>
+      <c r="P9" s="1">
+        <v>90</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>90</v>
+      </c>
+      <c r="R9" s="1">
+        <v>89</v>
+      </c>
+      <c r="S9" s="1">
+        <v>90</v>
+      </c>
+      <c r="T9" s="1">
+        <v>89</v>
+      </c>
+      <c r="U9" s="1">
+        <v>90</v>
+      </c>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16">
+        <v>339</v>
+      </c>
+      <c r="D10" s="33">
+        <v>340</v>
+      </c>
+      <c r="E10" s="33">
+        <v>341</v>
+      </c>
+      <c r="F10" s="33">
+        <v>343</v>
+      </c>
+      <c r="G10" s="33">
+        <v>346</v>
+      </c>
+      <c r="H10" s="33">
+        <v>378</v>
+      </c>
+      <c r="I10" s="33">
+        <v>336</v>
+      </c>
+      <c r="J10" s="33">
+        <v>337</v>
+      </c>
+      <c r="K10" s="33">
+        <v>339</v>
+      </c>
+      <c r="L10" s="33">
+        <v>341</v>
+      </c>
+      <c r="M10" s="33">
+        <v>346</v>
+      </c>
+      <c r="N10" s="33">
+        <v>351</v>
+      </c>
+      <c r="O10" s="33">
+        <v>356</v>
+      </c>
+      <c r="P10" s="33">
+        <v>361</v>
+      </c>
+      <c r="Q10" s="33">
+        <v>370</v>
+      </c>
+      <c r="R10" s="33">
+        <v>374</v>
+      </c>
+      <c r="S10" s="33">
+        <v>378</v>
+      </c>
+      <c r="T10" s="33">
+        <v>381</v>
+      </c>
+      <c r="U10" s="33">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>245.83</v>
+      </c>
+      <c r="D13">
+        <v>245.83</v>
+      </c>
+      <c r="E13">
+        <v>245.83</v>
+      </c>
+      <c r="F13">
+        <v>245.83</v>
+      </c>
+      <c r="G13">
+        <v>245.83</v>
+      </c>
+      <c r="H13">
+        <v>245.83</v>
+      </c>
+      <c r="I13">
+        <v>245.83</v>
+      </c>
+      <c r="J13">
+        <v>245.83</v>
+      </c>
+      <c r="K13">
+        <v>245.83</v>
+      </c>
+      <c r="L13">
+        <v>245.83</v>
+      </c>
+      <c r="M13">
+        <v>245.83</v>
+      </c>
+      <c r="N13">
+        <v>245.83</v>
+      </c>
+      <c r="O13">
+        <v>245.83</v>
+      </c>
+      <c r="P13">
+        <v>245.83</v>
+      </c>
+      <c r="Q13">
+        <v>245.83</v>
+      </c>
+      <c r="R13">
+        <v>245.83</v>
+      </c>
+      <c r="S13">
+        <v>245.83</v>
+      </c>
+      <c r="T13">
+        <v>245.83</v>
+      </c>
+      <c r="U13">
+        <v>245.83</v>
+      </c>
+      <c r="V13">
+        <v>245.83</v>
+      </c>
+      <c r="W13">
+        <v>245.83</v>
+      </c>
+      <c r="X13">
+        <v>245.83</v>
+      </c>
+      <c r="Y13">
+        <v>245.83</v>
+      </c>
+      <c r="Z13">
+        <v>245.83</v>
+      </c>
+      <c r="AA13">
+        <v>245.83</v>
+      </c>
+      <c r="AB13">
+        <v>245.83</v>
+      </c>
+      <c r="AC13">
+        <v>245.83</v>
+      </c>
+      <c r="AD13">
+        <v>245.83</v>
+      </c>
+      <c r="AE13">
+        <v>245.83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>33</v>
+      </c>
+      <c r="F14">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>62</v>
+      </c>
+      <c r="H14">
+        <v>85</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
+      <c r="K14">
+        <v>35</v>
+      </c>
+      <c r="L14">
+        <v>44</v>
+      </c>
+      <c r="M14">
+        <v>50</v>
+      </c>
+      <c r="N14">
+        <v>76</v>
+      </c>
+      <c r="O14">
+        <v>82</v>
+      </c>
+      <c r="P14">
+        <v>85</v>
+      </c>
+      <c r="Q14">
+        <v>88</v>
+      </c>
+      <c r="R14">
+        <v>87</v>
+      </c>
+      <c r="S14">
+        <v>85</v>
+      </c>
+      <c r="T14">
+        <v>85</v>
+      </c>
+      <c r="U14">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="16">
+        <f>-C6*SIN(RADIANS(C9+5.25))*C13/1000</f>
+        <v>-4.9109379769919088E-2</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:AE16" si="0">-D6*SIN(RADIANS(D9+5.25))*D13/1000</f>
+        <v>-0.83403244093913598</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.7200073984477242</v>
+      </c>
+      <c r="F16" s="16">
+        <f t="shared" si="0"/>
+        <v>-2.900103689581238</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>-4.5474653742290858</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>-18.319240363209158</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>-0.14749659592534689</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>-0.77675624770615737</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.8437074490668364</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="0"/>
+        <v>-2.9228908759206247</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>-5.0559532620861303</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="0"/>
+        <v>-7.5053908133297975</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="0"/>
+        <v>-10.014296277159817</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="0"/>
+        <v>-12.137120802638771</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>-16.328074980556799</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>-18.009994411252876</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>-19.562355739823911</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>-20.200690671447745</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>-19.951096115672847</v>
+      </c>
+      <c r="V16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="H17" t="s">
+        <v>83</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="Q17" t="s">
+        <v>86</v>
+      </c>
+      <c r="R17" t="s">
+        <v>88</v>
+      </c>
+      <c r="S17" t="s">
+        <v>89</v>
+      </c>
+      <c r="T17" t="s">
+        <v>91</v>
+      </c>
+      <c r="U17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s">
+        <v>85</v>
+      </c>
+      <c r="S18" t="s">
+        <v>90</v>
+      </c>
+      <c r="T18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="34"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D1208C-7CDD-421F-9FF0-096EE144B4F3}">
   <dimension ref="A1:AJ15"/>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7F1798-1087-4F15-A16B-810D4A81F2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9920989-4A16-4DCE-8028-31F803D33A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="14" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="8" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -31,21 +31,10 @@
     <sheet name="FlxTest10mm_4" sheetId="23" r:id="rId16"/>
     <sheet name="FlxTest10mm_5" sheetId="24" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -60,18 +49,36 @@
   <commentList>
     <comment ref="D3" authorId="0" shapeId="0" xr:uid="{31540696-8989-4ECF-9DA4-105271D5E559}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
+        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="1" shapeId="0" xr:uid="{4ABBB369-E711-4E3D-9229-46727333D172}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -90,42 +97,87 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{29300245-EF40-4E4F-8F6D-1266C425EACE}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{00298076-0747-4A6C-9F96-1B56DD480064}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{BDF31CF8-F642-45F3-81CA-9C8FF04449E8}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
+        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{C8A435E7-474C-41D6-A569-7731B05DEC1C}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{6E231C95-A9F8-4BE0-A13C-7D1696721C9B}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     So it can reach -114 degrees</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -144,42 +196,87 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{7429FFDB-7320-40ED-9095-CADFEE0453D3}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{56BB9B1E-AE6F-4367-98DA-1738BC17BA33}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{181A90AF-6CB1-444A-AC50-05218AF784A8}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
+        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{E9CB4941-5049-48DD-9386-0FE986486E00}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{4B24DE55-490A-4648-B1F6-ECBEA4FEDB7F}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     So it can reach -114 degrees</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -198,42 +295,87 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{F99A6D76-844F-423C-8E72-632020492202}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{57404540-41ED-4CFC-A34A-B0C06D36E435}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{FD23BCFD-5D0D-499D-B1BC-4D31A4174384}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
+        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{34C2BEB3-8987-42FD-9240-D19AB0F3395E}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{619279C5-5896-4658-A891-94E7656E0604}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     So it can reach -114 degrees</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -252,42 +394,87 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{B3DD3E36-DE23-4526-822F-7544076C12AF}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{44F69930-AA26-4737-9556-6F232E8AC193}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{6E9C7D1B-6D13-4A15-A63C-B49E3DDDDD72}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
+        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{A117DFD4-25AF-41A6-9D26-99F7C9197E59}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{70F2E1CB-BEA3-46AD-8012-48E9D04ADA3E}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     So it can reach -114 degrees</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -306,42 +493,87 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{1412A674-61A3-4D66-9D3E-5374366576D7}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{7BAEFA08-D790-466D-A190-320CBA26570E}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
+        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{E1852E19-B84C-463E-A0CB-BF0ADA1DC1BE}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
+        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{13B25287-2F50-4E04-AC48-02AB262B1DE9}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{50243B4E-1A69-4602-BC70-D861CF3BE17E}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -349,7 +581,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="99">
   <si>
     <t>Test #</t>
   </si>
@@ -632,12 +864,27 @@
   <si>
     <t>23.5 N pretension</t>
   </si>
+  <si>
+    <t>avg pressure</t>
+  </si>
+  <si>
+    <t>Average pressure</t>
+  </si>
+  <si>
+    <t>Noticed that bracket was shifting under higher loads.</t>
+  </si>
+  <si>
+    <t>Bracket failed material pull out.</t>
+  </si>
+  <si>
+    <t>abg pressure</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,14 +927,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,12 +949,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -863,7 +1098,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -894,11 +1129,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -2663,7 +2893,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>ExtTest10mm_12!$D$7:$S$7</c:f>
+              <c:f>ExtTest10mm_12!$C$7:$R$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -2720,7 +2950,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ExtTest10mm_12!$D$16:$AB$16</c:f>
+              <c:f>ExtTest10mm_12!$C$16:$AA$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
@@ -19964,9 +20194,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -20004,7 +20234,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -20110,7 +20340,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -20252,7 +20482,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -21325,7 +21555,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA3ACFF-8EC2-4AAF-BDC7-460D102A0BEE}">
-  <dimension ref="A1:AE21"/>
+  <dimension ref="A1:AE23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
@@ -22005,6 +22235,17 @@
     <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="21" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="N22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="N23">
+        <f>AVERAGE(C8:O8)</f>
+        <v>618.36923076923074</v>
       </c>
     </row>
   </sheetData>
@@ -22701,6 +22942,15 @@
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
+      <c r="O21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O22">
+        <f>AVERAGE(C8:P8)</f>
+        <v>622.92857142857144</v>
+      </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="29" t="s">
@@ -22896,65 +23146,64 @@
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6">
+        <v>1.56</v>
+      </c>
       <c r="D6">
-        <v>1.56</v>
+        <v>7.27</v>
       </c>
       <c r="E6">
-        <v>7.27</v>
+        <v>18.05</v>
       </c>
       <c r="F6">
-        <v>18.05</v>
+        <v>22.13</v>
       </c>
       <c r="G6">
-        <v>22.13</v>
+        <v>24.334</v>
       </c>
       <c r="H6">
-        <v>24.334</v>
+        <v>23.155999999999999</v>
       </c>
       <c r="I6">
-        <v>23.155999999999999</v>
+        <v>25.13</v>
       </c>
       <c r="J6">
-        <v>25.13</v>
+        <v>25.15</v>
       </c>
       <c r="K6">
-        <v>25.15</v>
+        <v>26.1</v>
       </c>
       <c r="L6">
-        <v>26.1</v>
+        <v>29.18</v>
       </c>
       <c r="M6">
-        <v>29.18</v>
+        <v>31.68</v>
       </c>
       <c r="N6">
-        <v>31.68</v>
+        <v>32.74</v>
       </c>
       <c r="O6">
-        <v>32.74</v>
+        <v>34.68</v>
       </c>
       <c r="P6">
-        <v>34.68</v>
+        <v>38.82</v>
       </c>
       <c r="Q6">
-        <v>38.82</v>
+        <v>29.24</v>
       </c>
       <c r="R6">
-        <v>29.24</v>
+        <v>22.6</v>
       </c>
       <c r="S6">
-        <v>22.6</v>
+        <v>20.248000000000001</v>
       </c>
       <c r="T6">
-        <v>20.248000000000001</v>
+        <v>19.89</v>
       </c>
       <c r="U6">
-        <v>19.89</v>
+        <v>18.373999999999999</v>
       </c>
       <c r="V6">
-        <v>18.373999999999999</v>
-      </c>
-      <c r="W6">
         <v>0.40200000000000002</v>
       </c>
     </row>
@@ -22963,65 +23212,64 @@
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="30"/>
+      <c r="C7">
+        <v>28.29</v>
+      </c>
       <c r="D7">
-        <v>28.29</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="E7">
-        <v>18.149999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="F7">
-        <v>1.29</v>
+        <v>-14.86</v>
       </c>
       <c r="G7">
-        <v>-14.86</v>
+        <v>-25.64</v>
       </c>
       <c r="H7">
-        <v>-25.64</v>
+        <v>-36.76</v>
       </c>
       <c r="I7">
-        <v>-36.76</v>
+        <v>-42.87</v>
       </c>
       <c r="J7">
-        <v>-42.87</v>
+        <v>-49.33</v>
       </c>
       <c r="K7">
-        <v>-49.33</v>
+        <v>-56.87</v>
       </c>
       <c r="L7">
-        <v>-56.87</v>
+        <v>-68.36</v>
       </c>
       <c r="M7">
-        <v>-68.36</v>
+        <v>-77.69</v>
       </c>
       <c r="N7">
-        <v>-77.69</v>
+        <v>-84.16</v>
       </c>
       <c r="O7">
-        <v>-84.16</v>
+        <v>-90.1</v>
       </c>
       <c r="P7">
-        <v>-90.1</v>
+        <v>-99.233999999999995</v>
       </c>
       <c r="Q7">
-        <v>-99.233999999999995</v>
+        <v>-82</v>
       </c>
       <c r="R7">
-        <v>-82</v>
+        <v>-65.48</v>
       </c>
       <c r="S7">
-        <v>-65.48</v>
+        <v>-47.537999999999997</v>
       </c>
       <c r="T7">
-        <v>-47.537999999999997</v>
+        <v>-26.72</v>
       </c>
       <c r="U7">
-        <v>-26.72</v>
+        <v>-6.2530000000000001</v>
       </c>
       <c r="V7">
-        <v>-6.2530000000000001</v>
-      </c>
-      <c r="W7">
         <v>31.442</v>
       </c>
     </row>
@@ -23030,65 +23278,64 @@
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8">
+        <v>622.09299999999996</v>
+      </c>
       <c r="D8">
+        <v>620.57899999999995</v>
+      </c>
+      <c r="E8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="F8">
+        <v>621.34</v>
+      </c>
+      <c r="G8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="H8">
+        <v>620.58000000000004</v>
+      </c>
+      <c r="I8">
+        <v>622.85</v>
+      </c>
+      <c r="J8">
         <v>622.09299999999996</v>
       </c>
-      <c r="E8">
+      <c r="K8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="L8">
+        <v>623.04999999999995</v>
+      </c>
+      <c r="M8">
+        <v>623.33600000000001</v>
+      </c>
+      <c r="N8">
         <v>620.57899999999995</v>
       </c>
-      <c r="F8">
+      <c r="O8">
+        <v>622.85</v>
+      </c>
+      <c r="P8">
         <v>621.33600000000001</v>
-      </c>
-      <c r="G8">
-        <v>621.34</v>
-      </c>
-      <c r="H8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="I8">
-        <v>620.58000000000004</v>
-      </c>
-      <c r="J8">
-        <v>622.85</v>
-      </c>
-      <c r="K8">
-        <v>622.09299999999996</v>
-      </c>
-      <c r="L8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="M8">
-        <v>623.04999999999995</v>
-      </c>
-      <c r="N8">
-        <v>623.33600000000001</v>
-      </c>
-      <c r="O8">
-        <v>620.57899999999995</v>
-      </c>
-      <c r="P8">
-        <v>622.85</v>
       </c>
       <c r="Q8">
         <v>621.33600000000001</v>
       </c>
       <c r="R8">
+        <v>622.09</v>
+      </c>
+      <c r="S8">
+        <v>622.6</v>
+      </c>
+      <c r="T8">
+        <v>622.85</v>
+      </c>
+      <c r="U8">
         <v>621.33600000000001</v>
       </c>
-      <c r="S8">
-        <v>622.09</v>
-      </c>
-      <c r="T8">
-        <v>622.6</v>
-      </c>
-      <c r="U8">
-        <v>622.85</v>
-      </c>
       <c r="V8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="W8">
         <v>620.57899999999995</v>
       </c>
     </row>
@@ -23099,24 +23346,26 @@
       <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="31"/>
+      <c r="C9" s="1">
+        <v>83</v>
+      </c>
       <c r="D9" s="1">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E9" s="1">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G9" s="1">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H9" s="1">
         <v>73</v>
       </c>
       <c r="I9" s="1">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J9" s="1">
         <v>71</v>
@@ -23125,41 +23374,39 @@
         <v>71</v>
       </c>
       <c r="L9" s="1">
+        <v>69</v>
+      </c>
+      <c r="M9" s="1">
+        <v>68</v>
+      </c>
+      <c r="N9" s="1">
         <v>71</v>
       </c>
-      <c r="M9" s="1">
+      <c r="O9" s="1">
         <v>69</v>
       </c>
-      <c r="N9" s="1">
-        <v>68</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
+        <v>70</v>
+      </c>
+      <c r="Q9" s="1">
         <v>71</v>
-      </c>
-      <c r="P9" s="1">
-        <v>69</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>70</v>
       </c>
       <c r="R9" s="1">
         <v>71</v>
       </c>
       <c r="S9" s="1">
-        <v>71</v>
+        <v>73.5</v>
       </c>
       <c r="T9" s="1">
-        <v>73.5</v>
+        <v>75</v>
       </c>
       <c r="U9" s="1">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="V9" s="1">
-        <v>77.5</v>
-      </c>
-      <c r="W9" s="1">
         <v>84</v>
       </c>
+      <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
@@ -23173,72 +23420,70 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
-      <c r="AK9" s="1"/>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="30"/>
+      <c r="C10">
+        <v>367</v>
+      </c>
       <c r="D10">
         <v>367</v>
       </c>
       <c r="E10">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="F10">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="G10">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H10">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="I10">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="J10">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="K10">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="L10">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="M10">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="N10">
         <v>428</v>
       </c>
       <c r="O10">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="P10">
         <v>434</v>
       </c>
       <c r="Q10">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="R10">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="S10">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="T10">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="U10">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="V10">
-        <v>386</v>
-      </c>
-      <c r="W10">
         <v>366</v>
       </c>
     </row>
@@ -23249,7 +23494,7 @@
       <c r="B11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="31"/>
+      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -23283,21 +23528,19 @@
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
-      <c r="AK11" s="1"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="30"/>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13">
         <v>249.71</v>
       </c>
       <c r="D13">
@@ -23379,9 +23622,6 @@
         <v>249.71</v>
       </c>
       <c r="AD13">
-        <v>249.71</v>
-      </c>
-      <c r="AE13">
         <v>249.71</v>
       </c>
     </row>
@@ -23390,24 +23630,26 @@
       <c r="B14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="30"/>
+      <c r="C14">
+        <v>78</v>
+      </c>
       <c r="D14">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E14">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G14">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J14">
         <v>30</v>
@@ -23416,39 +23658,36 @@
         <v>30</v>
       </c>
       <c r="L14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P14">
         <v>23</v>
       </c>
       <c r="Q14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="S14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="U14">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="V14">
-        <v>50</v>
-      </c>
-      <c r="W14">
         <v>88</v>
       </c>
     </row>
@@ -23457,7 +23696,7 @@
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="32"/>
+      <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -23491,96 +23730,95 @@
       <c r="AH15" s="2"/>
       <c r="AI15" s="2"/>
       <c r="AJ15" s="2"/>
-      <c r="AK15" s="2"/>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="30">
-        <f>C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
-        <v>0</v>
+      <c r="C16" s="16">
+        <f t="shared" ref="C16:AD16" si="0">C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
+        <v>0.38934455560856757</v>
       </c>
       <c r="D16" s="16">
-        <f t="shared" ref="D16:AE16" si="0">D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
-        <v>0.38934455560856757</v>
-      </c>
-      <c r="E16" s="16">
         <f t="shared" si="0"/>
         <v>1.8112948210918218</v>
       </c>
+      <c r="E16" s="16">
+        <f>E6*SIN(RADIANS(E9+5.15))*E13/1000</f>
+        <v>4.4750917512529496</v>
+      </c>
       <c r="F16" s="16">
-        <f>F6*SIN(RADIANS(F9+5.15))*F13/1000</f>
-        <v>4.4750917512529496</v>
+        <f t="shared" si="0"/>
+        <v>5.4446222516176634</v>
       </c>
       <c r="G16" s="16">
         <f t="shared" si="0"/>
-        <v>5.4446222516176634</v>
+        <v>5.9469453841091626</v>
       </c>
       <c r="H16" s="16">
         <f t="shared" si="0"/>
-        <v>5.9469453841091626</v>
+        <v>5.6590559428960212</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="0"/>
-        <v>5.6590559428960212</v>
+        <v>6.0927652115792634</v>
       </c>
       <c r="J16" s="16">
         <f t="shared" si="0"/>
-        <v>6.0927652115792634</v>
+        <v>6.0976142089621366</v>
       </c>
       <c r="K16" s="16">
         <f t="shared" si="0"/>
-        <v>6.0976142089621366</v>
+        <v>6.3279415846485803</v>
       </c>
       <c r="L16" s="16">
         <f t="shared" si="0"/>
-        <v>6.3279415846485803</v>
+        <v>7.0095037627925798</v>
       </c>
       <c r="M16" s="16">
         <f t="shared" si="0"/>
-        <v>7.0095037627925798</v>
+        <v>7.5711771242618884</v>
       </c>
       <c r="N16" s="16">
         <f t="shared" si="0"/>
-        <v>7.5711771242618884</v>
+        <v>7.937808715762241</v>
       </c>
       <c r="O16" s="16">
         <f t="shared" si="0"/>
-        <v>7.937808715762241</v>
+        <v>8.3306919291859725</v>
       </c>
       <c r="P16" s="16">
         <f t="shared" si="0"/>
-        <v>8.3306919291859725</v>
+        <v>9.369972199445602</v>
       </c>
       <c r="Q16" s="16">
         <f t="shared" si="0"/>
-        <v>9.369972199445602</v>
+        <v>7.0892341737595572</v>
       </c>
       <c r="R16" s="16">
         <f t="shared" si="0"/>
-        <v>7.0892341737595572</v>
+        <v>5.4793670426458965</v>
       </c>
       <c r="S16" s="16">
         <f t="shared" si="0"/>
-        <v>5.4793670426458965</v>
+        <v>4.957246848957868</v>
       </c>
       <c r="T16" s="16">
         <f t="shared" si="0"/>
-        <v>4.957246848957868</v>
+        <v>4.8935172428682936</v>
       </c>
       <c r="U16" s="16">
         <f t="shared" si="0"/>
-        <v>4.8935172428682936</v>
+        <v>4.5504713609212226</v>
       </c>
       <c r="V16" s="16">
         <f t="shared" si="0"/>
-        <v>4.5504713609212226</v>
+        <v>0.10037237370560359</v>
       </c>
       <c r="W16" s="16">
         <f t="shared" si="0"/>
-        <v>0.10037237370560359</v>
+        <v>0</v>
       </c>
       <c r="X16" s="16">
         <f t="shared" si="0"/>
@@ -23610,16 +23848,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
+      <c r="M17" s="3"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
@@ -23652,10 +23886,17 @@
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
+      <c r="O24" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
+      <c r="O25">
+        <f>AVERAGE(C8:V8)</f>
+        <v>621.77425000000005</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
@@ -23705,8 +23946,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -26549,34 +26791,34 @@
       <c r="J10">
         <v>447</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10">
         <v>445</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10">
         <v>452</v>
       </c>
-      <c r="M10" s="33">
+      <c r="M10">
         <v>449</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10">
         <v>403</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10">
         <v>407</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10">
         <v>415</v>
       </c>
-      <c r="Q10" s="33">
+      <c r="Q10">
         <v>430</v>
       </c>
-      <c r="R10" s="33">
+      <c r="R10">
         <v>438</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10">
         <v>450</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10">
         <v>453</v>
       </c>
     </row>
@@ -26868,7 +27110,7 @@
         <v>-14.697192119709124</v>
       </c>
       <c r="L16" s="16">
-        <f t="shared" ref="D16:AE16" si="1">-L6*SIN(RADIANS(L9+5.15))*L13/1000</f>
+        <f t="shared" ref="L16:AE16" si="1">-L6*SIN(RADIANS(L9+5.15))*L13/1000</f>
         <v>-15.358895091501429</v>
       </c>
       <c r="M16" s="16">
@@ -27491,58 +27733,58 @@
       <c r="C10" s="16">
         <v>339</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10">
         <v>340</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10">
         <v>341</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10">
         <v>343</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10">
         <v>346</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10">
         <v>378</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10">
         <v>336</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10">
         <v>337</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10">
         <v>339</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10">
         <v>341</v>
       </c>
-      <c r="M10" s="33">
+      <c r="M10">
         <v>346</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10">
         <v>351</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10">
         <v>356</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10">
         <v>361</v>
       </c>
-      <c r="Q10" s="33">
+      <c r="Q10">
         <v>370</v>
       </c>
-      <c r="R10" s="33">
+      <c r="R10">
         <v>374</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10">
         <v>378</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10">
         <v>381</v>
       </c>
-      <c r="U10" s="33">
+      <c r="U10">
         <v>382</v>
       </c>
     </row>
@@ -27990,7 +28232,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
-      <c r="B27" s="34"/>
+      <c r="B27" s="3"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
@@ -31659,7 +31901,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07511B1B-CFA9-4E3E-A27D-F86FFAE12463}">
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
@@ -32132,6 +32374,11 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -32141,7 +32388,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC7A6C4B-FDDD-4D0B-90C8-5B01A1705645}">
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="3"/>
@@ -32782,6 +33029,11 @@
         <v>51</v>
       </c>
     </row>
+    <row r="19" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="O19" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -32791,7 +33043,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4D735A-7F76-4974-8609-056275EBAB78}">
-  <dimension ref="A1:AE21"/>
+  <dimension ref="A1:AE22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
@@ -33439,6 +33691,15 @@
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
+      <c r="N21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="N22">
+        <f>AVERAGE(C8:M8)</f>
+        <v>624.85518181818179</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9920989-4A16-4DCE-8028-31F803D33A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89EFDFE-5E7B-4363-A0D8-5ADE892DBC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="8" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="16" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -31,10 +31,21 @@
     <sheet name="FlxTest10mm_4" sheetId="23" r:id="rId16"/>
     <sheet name="FlxTest10mm_5" sheetId="24" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -49,36 +60,18 @@
   <commentList>
     <comment ref="D3" authorId="0" shapeId="0" xr:uid="{31540696-8989-4ECF-9DA4-105271D5E559}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
-        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="1" shapeId="0" xr:uid="{4ABBB369-E711-4E3D-9229-46727333D172}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -97,87 +90,42 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{29300245-EF40-4E4F-8F6D-1266C425EACE}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{00298076-0747-4A6C-9F96-1B56DD480064}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{BDF31CF8-F642-45F3-81CA-9C8FF04449E8}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
-        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{C8A435E7-474C-41D6-A569-7731B05DEC1C}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{6E231C95-A9F8-4BE0-A13C-7D1696721C9B}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     So it can reach -114 degrees</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -196,87 +144,42 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{7429FFDB-7320-40ED-9095-CADFEE0453D3}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{56BB9B1E-AE6F-4367-98DA-1738BC17BA33}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{181A90AF-6CB1-444A-AC50-05218AF784A8}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
-        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{E9CB4941-5049-48DD-9386-0FE986486E00}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{4B24DE55-490A-4648-B1F6-ECBEA4FEDB7F}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     So it can reach -114 degrees</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -295,87 +198,42 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{F99A6D76-844F-423C-8E72-632020492202}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{57404540-41ED-4CFC-A34A-B0C06D36E435}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{FD23BCFD-5D0D-499D-B1BC-4D31A4174384}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
-        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{34C2BEB3-8987-42FD-9240-D19AB0F3395E}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{619279C5-5896-4658-A891-94E7656E0604}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     So it can reach -114 degrees</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -394,87 +252,42 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{B3DD3E36-DE23-4526-822F-7544076C12AF}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{44F69930-AA26-4737-9556-6F232E8AC193}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{6E9C7D1B-6D13-4A15-A63C-B49E3DDDDD72}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
-        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{A117DFD4-25AF-41A6-9D26-99F7C9197E59}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{70F2E1CB-BEA3-46AD-8012-48E9D04ADA3E}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     So it can reach -114 degrees</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -493,87 +306,42 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{1412A674-61A3-4D66-9D3E-5374366576D7}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{7BAEFA08-D790-466D-A190-320CBA26570E}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Recheck after test</t>
-        </r>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{E1852E19-B84C-463E-A0CB-BF0ADA1DC1BE}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Max contracted length normalized by resting length</t>
-        </r>
       </text>
     </comment>
     <comment ref="E3" authorId="3" shapeId="0" xr:uid="{13B25287-2F50-4E04-AC48-02AB262B1DE9}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="4" shapeId="0" xr:uid="{50243B4E-1A69-4602-BC70-D861CF3BE17E}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -581,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="98">
   <si>
     <t>Test #</t>
   </si>
@@ -824,9 +592,6 @@
   </si>
   <si>
     <t>^Collected by Moe &amp; Ben</t>
-  </si>
-  <si>
-    <t>oooooo</t>
   </si>
   <si>
     <t>Flex test 5</t>
@@ -19808,16 +19573,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>410920</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>572285</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>46935</xdr:rowOff>
+      <xdr:rowOff>73829</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>1130338</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>242832</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>78684</xdr:rowOff>
+      <xdr:rowOff>105578</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20194,9 +19959,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -20234,7 +19999,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -20340,7 +20105,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -20482,7 +20247,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -22239,7 +22004,7 @@
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="N22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
@@ -22943,7 +22708,7 @@
         <v>52</v>
       </c>
       <c r="O21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
@@ -23887,7 +23652,7 @@
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="O24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -26380,15 +26145,15 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D3">
         <f>(C3/C2)</f>
-        <v>0.86221294363256784</v>
+        <v>0.84133611691022969</v>
       </c>
       <c r="E3">
         <f>1-D3</f>
-        <v>0.13778705636743216</v>
+        <v>0.15866388308977031</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
@@ -27047,9 +26812,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
-      <c r="T15" s="2" t="s">
-        <v>81</v>
-      </c>
+      <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
@@ -27209,12 +26972,19 @@
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
+      <c r="M20" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
+      <c r="M21">
+        <f>AVERAGE(C8:T8)</f>
+        <v>623.16511111111129</v>
+      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
@@ -27280,8 +27050,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -27301,7 +27072,7 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -27346,14 +27117,14 @@
         <v>59</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O4" s="3"/>
       <c r="Q4" t="s">
         <v>26</v>
       </c>
       <c r="R4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
@@ -28161,24 +27932,24 @@
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="H17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="Q17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R17" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" t="s">
         <v>88</v>
       </c>
-      <c r="S17" t="s">
-        <v>89</v>
-      </c>
       <c r="T17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
@@ -28187,13 +27958,13 @@
         <v>72</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
@@ -28221,10 +27992,17 @@
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
+      <c r="M24" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
+      <c r="M25">
+        <f>AVERAGE(C8:U8)</f>
+        <v>623.42526315789462</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
@@ -32376,7 +32154,7 @@
     </row>
     <row r="18" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -33031,7 +32809,7 @@
     </row>
     <row r="19" spans="14:15" x14ac:dyDescent="0.3">
       <c r="O19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -33692,7 +33470,7 @@
         <v>52</v>
       </c>
       <c r="N21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD150D4-4730-494D-96AC-EE7AD0BAEDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A30B11-BBCA-4BDD-B5B7-9FDA39D18D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26685" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="13" activeTab="15" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="26670" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="12" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -25,10 +25,11 @@
     <sheet name="ExtTest10mm_10" sheetId="20" r:id="rId10"/>
     <sheet name="ExtTest10mm_11" sheetId="21" r:id="rId11"/>
     <sheet name="ExtTest10mm_12" sheetId="22" r:id="rId12"/>
-    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId13"/>
-    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId14"/>
-    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId15"/>
-    <sheet name="FlxTest10mm_4" sheetId="23" r:id="rId16"/>
+    <sheet name="ExtTest10mm_13" sheetId="24" r:id="rId13"/>
+    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId14"/>
+    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId15"/>
+    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId16"/>
+    <sheet name="FlxTest10mm_4" sheetId="23" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -242,6 +243,60 @@
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={A0F37F35-3C02-4428-95DF-F39F668FABAB}</author>
+    <author>tc={B330029E-0838-474A-A917-D75DCA8B89DE}</author>
+    <author>tc={54C76319-676A-40FF-BA34-557807290B63}</author>
+    <author>tc={3503805A-53F9-44E7-B5DE-1E572B8A5B05}</author>
+    <author>tc={1C8E06FF-9847-46B8-831A-746E2073BD30}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{A0F37F35-3C02-4428-95DF-F39F668FABAB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{B330029E-0838-474A-A917-D75DCA8B89DE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{54C76319-676A-40FF-BA34-557807290B63}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Max contracted length normalized by resting length</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{3503805A-53F9-44E7-B5DE-1E572B8A5B05}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kmax</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{1C8E06FF-9847-46B8-831A-746E2073BD30}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    So it can reach -114 degrees</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={B3DD3E36-DE23-4526-822F-7544076C12AF}</author>
     <author>tc={44F69930-AA26-4737-9556-6F232E8AC193}</author>
     <author>tc={6E9C7D1B-6D13-4A15-A63C-B49E3DDDDD72}</author>
@@ -294,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="83">
   <si>
     <t>Test #</t>
   </si>
@@ -538,6 +593,12 @@
   <si>
     <t>^Collected by Moe &amp; Ben</t>
   </si>
+  <si>
+    <t>*pretension 9.50N</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
 </sst>
 </file>
 
@@ -769,7 +830,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -803,7 +864,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -2916,36 +2976,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Flexor 10mm</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Knee Torque</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2977,25 +3007,18 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.4158344861650378E-2"/>
-          <c:y val="0.17072497123130037"/>
-          <c:w val="0.91627572927286405"/>
-          <c:h val="0.77864211737629463"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>result</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:noFill/>
               <a:round/>
             </a:ln>
@@ -3026,44 +3049,10 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="log"/>
             <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.60346456692913386"/>
-                  <c:y val="-0.28313193524076818"/>
-                </c:manualLayout>
-              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -3104,31 +3093,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="log"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="poly"/>
             <c:order val="3"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.27899278215223094"/>
-                  <c:y val="0.3201971535736251"/>
-                </c:manualLayout>
-              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -3161,200 +3130,140 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
+              <c:f>ExtTest10mm_12!$D$7:$S$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>-5.5</c:v>
+                  <c:v>28.29</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10.5</c:v>
+                  <c:v>18.149999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-25.5</c:v>
+                  <c:v>1.29</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.5</c:v>
+                  <c:v>-14.86</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-14.5</c:v>
+                  <c:v>-25.64</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-20</c:v>
+                  <c:v>-36.76</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-33</c:v>
+                  <c:v>-42.87</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-39.5</c:v>
+                  <c:v>-49.33</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-43</c:v>
+                  <c:v>-56.87</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-50</c:v>
+                  <c:v>-68.36</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-62.5</c:v>
+                  <c:v>-77.69</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-60</c:v>
+                  <c:v>-84.16</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-55</c:v>
+                  <c:v>-90.1</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-53.5</c:v>
+                  <c:v>-99.233999999999995</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-46</c:v>
+                  <c:v>-82</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-40</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-36.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-33.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-29.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-24.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-17.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-14.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-5.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>-0.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>11.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>19.5</c:v>
+                  <c:v>-65.48</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
+              <c:f>ExtTest10mm_12!$D$16:$AB$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-13.550199438030189</c:v>
+                  <c:v>0.38934455560856757</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.715746326203965</c:v>
+                  <c:v>1.8112948210918218</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-12.227450296743585</c:v>
+                  <c:v>4.4750917512529496</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-13.574295183417183</c:v>
+                  <c:v>5.4446222516176634</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-12.617833179689791</c:v>
+                  <c:v>5.9469453841091626</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11.427173303326315</c:v>
+                  <c:v>5.6590559428960212</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-7.8289359826583684</c:v>
+                  <c:v>6.0927652115792634</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-6.4962395866945686</c:v>
+                  <c:v>6.0976142089621366</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-4.9404873370427511</c:v>
+                  <c:v>6.3279415846485803</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.8261340010696823</c:v>
+                  <c:v>7.0095037627925798</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.2108000422274927</c:v>
+                  <c:v>7.5711771242618884</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.11021594724709009</c:v>
+                  <c:v>7.937808715762241</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.5137448723481624</c:v>
+                  <c:v>8.3306919291859725</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-3.1927408242720881</c:v>
+                  <c:v>9.369972199445602</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-4.8615958230354943</c:v>
+                  <c:v>7.0892341737595572</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-6.8694525901110115</c:v>
+                  <c:v>5.4793670426458965</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-8.5997889837959107</c:v>
+                  <c:v>4.957246848957868</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-10.35823139969961</c:v>
+                  <c:v>4.8935172428682936</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-11.863637901467659</c:v>
+                  <c:v>4.5504713609212226</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-13.477555041999489</c:v>
+                  <c:v>0.10037237370560359</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-13.77813076308844</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-14.884597105183458</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-14.534539473342328</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-14.338144060893327</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-14.021223986689929</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>-12.539046654783448</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>-11.167854768300959</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>-8.2836070695559112</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -3363,7 +3272,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
+              <c16:uniqueId val="{00000002-DE63-4F26-BE26-45C392EB0915}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3375,11 +3284,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1394438799"/>
-        <c:axId val="1190584639"/>
+        <c:axId val="1567646591"/>
+        <c:axId val="1566330175"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1394438799"/>
+        <c:axId val="1567646591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3436,12 +3345,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1190584639"/>
+        <c:crossAx val="1566330175"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1190584639"/>
+        <c:axId val="1566330175"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3498,7 +3407,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1394438799"/>
+        <c:crossAx val="1567646591"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3778,8 +3687,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.40762374401637524"/>
-                  <c:y val="4.5584595515824444E-2"/>
+                  <c:x val="-0.27899278215223094"/>
+                  <c:y val="0.3201971535736251"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -3814,162 +3723,186 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest10mm_2!$C$7:$AI$7</c:f>
+              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>-5.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>-10.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1</c:v>
+                  <c:v>-25.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-15</c:v>
+                  <c:v>-4.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-26.6</c:v>
+                  <c:v>-14.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-35</c:v>
+                  <c:v>-20</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-42.5</c:v>
+                  <c:v>-33</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-56</c:v>
+                  <c:v>-39.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-56</c:v>
+                  <c:v>-43</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-63</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-64</c:v>
+                  <c:v>-62.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>-60</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>-55</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>-48</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>-42</c:v>
+                  <c:v>-53.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-35</c:v>
+                  <c:v>-46</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-26</c:v>
+                  <c:v>-40</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-19</c:v>
+                  <c:v>-36.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-11</c:v>
+                  <c:v>-33.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.5</c:v>
+                  <c:v>-29.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>-24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-17.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-14.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>19.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest10mm_2!$C$15:$AI$15</c:f>
+              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>-12.024486481310953</c:v>
+                  <c:v>-13.550199438030189</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.010720430450908</c:v>
+                  <c:v>-12.715746326203965</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-12.467074331666348</c:v>
+                  <c:v>-12.227450296743585</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-11.429265093789359</c:v>
+                  <c:v>-13.574295183417183</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-9.361208446969103</c:v>
+                  <c:v>-12.617833179689791</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-7.6761795853386783</c:v>
+                  <c:v>-11.427173303326315</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-4.9579976724776733</c:v>
+                  <c:v>-7.8289359826583684</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.6722536503811283</c:v>
+                  <c:v>-6.4962395866945686</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.80746439223476663</c:v>
+                  <c:v>-4.9404873370427511</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-3.5743411708348779E-3</c:v>
+                  <c:v>-2.8261340010696823</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2.0198749999999999</c:v>
+                  <c:v>-1.2108000422274927</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-4.1705971185958441</c:v>
+                  <c:v>-0.11021594724709009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-6.4666790193515293</c:v>
+                  <c:v>-1.5137448723481624</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-8.1665094852463582</c:v>
+                  <c:v>-3.1927408242720881</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-10.603302506170124</c:v>
+                  <c:v>-4.8615958230354943</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-12.640024275140153</c:v>
+                  <c:v>-6.8694525901110115</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-13.930450567806828</c:v>
+                  <c:v>-8.5997889837959107</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-14.689482923460329</c:v>
+                  <c:v>-10.35823139969961</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-14.674822536018389</c:v>
+                  <c:v>-11.863637901467659</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-13.151302910231001</c:v>
+                  <c:v>-13.477555041999489</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>-13.77813076308844</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>-14.884597105183458</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>-14.534539473342328</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>-14.338144060893327</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>-14.021223986689929</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>-12.539046654783448</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>-11.167854768300959</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0</c:v>
+                  <c:v>-8.2836070695559112</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -3992,7 +3925,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-9D05-4463-B8B4-EFE1AE46B75E}"/>
+              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4198,6 +4131,635 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Flexor 10mm</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Knee Torque</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.4158344861650378E-2"/>
+          <c:y val="0.17072497123130037"/>
+          <c:w val="0.91627572927286405"/>
+          <c:h val="0.77864211737629463"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="power"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.60346456692913386"/>
+                  <c:y val="-0.28313193524076818"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.40762374401637524"/>
+                  <c:y val="4.5584595515824444E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_2!$C$7:$AI$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-26.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-42.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-56</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-56</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-64</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-55</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-48</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-42</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-35</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-26</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-19</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_2!$C$15:$AI$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>-12.024486481310953</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-12.010720430450908</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-12.467074331666348</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-11.429265093789359</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-9.361208446969103</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-7.6761795853386783</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.9579976724776733</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.6722536503811283</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.80746439223476663</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-3.5743411708348779E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-2.0198749999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-4.1705971185958441</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-6.4666790193515293</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-8.1665094852463582</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-10.603302506170124</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-12.640024275140153</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-13.930450567806828</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-14.689482923460329</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-14.674822536018389</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-13.151302910231001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-9D05-4463-B8B4-EFE1AE46B75E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1394438799"/>
+        <c:axId val="1190584639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1394438799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1190584639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1190584639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1394438799"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4631,7 +5193,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4809,6 +5371,12 @@
                 <c:pt idx="7">
                   <c:v>-24.202999999999999</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>-9.125</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-21.331</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4843,10 +5411,10 @@
                   <c:v>-16.386164614410578</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>-16.727950101680829</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>-14.931186025358189</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -9450,6 +10018,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors17.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -13898,6 +14506,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -18200,6 +19324,49 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>329710</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>108439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1340825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>41276</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8654B586-951D-46F4-A8A5-47D952B66B32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>740833</xdr:colOff>
       <xdr:row>20</xdr:row>
@@ -18239,7 +19406,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -18282,7 +19449,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -18323,7 +19490,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -19078,6 +20245,26 @@
 
 <file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{A0F37F35-3C02-4428-95DF-F39F668FABAB}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{B330029E-0838-474A-A917-D75DCA8B89DE}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{54C76319-676A-40FF-BA34-557807290B63}">
+    <text>Max contracted length normalized by resting length</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{3503805A-53F9-44E7-B5DE-1E572B8A5B05}">
+    <text>Kmax</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{1C8E06FF-9847-46B8-831A-746E2073BD30}">
+    <text>So it can reach -114 degrees</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{B3DD3E36-DE23-4526-822F-7544076C12AF}">
     <text>Recheck after test</text>
   </threadedComment>
@@ -21908,64 +23095,64 @@
         <v>3</v>
       </c>
       <c r="C10" s="30"/>
-      <c r="D10" s="33">
+      <c r="D10">
         <v>367</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10">
         <v>367</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10">
         <v>382</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10">
         <v>398</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10">
         <v>397</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10">
         <v>403</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10">
         <v>407</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10">
         <v>411</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10">
         <v>416</v>
       </c>
-      <c r="M10" s="33">
+      <c r="M10">
         <v>422</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10">
         <v>428</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10">
         <v>428</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10">
         <v>434</v>
       </c>
-      <c r="Q10" s="33">
+      <c r="Q10">
         <v>434</v>
       </c>
-      <c r="R10" s="33">
+      <c r="R10">
         <v>425</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10">
         <v>420</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10">
         <v>398</v>
       </c>
-      <c r="U10" s="33">
+      <c r="U10">
         <v>396</v>
       </c>
-      <c r="V10" s="33">
+      <c r="V10">
         <v>386</v>
       </c>
-      <c r="W10" s="33">
+      <c r="W10">
         <v>366</v>
       </c>
     </row>
@@ -22438,2399 +23625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
-  <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>485</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <f>C2-C2*0.17</f>
-        <v>402.55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>P5+1</f>
-        <v>15</v>
-      </c>
-      <c r="R5" s="10">
-        <f>Q5+1</f>
-        <v>16</v>
-      </c>
-      <c r="S5" s="10">
-        <f t="shared" ref="S5:AB5" si="0">R5+1</f>
-        <v>17</v>
-      </c>
-      <c r="T5" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="U5" s="10">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V5" s="10">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W5" s="10">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X5" s="10">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Z5" s="10">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA5" s="10">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="10">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AC5" s="10">
-        <f t="shared" ref="AC5:AI5" si="1">AB5+1</f>
-        <v>27</v>
-      </c>
-      <c r="AD5" s="10">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="AE5" s="10">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="AF5" s="10">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AG5" s="10">
-        <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="AH5" s="10">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="AI5" s="10">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>51.203000000000003</v>
-      </c>
-      <c r="D6">
-        <v>48.398000000000003</v>
-      </c>
-      <c r="E6">
-        <v>46.283999999999999</v>
-      </c>
-      <c r="F6">
-        <v>49.966000000000001</v>
-      </c>
-      <c r="G6">
-        <v>46.258000000000003</v>
-      </c>
-      <c r="H6">
-        <v>42.865000000000002</v>
-      </c>
-      <c r="I6">
-        <v>28.888999999999999</v>
-      </c>
-      <c r="J6">
-        <v>24.26</v>
-      </c>
-      <c r="K6">
-        <v>18.155999999999999</v>
-      </c>
-      <c r="L6">
-        <v>10.234</v>
-      </c>
-      <c r="M6">
-        <v>4.266</v>
-      </c>
-      <c r="N6">
-        <v>0.39300000000000002</v>
-      </c>
-      <c r="O6">
-        <v>5.4537000000000004</v>
-      </c>
-      <c r="P6">
-        <v>11.362</v>
-      </c>
-      <c r="Q6">
-        <v>17.478000000000002</v>
-      </c>
-      <c r="R6">
-        <v>24.577000000000002</v>
-      </c>
-      <c r="S6">
-        <v>31.812999999999999</v>
-      </c>
-      <c r="T6">
-        <v>37.369</v>
-      </c>
-      <c r="U6">
-        <v>42.365000000000002</v>
-      </c>
-      <c r="V6">
-        <v>47.408000000000001</v>
-      </c>
-      <c r="W6">
-        <v>50.768000000000001</v>
-      </c>
-      <c r="X6">
-        <v>53.197000000000003</v>
-      </c>
-      <c r="Y6">
-        <v>52.39</v>
-      </c>
-      <c r="Z6">
-        <v>52.238999999999997</v>
-      </c>
-      <c r="AA6">
-        <v>50.945</v>
-      </c>
-      <c r="AB6">
-        <v>46.247</v>
-      </c>
-      <c r="AC6">
-        <v>39.781999999999996</v>
-      </c>
-      <c r="AD6">
-        <v>30.405999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>-5.5</v>
-      </c>
-      <c r="D7">
-        <v>-10.5</v>
-      </c>
-      <c r="E7">
-        <v>-25.5</v>
-      </c>
-      <c r="F7">
-        <v>-4.5</v>
-      </c>
-      <c r="G7">
-        <v>-14.5</v>
-      </c>
-      <c r="H7">
-        <v>-20</v>
-      </c>
-      <c r="I7">
-        <v>-33</v>
-      </c>
-      <c r="J7">
-        <v>-39.5</v>
-      </c>
-      <c r="K7">
-        <v>-43</v>
-      </c>
-      <c r="L7">
-        <v>-50</v>
-      </c>
-      <c r="M7">
-        <v>-62.5</v>
-      </c>
-      <c r="N7">
-        <v>-60</v>
-      </c>
-      <c r="O7">
-        <v>-55</v>
-      </c>
-      <c r="P7">
-        <v>-53.5</v>
-      </c>
-      <c r="Q7">
-        <v>-46</v>
-      </c>
-      <c r="R7">
-        <v>-40</v>
-      </c>
-      <c r="S7">
-        <v>-36.5</v>
-      </c>
-      <c r="T7">
-        <v>-33.5</v>
-      </c>
-      <c r="U7">
-        <v>-29.5</v>
-      </c>
-      <c r="V7">
-        <v>-24.5</v>
-      </c>
-      <c r="W7">
-        <v>-17.5</v>
-      </c>
-      <c r="X7">
-        <v>-14.5</v>
-      </c>
-      <c r="Y7">
-        <v>-5.5</v>
-      </c>
-      <c r="Z7">
-        <v>-3</v>
-      </c>
-      <c r="AA7">
-        <v>-0.5</v>
-      </c>
-      <c r="AB7">
-        <v>3.5</v>
-      </c>
-      <c r="AC7">
-        <v>11.5</v>
-      </c>
-      <c r="AD7">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>87</v>
-      </c>
-      <c r="D8" s="1">
-        <v>82.5</v>
-      </c>
-      <c r="E8" s="1">
-        <v>94.5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>115.1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>114.6</v>
-      </c>
-      <c r="H8" s="1">
-        <v>117.3</v>
-      </c>
-      <c r="I8" s="1">
-        <v>115.4</v>
-      </c>
-      <c r="J8" s="1">
-        <v>116.8</v>
-      </c>
-      <c r="K8" s="1">
-        <v>114.9</v>
-      </c>
-      <c r="L8" s="1">
-        <v>113</v>
-      </c>
-      <c r="M8" s="1">
-        <v>108.9</v>
-      </c>
-      <c r="N8" s="1">
-        <v>110.8</v>
-      </c>
-      <c r="O8" s="1">
-        <v>112.3</v>
-      </c>
-      <c r="P8" s="1">
-        <v>110.5</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>112</v>
-      </c>
-      <c r="R8" s="1">
-        <v>111.3</v>
-      </c>
-      <c r="S8" s="1">
-        <v>115.7</v>
-      </c>
-      <c r="T8" s="1">
-        <v>116.6</v>
-      </c>
-      <c r="U8" s="1">
-        <v>115.4</v>
-      </c>
-      <c r="V8" s="1">
-        <v>113.5</v>
-      </c>
-      <c r="W8" s="1">
-        <v>118.9</v>
-      </c>
-      <c r="X8" s="1">
-        <v>115.5</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>116.5</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>117.7</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>117.4</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>119</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>115.1</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>118.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>461.5</v>
-      </c>
-      <c r="D10">
-        <v>456</v>
-      </c>
-      <c r="E10">
-        <v>450.5</v>
-      </c>
-      <c r="F10">
-        <v>460.5</v>
-      </c>
-      <c r="G10">
-        <v>452</v>
-      </c>
-      <c r="H10">
-        <v>449</v>
-      </c>
-      <c r="I10">
-        <v>432</v>
-      </c>
-      <c r="J10">
-        <v>428</v>
-      </c>
-      <c r="K10">
-        <v>423</v>
-      </c>
-      <c r="L10">
-        <v>415</v>
-      </c>
-      <c r="M10">
-        <v>409.5</v>
-      </c>
-      <c r="N10">
-        <v>406</v>
-      </c>
-      <c r="O10">
-        <v>410</v>
-      </c>
-      <c r="P10">
-        <v>414.5</v>
-      </c>
-      <c r="Q10">
-        <v>420.5</v>
-      </c>
-      <c r="R10">
-        <v>426</v>
-      </c>
-      <c r="S10">
-        <v>430</v>
-      </c>
-      <c r="T10">
-        <v>433.5</v>
-      </c>
-      <c r="U10" s="2">
-        <v>441</v>
-      </c>
-      <c r="V10" s="2">
-        <v>445</v>
-      </c>
-      <c r="W10" s="2">
-        <v>451</v>
-      </c>
-      <c r="X10" s="2">
-        <v>454</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>455.5</v>
-      </c>
-      <c r="Z10" s="2">
-        <v>458.5</v>
-      </c>
-      <c r="AA10" s="2">
-        <v>462</v>
-      </c>
-      <c r="AB10" s="2">
-        <v>461.5</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>465</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>467</v>
-      </c>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>265</v>
-      </c>
-      <c r="D12">
-        <v>265</v>
-      </c>
-      <c r="E12">
-        <v>265</v>
-      </c>
-      <c r="F12">
-        <v>300</v>
-      </c>
-      <c r="G12">
-        <v>300</v>
-      </c>
-      <c r="H12">
-        <v>300</v>
-      </c>
-      <c r="I12">
-        <v>300</v>
-      </c>
-      <c r="J12">
-        <v>300</v>
-      </c>
-      <c r="K12">
-        <v>300</v>
-      </c>
-      <c r="L12">
-        <v>300</v>
-      </c>
-      <c r="M12">
-        <v>300</v>
-      </c>
-      <c r="N12">
-        <v>300</v>
-      </c>
-      <c r="O12">
-        <v>300</v>
-      </c>
-      <c r="P12">
-        <v>300</v>
-      </c>
-      <c r="Q12">
-        <v>300</v>
-      </c>
-      <c r="R12">
-        <v>300</v>
-      </c>
-      <c r="S12">
-        <v>300</v>
-      </c>
-      <c r="T12">
-        <v>310</v>
-      </c>
-      <c r="U12">
-        <v>310</v>
-      </c>
-      <c r="V12">
-        <v>310</v>
-      </c>
-      <c r="W12">
-        <v>310</v>
-      </c>
-      <c r="X12">
-        <v>310</v>
-      </c>
-      <c r="Y12">
-        <v>310</v>
-      </c>
-      <c r="Z12">
-        <v>310</v>
-      </c>
-      <c r="AA12">
-        <v>310</v>
-      </c>
-      <c r="AB12">
-        <v>310</v>
-      </c>
-      <c r="AC12">
-        <v>310</v>
-      </c>
-      <c r="AD12">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>62</v>
-      </c>
-      <c r="D13">
-        <v>74</v>
-      </c>
-      <c r="E13">
-        <v>76</v>
-      </c>
-      <c r="F13">
-        <v>64</v>
-      </c>
-      <c r="G13">
-        <v>72</v>
-      </c>
-      <c r="H13">
-        <v>76</v>
-      </c>
-      <c r="I13">
-        <v>79.5</v>
-      </c>
-      <c r="J13">
-        <v>81.5</v>
-      </c>
-      <c r="K13">
-        <v>77</v>
-      </c>
-      <c r="L13">
-        <v>81</v>
-      </c>
-      <c r="M13">
-        <v>74</v>
-      </c>
-      <c r="N13">
-        <v>68</v>
-      </c>
-      <c r="O13">
-        <v>74</v>
-      </c>
-      <c r="P13">
-        <v>77</v>
-      </c>
-      <c r="Q13">
-        <v>75</v>
-      </c>
-      <c r="R13">
-        <v>79</v>
-      </c>
-      <c r="S13">
-        <v>80</v>
-      </c>
-      <c r="T13">
-        <v>78</v>
-      </c>
-      <c r="U13">
-        <v>79</v>
-      </c>
-      <c r="V13">
-        <v>77</v>
-      </c>
-      <c r="W13">
-        <v>75.5</v>
-      </c>
-      <c r="X13">
-        <v>72</v>
-      </c>
-      <c r="Y13">
-        <v>61.5</v>
-      </c>
-      <c r="Z13">
-        <v>62.5</v>
-      </c>
-      <c r="AA13">
-        <v>54.5</v>
-      </c>
-      <c r="AB13">
-        <v>48</v>
-      </c>
-      <c r="AC13">
-        <v>38.5</v>
-      </c>
-      <c r="AD13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <f t="shared" ref="C15:AI15" si="2">C6*-SIN(RADIANS(C8))*C12/1000</f>
-        <v>-13.550199438030189</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="2"/>
-        <v>-12.715746326203965</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="2"/>
-        <v>-12.227450296743585</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="2"/>
-        <v>-13.574295183417183</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="2"/>
-        <v>-12.617833179689791</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="2"/>
-        <v>-11.427173303326315</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="2"/>
-        <v>-7.8289359826583684</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="2"/>
-        <v>-6.4962395866945686</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="2"/>
-        <v>-4.9404873370427511</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="2"/>
-        <v>-2.8261340010696823</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="2"/>
-        <v>-1.2108000422274927</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="2"/>
-        <v>-0.11021594724709009</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="2"/>
-        <v>-1.5137448723481624</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="2"/>
-        <v>-3.1927408242720881</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="2"/>
-        <v>-4.8615958230354943</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="2"/>
-        <v>-6.8694525901110115</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="2"/>
-        <v>-8.5997889837959107</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="2"/>
-        <v>-10.35823139969961</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="2"/>
-        <v>-11.863637901467659</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="2"/>
-        <v>-13.477555041999489</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="2"/>
-        <v>-13.77813076308844</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="2"/>
-        <v>-14.884597105183458</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="2"/>
-        <v>-14.534539473342328</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="2"/>
-        <v>-14.338144060893327</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="2"/>
-        <v>-14.021223986689929</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="2"/>
-        <v>-12.539046654783448</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="2"/>
-        <v>-11.167854768300959</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="2"/>
-        <v>-8.2836070695559112</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
-  <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>485</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <f>C2-C2*0.17</f>
-        <v>402.55</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>398</v>
-      </c>
-      <c r="L4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>P5+1</f>
-        <v>15</v>
-      </c>
-      <c r="R5" s="10">
-        <f>Q5+1</f>
-        <v>16</v>
-      </c>
-      <c r="S5" s="10">
-        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
-        <v>17</v>
-      </c>
-      <c r="T5" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="U5" s="10">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V5" s="10">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W5" s="10">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X5" s="10">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Z5" s="10">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA5" s="10">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="10">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AC5" s="10">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="AD5" s="10">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="AE5" s="10">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="AF5" s="10">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AG5" s="10">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="AH5" s="10">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="AI5" s="10">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>43.774000000000001</v>
-      </c>
-      <c r="D6">
-        <v>43.682000000000002</v>
-      </c>
-      <c r="E6">
-        <v>45.475000000000001</v>
-      </c>
-      <c r="F6">
-        <v>41.618000000000002</v>
-      </c>
-      <c r="G6">
-        <v>34.204000000000001</v>
-      </c>
-      <c r="H6">
-        <v>27.984999999999999</v>
-      </c>
-      <c r="I6">
-        <v>18.039000000000001</v>
-      </c>
-      <c r="J6">
-        <v>6.0835999999999997</v>
-      </c>
-      <c r="K6">
-        <v>2.9384000000000001</v>
-      </c>
-      <c r="L6">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="M6">
-        <v>7.3449999999999998</v>
-      </c>
-      <c r="N6">
-        <v>15.176</v>
-      </c>
-      <c r="O6">
-        <v>23.530999999999999</v>
-      </c>
-      <c r="P6">
-        <v>29.727</v>
-      </c>
-      <c r="Q6">
-        <v>38.637999999999998</v>
-      </c>
-      <c r="R6">
-        <v>46.064999999999998</v>
-      </c>
-      <c r="S6">
-        <v>50.881999999999998</v>
-      </c>
-      <c r="T6">
-        <v>53.805999999999997</v>
-      </c>
-      <c r="U6">
-        <v>53.527999999999999</v>
-      </c>
-      <c r="V6">
-        <v>48.012999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>5.5</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
-      </c>
-      <c r="F7">
-        <v>-15</v>
-      </c>
-      <c r="G7">
-        <v>-26.6</v>
-      </c>
-      <c r="H7">
-        <v>-35</v>
-      </c>
-      <c r="I7">
-        <v>-42.5</v>
-      </c>
-      <c r="J7">
-        <v>-56</v>
-      </c>
-      <c r="K7">
-        <v>-56</v>
-      </c>
-      <c r="L7">
-        <v>-63</v>
-      </c>
-      <c r="M7">
-        <v>-64</v>
-      </c>
-      <c r="N7">
-        <v>-55</v>
-      </c>
-      <c r="O7">
-        <v>-48</v>
-      </c>
-      <c r="P7">
-        <v>-42</v>
-      </c>
-      <c r="Q7">
-        <v>-35</v>
-      </c>
-      <c r="R7">
-        <v>-26</v>
-      </c>
-      <c r="S7">
-        <v>-19</v>
-      </c>
-      <c r="T7">
-        <v>-11</v>
-      </c>
-      <c r="U7">
-        <v>0.5</v>
-      </c>
-      <c r="V7">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>92.7</v>
-      </c>
-      <c r="D8" s="1">
-        <v>91</v>
-      </c>
-      <c r="E8" s="1">
-        <v>94.5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>93</v>
-      </c>
-      <c r="G8" s="1">
-        <v>95.6</v>
-      </c>
-      <c r="H8" s="1">
-        <v>94.1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>91.9</v>
-      </c>
-      <c r="J8" s="1">
-        <v>91.7</v>
-      </c>
-      <c r="K8" s="1">
-        <v>92.2</v>
-      </c>
-      <c r="L8" s="1">
-        <v>91.1</v>
-      </c>
-      <c r="M8" s="1">
-        <v>90</v>
-      </c>
-      <c r="N8" s="1">
-        <v>92.1</v>
-      </c>
-      <c r="O8" s="1">
-        <v>92.1</v>
-      </c>
-      <c r="P8" s="1">
-        <v>92.6</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>93.7</v>
-      </c>
-      <c r="R8" s="1">
-        <v>93.8</v>
-      </c>
-      <c r="S8" s="1">
-        <v>95.4</v>
-      </c>
-      <c r="T8" s="1">
-        <v>96.9</v>
-      </c>
-      <c r="U8" s="1">
-        <v>94.5</v>
-      </c>
-      <c r="V8" s="1">
-        <v>95.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>467</v>
-      </c>
-      <c r="D10">
-        <v>466</v>
-      </c>
-      <c r="E10">
-        <v>463</v>
-      </c>
-      <c r="F10">
-        <v>450</v>
-      </c>
-      <c r="G10">
-        <v>443</v>
-      </c>
-      <c r="H10">
-        <v>431</v>
-      </c>
-      <c r="I10">
-        <v>423</v>
-      </c>
-      <c r="J10">
-        <v>411</v>
-      </c>
-      <c r="K10">
-        <v>408</v>
-      </c>
-      <c r="L10">
-        <v>404</v>
-      </c>
-      <c r="M10">
-        <v>407</v>
-      </c>
-      <c r="N10">
-        <v>413</v>
-      </c>
-      <c r="O10">
-        <v>420</v>
-      </c>
-      <c r="P10">
-        <v>422</v>
-      </c>
-      <c r="Q10">
-        <v>433</v>
-      </c>
-      <c r="R10">
-        <v>442</v>
-      </c>
-      <c r="S10">
-        <v>448</v>
-      </c>
-      <c r="T10">
-        <v>455</v>
-      </c>
-      <c r="U10" s="2">
-        <v>460</v>
-      </c>
-      <c r="V10" s="2">
-        <v>466</v>
-      </c>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>275</v>
-      </c>
-      <c r="D12">
-        <v>275</v>
-      </c>
-      <c r="E12">
-        <v>275</v>
-      </c>
-      <c r="F12">
-        <v>275</v>
-      </c>
-      <c r="G12">
-        <v>275</v>
-      </c>
-      <c r="H12">
-        <v>275</v>
-      </c>
-      <c r="I12">
-        <v>275</v>
-      </c>
-      <c r="J12">
-        <v>275</v>
-      </c>
-      <c r="K12">
-        <v>275</v>
-      </c>
-      <c r="L12">
-        <v>275</v>
-      </c>
-      <c r="M12">
-        <v>275</v>
-      </c>
-      <c r="N12">
-        <v>275</v>
-      </c>
-      <c r="O12">
-        <v>275</v>
-      </c>
-      <c r="P12">
-        <v>275</v>
-      </c>
-      <c r="Q12">
-        <v>275</v>
-      </c>
-      <c r="R12">
-        <v>275</v>
-      </c>
-      <c r="S12">
-        <v>275</v>
-      </c>
-      <c r="T12">
-        <v>275</v>
-      </c>
-      <c r="U12">
-        <v>275</v>
-      </c>
-      <c r="V12">
-        <v>275</v>
-      </c>
-      <c r="W12">
-        <v>275</v>
-      </c>
-      <c r="X12">
-        <v>275</v>
-      </c>
-      <c r="Y12">
-        <v>275</v>
-      </c>
-      <c r="Z12">
-        <v>275</v>
-      </c>
-      <c r="AA12">
-        <v>275</v>
-      </c>
-      <c r="AB12">
-        <v>275</v>
-      </c>
-      <c r="AC12">
-        <v>275</v>
-      </c>
-      <c r="AD12">
-        <v>275</v>
-      </c>
-      <c r="AE12">
-        <v>275</v>
-      </c>
-      <c r="AF12">
-        <v>275</v>
-      </c>
-      <c r="AG12">
-        <v>275</v>
-      </c>
-      <c r="AH12">
-        <v>275</v>
-      </c>
-      <c r="AI12">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>45</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>55</v>
-      </c>
-      <c r="F13">
-        <v>65</v>
-      </c>
-      <c r="G13">
-        <v>70</v>
-      </c>
-      <c r="H13">
-        <v>74</v>
-      </c>
-      <c r="I13">
-        <v>73</v>
-      </c>
-      <c r="J13">
-        <v>72</v>
-      </c>
-      <c r="K13">
-        <v>65</v>
-      </c>
-      <c r="L13">
-        <v>63</v>
-      </c>
-      <c r="M13">
-        <v>66</v>
-      </c>
-      <c r="N13">
-        <v>71</v>
-      </c>
-      <c r="O13">
-        <v>75</v>
-      </c>
-      <c r="P13">
-        <v>75</v>
-      </c>
-      <c r="Q13">
-        <v>76</v>
-      </c>
-      <c r="R13">
-        <v>75</v>
-      </c>
-      <c r="S13">
-        <v>69</v>
-      </c>
-      <c r="T13">
-        <v>65</v>
-      </c>
-      <c r="U13">
-        <v>56</v>
-      </c>
-      <c r="V13">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
-        <v>-12.024486481310953</v>
-      </c>
-      <c r="D15">
-        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
-        <v>-12.010720430450908</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="1"/>
-        <v>-12.467074331666348</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>-11.429265093789359</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>-9.361208446969103</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>-7.6761795853386783</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>-4.9579976724776733</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>-1.6722536503811283</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>-0.80746439223476663</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>-3.5743411708348779E-3</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="1"/>
-        <v>-2.0198749999999999</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="1"/>
-        <v>-4.1705971185958441</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="1"/>
-        <v>-6.4666790193515293</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="1"/>
-        <v>-8.1665094852463582</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="1"/>
-        <v>-10.603302506170124</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="1"/>
-        <v>-12.640024275140153</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="1"/>
-        <v>-13.930450567806828</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>-14.689482923460329</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="1"/>
-        <v>-14.674822536018389</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="1"/>
-        <v>-13.151302910231001</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="L16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
-      <c r="R29">
-        <f>485*1.03</f>
-        <v>499.55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
-  <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>457</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <f>C2-C2*0.17</f>
-        <v>379.31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>P5+1</f>
-        <v>15</v>
-      </c>
-      <c r="R5" s="10">
-        <f>Q5+1</f>
-        <v>16</v>
-      </c>
-      <c r="S5" s="10">
-        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
-        <v>17</v>
-      </c>
-      <c r="T5" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="U5" s="10">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V5" s="10">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W5" s="10">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X5" s="10">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Z5" s="10">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA5" s="10">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="10">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AC5" s="10">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="AD5" s="10">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="AE5" s="10">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="AF5" s="10">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AG5" s="10">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="AH5" s="10">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="AI5" s="10">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>67.698999999999998</v>
-      </c>
-      <c r="D6">
-        <v>53.807000000000002</v>
-      </c>
-      <c r="E6">
-        <v>40.158999999999999</v>
-      </c>
-      <c r="F6">
-        <v>29.155000000000001</v>
-      </c>
-      <c r="G6">
-        <v>19.347000000000001</v>
-      </c>
-      <c r="H6">
-        <v>18.911000000000001</v>
-      </c>
-      <c r="I6">
-        <v>10.577</v>
-      </c>
-      <c r="J6">
-        <v>6.6810999999999998</v>
-      </c>
-      <c r="K6">
-        <v>3.8237000000000001</v>
-      </c>
-      <c r="L6">
-        <v>2.0994000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>-41</v>
-      </c>
-      <c r="D7">
-        <v>-45</v>
-      </c>
-      <c r="E7">
-        <v>-57</v>
-      </c>
-      <c r="F7">
-        <v>-63</v>
-      </c>
-      <c r="G7">
-        <v>-77</v>
-      </c>
-      <c r="H7">
-        <v>-75</v>
-      </c>
-      <c r="I7">
-        <v>-80</v>
-      </c>
-      <c r="J7">
-        <v>-90</v>
-      </c>
-      <c r="K7">
-        <v>-95</v>
-      </c>
-      <c r="L7">
-        <v>-105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>71.2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>75.3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>72.7</v>
-      </c>
-      <c r="F8" s="1">
-        <v>74.2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>81.599999999999994</v>
-      </c>
-      <c r="H8" s="1">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I8" s="1">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="J8" s="1">
-        <v>79.599999999999994</v>
-      </c>
-      <c r="K8" s="1">
-        <v>78</v>
-      </c>
-      <c r="L8" s="1">
-        <v>76.599999999999994</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>428</v>
-      </c>
-      <c r="D10">
-        <v>418</v>
-      </c>
-      <c r="E10">
-        <v>409.5</v>
-      </c>
-      <c r="F10">
-        <v>405.5</v>
-      </c>
-      <c r="G10">
-        <v>395</v>
-      </c>
-      <c r="H10">
-        <v>396</v>
-      </c>
-      <c r="I10">
-        <v>390</v>
-      </c>
-      <c r="J10">
-        <v>384</v>
-      </c>
-      <c r="K10">
-        <v>381</v>
-      </c>
-      <c r="L10">
-        <v>376</v>
-      </c>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
-      <c r="R10"/>
-      <c r="S10"/>
-      <c r="T10"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>275</v>
-      </c>
-      <c r="D12">
-        <v>275</v>
-      </c>
-      <c r="E12">
-        <v>275</v>
-      </c>
-      <c r="F12">
-        <v>275</v>
-      </c>
-      <c r="G12">
-        <v>275</v>
-      </c>
-      <c r="H12">
-        <v>275</v>
-      </c>
-      <c r="I12">
-        <v>275</v>
-      </c>
-      <c r="J12">
-        <v>275</v>
-      </c>
-      <c r="K12">
-        <v>275</v>
-      </c>
-      <c r="L12">
-        <v>275</v>
-      </c>
-      <c r="M12">
-        <v>275</v>
-      </c>
-      <c r="N12">
-        <v>275</v>
-      </c>
-      <c r="O12">
-        <v>275</v>
-      </c>
-      <c r="P12">
-        <v>275</v>
-      </c>
-      <c r="Q12">
-        <v>275</v>
-      </c>
-      <c r="R12">
-        <v>275</v>
-      </c>
-      <c r="S12">
-        <v>275</v>
-      </c>
-      <c r="T12">
-        <v>275</v>
-      </c>
-      <c r="U12">
-        <v>275</v>
-      </c>
-      <c r="V12">
-        <v>275</v>
-      </c>
-      <c r="W12">
-        <v>275</v>
-      </c>
-      <c r="X12">
-        <v>275</v>
-      </c>
-      <c r="Y12">
-        <v>275</v>
-      </c>
-      <c r="Z12">
-        <v>275</v>
-      </c>
-      <c r="AA12">
-        <v>275</v>
-      </c>
-      <c r="AB12">
-        <v>275</v>
-      </c>
-      <c r="AC12">
-        <v>275</v>
-      </c>
-      <c r="AD12">
-        <v>275</v>
-      </c>
-      <c r="AE12">
-        <v>275</v>
-      </c>
-      <c r="AF12">
-        <v>275</v>
-      </c>
-      <c r="AG12">
-        <v>275</v>
-      </c>
-      <c r="AH12">
-        <v>275</v>
-      </c>
-      <c r="AI12">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>80</v>
-      </c>
-      <c r="D13">
-        <v>81</v>
-      </c>
-      <c r="E13">
-        <v>78</v>
-      </c>
-      <c r="F13">
-        <v>76</v>
-      </c>
-      <c r="G13">
-        <v>62</v>
-      </c>
-      <c r="H13">
-        <v>62.5</v>
-      </c>
-      <c r="I13">
-        <v>60</v>
-      </c>
-      <c r="J13">
-        <v>48</v>
-      </c>
-      <c r="K13">
-        <v>34</v>
-      </c>
-      <c r="L13">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
-        <v>-17.623982271657447</v>
-      </c>
-      <c r="D15">
-        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
-        <v>-14.312588392743191</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="1"/>
-        <v>-10.544115710489031</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>-7.714703040370237</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>-5.2633492521046072</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>-5.0482353303594207</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>-2.8329795466253955</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>-1.807118322254111</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>-1.0285393197546095</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>-0.56161756164602195</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="10:18" x14ac:dyDescent="0.35">
-      <c r="J18">
-        <f>1-348/457</f>
-        <v>0.23851203501094087</v>
-      </c>
-    </row>
-    <row r="29" spans="10:18" x14ac:dyDescent="0.35">
-      <c r="R29">
-        <f>485*1.03</f>
-        <v>499.55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B26E4-CFF3-41E2-8721-B0918FFC9B0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4765B8-342C-4A6E-9692-B7C6F1796DEE}">
   <dimension ref="A1:AK36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -24843,7 +23638,7 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -24853,10 +23648,10 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2">
-        <v>479</v>
+        <v>436</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.35">
@@ -24865,15 +23660,15 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3">
-        <v>413</v>
+        <v>371</v>
       </c>
       <c r="D3">
         <f>(C3/C2)</f>
-        <v>0.86221294363256784</v>
+        <v>0.8509174311926605</v>
       </c>
       <c r="E3">
         <f>1-D3</f>
-        <v>0.13778705636743216</v>
+        <v>0.1490825688073395</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.35">
@@ -25010,90 +23805,21 @@
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="16">
-        <v>7.6539999999999999</v>
-      </c>
-      <c r="D6">
-        <v>16.346</v>
-      </c>
-      <c r="E6">
-        <v>28.263000000000002</v>
-      </c>
-      <c r="F6">
-        <v>41.6</v>
-      </c>
-      <c r="G6">
-        <v>53.704999999999998</v>
-      </c>
-      <c r="H6">
-        <v>59.472000000000001</v>
-      </c>
-      <c r="I6">
-        <v>63.2</v>
-      </c>
-      <c r="J6">
-        <v>65.655000000000001</v>
-      </c>
+      <c r="C6" s="30"/>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="16">
-        <v>-68.718999999999994</v>
-      </c>
-      <c r="D7">
-        <v>-61.898000000000003</v>
-      </c>
-      <c r="E7">
-        <v>-54.359000000000002</v>
-      </c>
-      <c r="F7">
-        <v>-46.460999999999999</v>
-      </c>
-      <c r="G7">
-        <v>-38.204000000000001</v>
-      </c>
-      <c r="H7">
-        <v>-32.100999999999999</v>
-      </c>
-      <c r="I7">
-        <v>-27.8</v>
-      </c>
-      <c r="J7">
-        <v>-24.202999999999999</v>
-      </c>
+      <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="16">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="D8">
-        <v>623.60699999999997</v>
-      </c>
-      <c r="E8">
-        <v>622.85</v>
-      </c>
-      <c r="F8">
-        <v>622.85</v>
-      </c>
-      <c r="G8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="H8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="I8">
-        <v>623.60699999999997</v>
-      </c>
-      <c r="J8">
-        <v>622.85</v>
-      </c>
+      <c r="C8" s="30"/>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
@@ -25102,30 +23828,14 @@
       <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="15">
-        <v>82</v>
-      </c>
-      <c r="D9" s="1">
-        <v>86</v>
-      </c>
-      <c r="E9" s="1">
-        <v>84.5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>98.5</v>
-      </c>
-      <c r="G9" s="1">
-        <v>87</v>
-      </c>
-      <c r="H9" s="1">
-        <v>86</v>
-      </c>
-      <c r="I9" s="1">
-        <v>85</v>
-      </c>
-      <c r="J9" s="1">
-        <v>83</v>
-      </c>
+      <c r="C9" s="31"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -25159,43 +23869,3176 @@
       <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="C10" s="30"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="31"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="30"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="30">
+        <v>249.71</v>
+      </c>
+      <c r="D13">
+        <v>249.71</v>
+      </c>
+      <c r="E13">
+        <v>249.71</v>
+      </c>
+      <c r="F13">
+        <v>249.71</v>
+      </c>
+      <c r="G13">
+        <v>249.71</v>
+      </c>
+      <c r="H13">
+        <v>249.71</v>
+      </c>
+      <c r="I13">
+        <v>249.71</v>
+      </c>
+      <c r="J13">
+        <v>249.71</v>
+      </c>
+      <c r="K13">
+        <v>249.71</v>
+      </c>
+      <c r="L13">
+        <v>249.71</v>
+      </c>
+      <c r="M13">
+        <v>249.71</v>
+      </c>
+      <c r="N13">
+        <v>249.71</v>
+      </c>
+      <c r="O13">
+        <v>249.71</v>
+      </c>
+      <c r="P13">
+        <v>249.71</v>
+      </c>
+      <c r="Q13">
+        <v>249.71</v>
+      </c>
+      <c r="R13">
+        <v>249.71</v>
+      </c>
+      <c r="S13">
+        <v>249.71</v>
+      </c>
+      <c r="T13">
+        <v>249.71</v>
+      </c>
+      <c r="U13">
+        <v>249.71</v>
+      </c>
+      <c r="V13">
+        <v>249.71</v>
+      </c>
+      <c r="W13">
+        <v>249.71</v>
+      </c>
+      <c r="X13">
+        <v>249.71</v>
+      </c>
+      <c r="Y13">
+        <v>249.71</v>
+      </c>
+      <c r="Z13">
+        <v>249.71</v>
+      </c>
+      <c r="AA13">
+        <v>249.71</v>
+      </c>
+      <c r="AB13">
+        <v>249.71</v>
+      </c>
+      <c r="AC13">
+        <v>249.71</v>
+      </c>
+      <c r="AD13">
+        <v>249.71</v>
+      </c>
+      <c r="AE13">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="30"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="30">
+        <f>C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:AE16" si="0">D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="16">
+        <f>F6*SIN(RADIANS(F9+5.15))*F13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
+  <dimension ref="A1:AJ15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>485</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <f>C2-C2*0.17</f>
+        <v>402.55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <f>P5+1</f>
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <f>Q5+1</f>
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <f t="shared" ref="S5:AB5" si="0">R5+1</f>
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <f t="shared" ref="AC5:AI5" si="1">AB5+1</f>
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AG5" s="10">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="AH5" s="10">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="AI5" s="10">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>51.203000000000003</v>
+      </c>
+      <c r="D6">
+        <v>48.398000000000003</v>
+      </c>
+      <c r="E6">
+        <v>46.283999999999999</v>
+      </c>
+      <c r="F6">
+        <v>49.966000000000001</v>
+      </c>
+      <c r="G6">
+        <v>46.258000000000003</v>
+      </c>
+      <c r="H6">
+        <v>42.865000000000002</v>
+      </c>
+      <c r="I6">
+        <v>28.888999999999999</v>
+      </c>
+      <c r="J6">
+        <v>24.26</v>
+      </c>
+      <c r="K6">
+        <v>18.155999999999999</v>
+      </c>
+      <c r="L6">
+        <v>10.234</v>
+      </c>
+      <c r="M6">
+        <v>4.266</v>
+      </c>
+      <c r="N6">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="O6">
+        <v>5.4537000000000004</v>
+      </c>
+      <c r="P6">
+        <v>11.362</v>
+      </c>
+      <c r="Q6">
+        <v>17.478000000000002</v>
+      </c>
+      <c r="R6">
+        <v>24.577000000000002</v>
+      </c>
+      <c r="S6">
+        <v>31.812999999999999</v>
+      </c>
+      <c r="T6">
+        <v>37.369</v>
+      </c>
+      <c r="U6">
+        <v>42.365000000000002</v>
+      </c>
+      <c r="V6">
+        <v>47.408000000000001</v>
+      </c>
+      <c r="W6">
+        <v>50.768000000000001</v>
+      </c>
+      <c r="X6">
+        <v>53.197000000000003</v>
+      </c>
+      <c r="Y6">
+        <v>52.39</v>
+      </c>
+      <c r="Z6">
+        <v>52.238999999999997</v>
+      </c>
+      <c r="AA6">
+        <v>50.945</v>
+      </c>
+      <c r="AB6">
+        <v>46.247</v>
+      </c>
+      <c r="AC6">
+        <v>39.781999999999996</v>
+      </c>
+      <c r="AD6">
+        <v>30.405999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>-5.5</v>
+      </c>
+      <c r="D7">
+        <v>-10.5</v>
+      </c>
+      <c r="E7">
+        <v>-25.5</v>
+      </c>
+      <c r="F7">
+        <v>-4.5</v>
+      </c>
+      <c r="G7">
+        <v>-14.5</v>
+      </c>
+      <c r="H7">
+        <v>-20</v>
+      </c>
+      <c r="I7">
+        <v>-33</v>
+      </c>
+      <c r="J7">
+        <v>-39.5</v>
+      </c>
+      <c r="K7">
+        <v>-43</v>
+      </c>
+      <c r="L7">
+        <v>-50</v>
+      </c>
+      <c r="M7">
+        <v>-62.5</v>
+      </c>
+      <c r="N7">
+        <v>-60</v>
+      </c>
+      <c r="O7">
+        <v>-55</v>
+      </c>
+      <c r="P7">
+        <v>-53.5</v>
+      </c>
+      <c r="Q7">
+        <v>-46</v>
+      </c>
+      <c r="R7">
+        <v>-40</v>
+      </c>
+      <c r="S7">
+        <v>-36.5</v>
+      </c>
+      <c r="T7">
+        <v>-33.5</v>
+      </c>
+      <c r="U7">
+        <v>-29.5</v>
+      </c>
+      <c r="V7">
+        <v>-24.5</v>
+      </c>
+      <c r="W7">
+        <v>-17.5</v>
+      </c>
+      <c r="X7">
+        <v>-14.5</v>
+      </c>
+      <c r="Y7">
+        <v>-5.5</v>
+      </c>
+      <c r="Z7">
+        <v>-3</v>
+      </c>
+      <c r="AA7">
+        <v>-0.5</v>
+      </c>
+      <c r="AB7">
+        <v>3.5</v>
+      </c>
+      <c r="AC7">
+        <v>11.5</v>
+      </c>
+      <c r="AD7">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>87</v>
+      </c>
+      <c r="D8" s="1">
+        <v>82.5</v>
+      </c>
+      <c r="E8" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>115.1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>114.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>117.3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>115.4</v>
+      </c>
+      <c r="J8" s="1">
+        <v>116.8</v>
+      </c>
+      <c r="K8" s="1">
+        <v>114.9</v>
+      </c>
+      <c r="L8" s="1">
+        <v>113</v>
+      </c>
+      <c r="M8" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="N8" s="1">
+        <v>110.8</v>
+      </c>
+      <c r="O8" s="1">
+        <v>112.3</v>
+      </c>
+      <c r="P8" s="1">
+        <v>110.5</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>112</v>
+      </c>
+      <c r="R8" s="1">
+        <v>111.3</v>
+      </c>
+      <c r="S8" s="1">
+        <v>115.7</v>
+      </c>
+      <c r="T8" s="1">
+        <v>116.6</v>
+      </c>
+      <c r="U8" s="1">
+        <v>115.4</v>
+      </c>
+      <c r="V8" s="1">
+        <v>113.5</v>
+      </c>
+      <c r="W8" s="1">
+        <v>118.9</v>
+      </c>
+      <c r="X8" s="1">
+        <v>115.5</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>116.5</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>117.7</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>117.4</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>119</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>115.1</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>461.5</v>
+      </c>
+      <c r="D10">
+        <v>456</v>
+      </c>
+      <c r="E10">
+        <v>450.5</v>
+      </c>
+      <c r="F10">
+        <v>460.5</v>
+      </c>
+      <c r="G10">
+        <v>452</v>
+      </c>
+      <c r="H10">
+        <v>449</v>
+      </c>
+      <c r="I10">
+        <v>432</v>
+      </c>
+      <c r="J10">
+        <v>428</v>
+      </c>
+      <c r="K10">
+        <v>423</v>
+      </c>
+      <c r="L10">
+        <v>415</v>
+      </c>
+      <c r="M10">
+        <v>409.5</v>
+      </c>
+      <c r="N10">
+        <v>406</v>
+      </c>
+      <c r="O10">
+        <v>410</v>
+      </c>
+      <c r="P10">
+        <v>414.5</v>
+      </c>
+      <c r="Q10">
+        <v>420.5</v>
+      </c>
+      <c r="R10">
+        <v>426</v>
+      </c>
+      <c r="S10">
+        <v>430</v>
+      </c>
+      <c r="T10">
+        <v>433.5</v>
+      </c>
+      <c r="U10" s="2">
+        <v>441</v>
+      </c>
+      <c r="V10" s="2">
+        <v>445</v>
+      </c>
+      <c r="W10" s="2">
+        <v>451</v>
+      </c>
+      <c r="X10" s="2">
+        <v>454</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>455.5</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>458.5</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>462</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>461.5</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>465</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>467</v>
+      </c>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>265</v>
+      </c>
+      <c r="D12">
+        <v>265</v>
+      </c>
+      <c r="E12">
+        <v>265</v>
+      </c>
+      <c r="F12">
+        <v>300</v>
+      </c>
+      <c r="G12">
+        <v>300</v>
+      </c>
+      <c r="H12">
+        <v>300</v>
+      </c>
+      <c r="I12">
+        <v>300</v>
+      </c>
+      <c r="J12">
+        <v>300</v>
+      </c>
+      <c r="K12">
+        <v>300</v>
+      </c>
+      <c r="L12">
+        <v>300</v>
+      </c>
+      <c r="M12">
+        <v>300</v>
+      </c>
+      <c r="N12">
+        <v>300</v>
+      </c>
+      <c r="O12">
+        <v>300</v>
+      </c>
+      <c r="P12">
+        <v>300</v>
+      </c>
+      <c r="Q12">
+        <v>300</v>
+      </c>
+      <c r="R12">
+        <v>300</v>
+      </c>
+      <c r="S12">
+        <v>300</v>
+      </c>
+      <c r="T12">
+        <v>310</v>
+      </c>
+      <c r="U12">
+        <v>310</v>
+      </c>
+      <c r="V12">
+        <v>310</v>
+      </c>
+      <c r="W12">
+        <v>310</v>
+      </c>
+      <c r="X12">
+        <v>310</v>
+      </c>
+      <c r="Y12">
+        <v>310</v>
+      </c>
+      <c r="Z12">
+        <v>310</v>
+      </c>
+      <c r="AA12">
+        <v>310</v>
+      </c>
+      <c r="AB12">
+        <v>310</v>
+      </c>
+      <c r="AC12">
+        <v>310</v>
+      </c>
+      <c r="AD12">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>62</v>
+      </c>
+      <c r="D13">
+        <v>74</v>
+      </c>
+      <c r="E13">
+        <v>76</v>
+      </c>
+      <c r="F13">
+        <v>64</v>
+      </c>
+      <c r="G13">
+        <v>72</v>
+      </c>
+      <c r="H13">
+        <v>76</v>
+      </c>
+      <c r="I13">
+        <v>79.5</v>
+      </c>
+      <c r="J13">
+        <v>81.5</v>
+      </c>
+      <c r="K13">
+        <v>77</v>
+      </c>
+      <c r="L13">
+        <v>81</v>
+      </c>
+      <c r="M13">
+        <v>74</v>
+      </c>
+      <c r="N13">
+        <v>68</v>
+      </c>
+      <c r="O13">
+        <v>74</v>
+      </c>
+      <c r="P13">
+        <v>77</v>
+      </c>
+      <c r="Q13">
+        <v>75</v>
+      </c>
+      <c r="R13">
+        <v>79</v>
+      </c>
+      <c r="S13">
+        <v>80</v>
+      </c>
+      <c r="T13">
+        <v>78</v>
+      </c>
+      <c r="U13">
+        <v>79</v>
+      </c>
+      <c r="V13">
+        <v>77</v>
+      </c>
+      <c r="W13">
+        <v>75.5</v>
+      </c>
+      <c r="X13">
+        <v>72</v>
+      </c>
+      <c r="Y13">
+        <v>61.5</v>
+      </c>
+      <c r="Z13">
+        <v>62.5</v>
+      </c>
+      <c r="AA13">
+        <v>54.5</v>
+      </c>
+      <c r="AB13">
+        <v>48</v>
+      </c>
+      <c r="AC13">
+        <v>38.5</v>
+      </c>
+      <c r="AD13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:AI15" si="2">C6*-SIN(RADIANS(C8))*C12/1000</f>
+        <v>-13.550199438030189</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>-12.715746326203965</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>-12.227450296743585</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>-13.574295183417183</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>-12.617833179689791</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>-11.427173303326315</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>-7.8289359826583684</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="2"/>
+        <v>-6.4962395866945686</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>-4.9404873370427511</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>-2.8261340010696823</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="2"/>
+        <v>-1.2108000422274927</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="2"/>
+        <v>-0.11021594724709009</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="2"/>
+        <v>-1.5137448723481624</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="2"/>
+        <v>-3.1927408242720881</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="2"/>
+        <v>-4.8615958230354943</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="2"/>
+        <v>-6.8694525901110115</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="2"/>
+        <v>-8.5997889837959107</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="2"/>
+        <v>-10.35823139969961</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="2"/>
+        <v>-11.863637901467659</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="2"/>
+        <v>-13.477555041999489</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="2"/>
+        <v>-13.77813076308844</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="2"/>
+        <v>-14.884597105183458</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="2"/>
+        <v>-14.534539473342328</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="2"/>
+        <v>-14.338144060893327</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="2"/>
+        <v>-14.021223986689929</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="2"/>
+        <v>-12.539046654783448</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="2"/>
+        <v>-11.167854768300959</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="2"/>
+        <v>-8.2836070695559112</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
+  <dimension ref="A1:AJ29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>485</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <f>C2-C2*0.17</f>
+        <v>402.55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>398</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <f>P5+1</f>
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <f>Q5+1</f>
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AG5" s="10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AH5" s="10">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="AI5" s="10">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>43.774000000000001</v>
+      </c>
+      <c r="D6">
+        <v>43.682000000000002</v>
+      </c>
+      <c r="E6">
+        <v>45.475000000000001</v>
+      </c>
+      <c r="F6">
+        <v>41.618000000000002</v>
+      </c>
+      <c r="G6">
+        <v>34.204000000000001</v>
+      </c>
+      <c r="H6">
+        <v>27.984999999999999</v>
+      </c>
+      <c r="I6">
+        <v>18.039000000000001</v>
+      </c>
+      <c r="J6">
+        <v>6.0835999999999997</v>
+      </c>
+      <c r="K6">
+        <v>2.9384000000000001</v>
+      </c>
+      <c r="L6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="M6">
+        <v>7.3449999999999998</v>
+      </c>
+      <c r="N6">
+        <v>15.176</v>
+      </c>
+      <c r="O6">
+        <v>23.530999999999999</v>
+      </c>
+      <c r="P6">
+        <v>29.727</v>
+      </c>
+      <c r="Q6">
+        <v>38.637999999999998</v>
+      </c>
+      <c r="R6">
+        <v>46.064999999999998</v>
+      </c>
+      <c r="S6">
+        <v>50.881999999999998</v>
+      </c>
+      <c r="T6">
+        <v>53.805999999999997</v>
+      </c>
+      <c r="U6">
+        <v>53.527999999999999</v>
+      </c>
+      <c r="V6">
+        <v>48.012999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>5.5</v>
+      </c>
+      <c r="E7">
+        <v>-1</v>
+      </c>
+      <c r="F7">
+        <v>-15</v>
+      </c>
+      <c r="G7">
+        <v>-26.6</v>
+      </c>
+      <c r="H7">
+        <v>-35</v>
+      </c>
+      <c r="I7">
+        <v>-42.5</v>
+      </c>
+      <c r="J7">
+        <v>-56</v>
+      </c>
+      <c r="K7">
+        <v>-56</v>
+      </c>
+      <c r="L7">
+        <v>-63</v>
+      </c>
+      <c r="M7">
+        <v>-64</v>
+      </c>
+      <c r="N7">
+        <v>-55</v>
+      </c>
+      <c r="O7">
+        <v>-48</v>
+      </c>
+      <c r="P7">
+        <v>-42</v>
+      </c>
+      <c r="Q7">
+        <v>-35</v>
+      </c>
+      <c r="R7">
+        <v>-26</v>
+      </c>
+      <c r="S7">
+        <v>-19</v>
+      </c>
+      <c r="T7">
+        <v>-11</v>
+      </c>
+      <c r="U7">
+        <v>0.5</v>
+      </c>
+      <c r="V7">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>92.7</v>
+      </c>
+      <c r="D8" s="1">
+        <v>91</v>
+      </c>
+      <c r="E8" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>93</v>
+      </c>
+      <c r="G8" s="1">
+        <v>95.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>94.1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>91.9</v>
+      </c>
+      <c r="J8" s="1">
+        <v>91.7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>92.2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>91.1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>90</v>
+      </c>
+      <c r="N8" s="1">
+        <v>92.1</v>
+      </c>
+      <c r="O8" s="1">
+        <v>92.1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>92.6</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>93.7</v>
+      </c>
+      <c r="R8" s="1">
+        <v>93.8</v>
+      </c>
+      <c r="S8" s="1">
+        <v>95.4</v>
+      </c>
+      <c r="T8" s="1">
+        <v>96.9</v>
+      </c>
+      <c r="U8" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="V8" s="1">
+        <v>95.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>467</v>
+      </c>
+      <c r="D10">
+        <v>466</v>
+      </c>
+      <c r="E10">
+        <v>463</v>
+      </c>
+      <c r="F10">
+        <v>450</v>
+      </c>
+      <c r="G10">
+        <v>443</v>
+      </c>
+      <c r="H10">
+        <v>431</v>
+      </c>
+      <c r="I10">
+        <v>423</v>
+      </c>
+      <c r="J10">
+        <v>411</v>
+      </c>
+      <c r="K10">
+        <v>408</v>
+      </c>
+      <c r="L10">
+        <v>404</v>
+      </c>
+      <c r="M10">
+        <v>407</v>
+      </c>
+      <c r="N10">
+        <v>413</v>
+      </c>
+      <c r="O10">
+        <v>420</v>
+      </c>
+      <c r="P10">
+        <v>422</v>
+      </c>
+      <c r="Q10">
+        <v>433</v>
+      </c>
+      <c r="R10">
+        <v>442</v>
+      </c>
+      <c r="S10">
+        <v>448</v>
+      </c>
+      <c r="T10">
+        <v>455</v>
+      </c>
+      <c r="U10" s="2">
+        <v>460</v>
+      </c>
+      <c r="V10" s="2">
+        <v>466</v>
+      </c>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>275</v>
+      </c>
+      <c r="D12">
+        <v>275</v>
+      </c>
+      <c r="E12">
+        <v>275</v>
+      </c>
+      <c r="F12">
+        <v>275</v>
+      </c>
+      <c r="G12">
+        <v>275</v>
+      </c>
+      <c r="H12">
+        <v>275</v>
+      </c>
+      <c r="I12">
+        <v>275</v>
+      </c>
+      <c r="J12">
+        <v>275</v>
+      </c>
+      <c r="K12">
+        <v>275</v>
+      </c>
+      <c r="L12">
+        <v>275</v>
+      </c>
+      <c r="M12">
+        <v>275</v>
+      </c>
+      <c r="N12">
+        <v>275</v>
+      </c>
+      <c r="O12">
+        <v>275</v>
+      </c>
+      <c r="P12">
+        <v>275</v>
+      </c>
+      <c r="Q12">
+        <v>275</v>
+      </c>
+      <c r="R12">
+        <v>275</v>
+      </c>
+      <c r="S12">
+        <v>275</v>
+      </c>
+      <c r="T12">
+        <v>275</v>
+      </c>
+      <c r="U12">
+        <v>275</v>
+      </c>
+      <c r="V12">
+        <v>275</v>
+      </c>
+      <c r="W12">
+        <v>275</v>
+      </c>
+      <c r="X12">
+        <v>275</v>
+      </c>
+      <c r="Y12">
+        <v>275</v>
+      </c>
+      <c r="Z12">
+        <v>275</v>
+      </c>
+      <c r="AA12">
+        <v>275</v>
+      </c>
+      <c r="AB12">
+        <v>275</v>
+      </c>
+      <c r="AC12">
+        <v>275</v>
+      </c>
+      <c r="AD12">
+        <v>275</v>
+      </c>
+      <c r="AE12">
+        <v>275</v>
+      </c>
+      <c r="AF12">
+        <v>275</v>
+      </c>
+      <c r="AG12">
+        <v>275</v>
+      </c>
+      <c r="AH12">
+        <v>275</v>
+      </c>
+      <c r="AI12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>45</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>55</v>
+      </c>
+      <c r="F13">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>70</v>
+      </c>
+      <c r="H13">
+        <v>74</v>
+      </c>
+      <c r="I13">
+        <v>73</v>
+      </c>
+      <c r="J13">
+        <v>72</v>
+      </c>
+      <c r="K13">
+        <v>65</v>
+      </c>
+      <c r="L13">
+        <v>63</v>
+      </c>
+      <c r="M13">
+        <v>66</v>
+      </c>
+      <c r="N13">
+        <v>71</v>
+      </c>
+      <c r="O13">
+        <v>75</v>
+      </c>
+      <c r="P13">
+        <v>75</v>
+      </c>
+      <c r="Q13">
+        <v>76</v>
+      </c>
+      <c r="R13">
+        <v>75</v>
+      </c>
+      <c r="S13">
+        <v>69</v>
+      </c>
+      <c r="T13">
+        <v>65</v>
+      </c>
+      <c r="U13">
+        <v>56</v>
+      </c>
+      <c r="V13">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
+        <v>-12.024486481310953</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
+        <v>-12.010720430450908</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>-12.467074331666348</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>-11.429265093789359</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>-9.361208446969103</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>-7.6761795853386783</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>-4.9579976724776733</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>-1.6722536503811283</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>-0.80746439223476663</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>-3.5743411708348779E-3</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="1"/>
+        <v>-2.0198749999999999</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>-4.1705971185958441</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="1"/>
+        <v>-6.4666790193515293</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>-8.1665094852463582</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="1"/>
+        <v>-10.603302506170124</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>-12.640024275140153</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>-13.930450567806828</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="1"/>
+        <v>-14.689482923460329</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="1"/>
+        <v>-14.674822536018389</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="1"/>
+        <v>-13.151302910231001</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
+      <c r="R29">
+        <f>485*1.03</f>
+        <v>499.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
+  <dimension ref="A1:AJ29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>457</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <f>C2-C2*0.17</f>
+        <v>379.31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <f>P5+1</f>
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <f>Q5+1</f>
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AG5" s="10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AH5" s="10">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="AI5" s="10">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>67.698999999999998</v>
+      </c>
+      <c r="D6">
+        <v>53.807000000000002</v>
+      </c>
+      <c r="E6">
+        <v>40.158999999999999</v>
+      </c>
+      <c r="F6">
+        <v>29.155000000000001</v>
+      </c>
+      <c r="G6">
+        <v>19.347000000000001</v>
+      </c>
+      <c r="H6">
+        <v>18.911000000000001</v>
+      </c>
+      <c r="I6">
+        <v>10.577</v>
+      </c>
+      <c r="J6">
+        <v>6.6810999999999998</v>
+      </c>
+      <c r="K6">
+        <v>3.8237000000000001</v>
+      </c>
+      <c r="L6">
+        <v>2.0994000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>-41</v>
+      </c>
+      <c r="D7">
+        <v>-45</v>
+      </c>
+      <c r="E7">
+        <v>-57</v>
+      </c>
+      <c r="F7">
+        <v>-63</v>
+      </c>
+      <c r="G7">
+        <v>-77</v>
+      </c>
+      <c r="H7">
+        <v>-75</v>
+      </c>
+      <c r="I7">
+        <v>-80</v>
+      </c>
+      <c r="J7">
+        <v>-90</v>
+      </c>
+      <c r="K7">
+        <v>-95</v>
+      </c>
+      <c r="L7">
+        <v>-105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>71.2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>75.3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>72.7</v>
+      </c>
+      <c r="F8" s="1">
+        <v>74.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="H8" s="1">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I8" s="1">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="J8" s="1">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="K8" s="1">
+        <v>78</v>
+      </c>
+      <c r="L8" s="1">
+        <v>76.599999999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>428</v>
+      </c>
+      <c r="D10">
+        <v>418</v>
+      </c>
+      <c r="E10">
+        <v>409.5</v>
+      </c>
+      <c r="F10">
+        <v>405.5</v>
+      </c>
+      <c r="G10">
+        <v>395</v>
+      </c>
+      <c r="H10">
+        <v>396</v>
+      </c>
+      <c r="I10">
+        <v>390</v>
+      </c>
+      <c r="J10">
+        <v>384</v>
+      </c>
+      <c r="K10">
+        <v>381</v>
+      </c>
+      <c r="L10">
+        <v>376</v>
+      </c>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>275</v>
+      </c>
+      <c r="D12">
+        <v>275</v>
+      </c>
+      <c r="E12">
+        <v>275</v>
+      </c>
+      <c r="F12">
+        <v>275</v>
+      </c>
+      <c r="G12">
+        <v>275</v>
+      </c>
+      <c r="H12">
+        <v>275</v>
+      </c>
+      <c r="I12">
+        <v>275</v>
+      </c>
+      <c r="J12">
+        <v>275</v>
+      </c>
+      <c r="K12">
+        <v>275</v>
+      </c>
+      <c r="L12">
+        <v>275</v>
+      </c>
+      <c r="M12">
+        <v>275</v>
+      </c>
+      <c r="N12">
+        <v>275</v>
+      </c>
+      <c r="O12">
+        <v>275</v>
+      </c>
+      <c r="P12">
+        <v>275</v>
+      </c>
+      <c r="Q12">
+        <v>275</v>
+      </c>
+      <c r="R12">
+        <v>275</v>
+      </c>
+      <c r="S12">
+        <v>275</v>
+      </c>
+      <c r="T12">
+        <v>275</v>
+      </c>
+      <c r="U12">
+        <v>275</v>
+      </c>
+      <c r="V12">
+        <v>275</v>
+      </c>
+      <c r="W12">
+        <v>275</v>
+      </c>
+      <c r="X12">
+        <v>275</v>
+      </c>
+      <c r="Y12">
+        <v>275</v>
+      </c>
+      <c r="Z12">
+        <v>275</v>
+      </c>
+      <c r="AA12">
+        <v>275</v>
+      </c>
+      <c r="AB12">
+        <v>275</v>
+      </c>
+      <c r="AC12">
+        <v>275</v>
+      </c>
+      <c r="AD12">
+        <v>275</v>
+      </c>
+      <c r="AE12">
+        <v>275</v>
+      </c>
+      <c r="AF12">
+        <v>275</v>
+      </c>
+      <c r="AG12">
+        <v>275</v>
+      </c>
+      <c r="AH12">
+        <v>275</v>
+      </c>
+      <c r="AI12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>80</v>
+      </c>
+      <c r="D13">
+        <v>81</v>
+      </c>
+      <c r="E13">
+        <v>78</v>
+      </c>
+      <c r="F13">
+        <v>76</v>
+      </c>
+      <c r="G13">
+        <v>62</v>
+      </c>
+      <c r="H13">
+        <v>62.5</v>
+      </c>
+      <c r="I13">
+        <v>60</v>
+      </c>
+      <c r="J13">
+        <v>48</v>
+      </c>
+      <c r="K13">
+        <v>34</v>
+      </c>
+      <c r="L13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
+        <v>-17.623982271657447</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
+        <v>-14.312588392743191</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>-10.544115710489031</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>-7.714703040370237</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>-5.2633492521046072</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>-5.0482353303594207</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>-2.8329795466253955</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>-1.807118322254111</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>-1.0285393197546095</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>-0.56161756164602195</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="10:18" x14ac:dyDescent="0.35">
+      <c r="J18">
+        <f>1-348/457</f>
+        <v>0.23851203501094087</v>
+      </c>
+    </row>
+    <row r="29" spans="10:18" x14ac:dyDescent="0.35">
+      <c r="R29">
+        <f>485*1.03</f>
+        <v>499.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B26E4-CFF3-41E2-8721-B0918FFC9B0E}">
+  <dimension ref="A1:AK36"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2">
+        <v>479</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3">
+        <v>413</v>
+      </c>
+      <c r="D3">
+        <f>(C3/C2)</f>
+        <v>0.86221294363256784</v>
+      </c>
+      <c r="E3">
+        <f>1-D3</f>
+        <v>0.13778705636743216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A5" s="10"/>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>7.6539999999999999</v>
+      </c>
+      <c r="D6">
+        <v>16.346</v>
+      </c>
+      <c r="E6">
+        <v>28.263000000000002</v>
+      </c>
+      <c r="F6">
+        <v>41.6</v>
+      </c>
+      <c r="G6">
+        <v>53.704999999999998</v>
+      </c>
+      <c r="H6">
+        <v>59.472000000000001</v>
+      </c>
+      <c r="I6">
+        <v>63.2</v>
+      </c>
+      <c r="J6">
+        <v>65.655000000000001</v>
+      </c>
+      <c r="K6">
+        <v>76.481999999999999</v>
+      </c>
+      <c r="L6">
+        <v>68.266999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="16">
+        <v>-68.718999999999994</v>
+      </c>
+      <c r="D7">
+        <v>-61.898000000000003</v>
+      </c>
+      <c r="E7">
+        <v>-54.359000000000002</v>
+      </c>
+      <c r="F7">
+        <v>-46.460999999999999</v>
+      </c>
+      <c r="G7">
+        <v>-38.204000000000001</v>
+      </c>
+      <c r="H7">
+        <v>-32.100999999999999</v>
+      </c>
+      <c r="I7">
+        <v>-27.8</v>
+      </c>
+      <c r="J7">
+        <v>-24.202999999999999</v>
+      </c>
+      <c r="K7">
+        <v>-9.125</v>
+      </c>
+      <c r="L7">
+        <v>-21.331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="D8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="E8">
+        <v>622.85</v>
+      </c>
+      <c r="F8">
+        <v>622.85</v>
+      </c>
+      <c r="G8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="H8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="I8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="J8">
+        <v>622.85</v>
+      </c>
+      <c r="K8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="L8">
+        <v>621.36500000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="15">
+        <v>82</v>
+      </c>
+      <c r="D9" s="1">
+        <v>86</v>
+      </c>
+      <c r="E9" s="1">
+        <v>84.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>98.5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>87</v>
+      </c>
+      <c r="H9" s="1">
+        <v>86</v>
+      </c>
+      <c r="I9" s="1">
+        <v>85</v>
+      </c>
+      <c r="J9" s="1">
+        <v>83</v>
+      </c>
+      <c r="K9" s="1">
+        <v>56</v>
+      </c>
+      <c r="L9" s="1">
+        <v>56</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="C10" s="16">
         <v>408</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10">
         <v>410</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10">
         <v>421</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10">
         <v>427</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10">
         <v>437</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10">
         <v>441</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10">
         <v>444</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10">
         <v>447</v>
       </c>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
+      <c r="K10">
+        <v>456</v>
+      </c>
+      <c r="L10">
+        <v>446</v>
+      </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
@@ -25369,6 +27212,12 @@
       <c r="J14">
         <v>77</v>
       </c>
+      <c r="K14">
+        <v>67</v>
+      </c>
+      <c r="L14">
+        <v>76</v>
+      </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
@@ -25450,11 +27299,11 @@
       </c>
       <c r="K16" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-16.727950101680829</v>
       </c>
       <c r="L16" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-14.931186025358189</v>
       </c>
       <c r="M16" s="16">
         <f t="shared" si="0"/>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A30B11-BBCA-4BDD-B5B7-9FDA39D18D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C53A715-A518-499E-84CF-594F33F4204D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26670" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="12" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="41085" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="11" activeTab="12" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -349,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="85">
   <si>
     <t>Test #</t>
   </si>
@@ -599,12 +599,18 @@
   <si>
     <t>v</t>
   </si>
+  <si>
+    <t>Ext Test 13</t>
+  </si>
+  <si>
+    <t>Ext Test 12</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -646,12 +652,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -830,7 +830,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -864,6 +864,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -2975,36 +2976,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -3014,9 +2985,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:v>result</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -3130,126 +3098,117 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>ExtTest10mm_12!$D$7:$S$7</c:f>
+              <c:f>ExtTest10mm_13!$C$7:$S$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>28.29</c:v>
+                  <c:v>23.184999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.149999999999999</c:v>
+                  <c:v>17.440999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.29</c:v>
+                  <c:v>9.1839999999999993</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-14.86</c:v>
+                  <c:v>2.004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-25.64</c:v>
+                  <c:v>-4.8170000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-36.76</c:v>
+                  <c:v>-10.561</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-42.87</c:v>
+                  <c:v>-16.305</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-49.33</c:v>
+                  <c:v>-21.331</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-56.87</c:v>
+                  <c:v>-26.356999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-68.36</c:v>
+                  <c:v>-32.46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-77.69</c:v>
+                  <c:v>-40.716999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-84.16</c:v>
+                  <c:v>-50.051000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-90.1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-99.233999999999995</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>-82</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>-65.48</c:v>
+                  <c:v>-55.795000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ExtTest10mm_12!$D$16:$AB$16</c:f>
+              <c:f>ExtTest10mm_13!$C$16:$AB$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.38934455560856757</c:v>
+                  <c:v>0.17716929126497558</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.8112948210918218</c:v>
+                  <c:v>0.23580983133155201</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.4750917512529496</c:v>
+                  <c:v>0.31887857721722329</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.4446222516176634</c:v>
+                  <c:v>0.72357994775830636</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.9469453841091626</c:v>
+                  <c:v>0.89299667946631711</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.6590559428960212</c:v>
+                  <c:v>1.9413384783051184</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.0927652115792634</c:v>
+                  <c:v>2.4204380693667997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.0976142089621366</c:v>
+                  <c:v>2.7329938745931397</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.3279415846485803</c:v>
+                  <c:v>2.898194169907315</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.0095037627925798</c:v>
+                  <c:v>2.9622838327028997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.5711771242618884</c:v>
+                  <c:v>3.0909599773855079</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.937808715762241</c:v>
+                  <c:v>3.5556114225204913</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.3306919291859725</c:v>
+                  <c:v>3.8508462486362252</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.369972199445602</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.0892341737595572</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.4793670426458965</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.957246848957868</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.8935172428682936</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.5504713609212226</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.10037237370560359</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -3264,6 +3223,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -22634,6 +22596,7 @@
   <dimension ref="A1:AK36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
@@ -22643,7 +22606,7 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -23629,6 +23592,7 @@
   <dimension ref="A1:AK36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
@@ -23638,7 +23602,7 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -23648,7 +23612,7 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2">
-        <v>436</v>
+        <v>465</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
@@ -23660,15 +23624,15 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="D3">
         <f>(C3/C2)</f>
-        <v>0.8509174311926605</v>
+        <v>0.86236559139784941</v>
       </c>
       <c r="E3">
         <f>1-D3</f>
-        <v>0.1490825688073395</v>
+        <v>0.13763440860215059</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.35">
@@ -23682,24 +23646,7 @@
       <c r="E4" t="s">
         <v>59</v>
       </c>
-      <c r="M4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>77</v>
-      </c>
-      <c r="R4" t="s">
-        <v>78</v>
-      </c>
+      <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
@@ -23805,21 +23752,135 @@
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="16">
+        <v>0.71</v>
+      </c>
+      <c r="D6">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="E6">
+        <v>1.2769999999999999</v>
+      </c>
+      <c r="F6">
+        <v>2.8980000000000001</v>
+      </c>
+      <c r="G6">
+        <v>3.5779999999999998</v>
+      </c>
+      <c r="H6">
+        <v>7.7839999999999998</v>
+      </c>
+      <c r="I6">
+        <v>9.7050000000000001</v>
+      </c>
+      <c r="J6">
+        <v>10.984</v>
+      </c>
+      <c r="K6">
+        <v>11.667</v>
+      </c>
+      <c r="L6">
+        <v>11.925000000000001</v>
+      </c>
+      <c r="M6">
+        <v>12.443</v>
+      </c>
+      <c r="N6">
+        <v>14.452</v>
+      </c>
+      <c r="O6">
+        <v>15.651999999999999</v>
+      </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="30"/>
+      <c r="C7" s="16">
+        <v>23.184999999999999</v>
+      </c>
+      <c r="D7">
+        <v>17.440999999999999</v>
+      </c>
+      <c r="E7">
+        <v>9.1839999999999993</v>
+      </c>
+      <c r="F7">
+        <v>2.004</v>
+      </c>
+      <c r="G7">
+        <v>-4.8170000000000002</v>
+      </c>
+      <c r="H7">
+        <v>-10.561</v>
+      </c>
+      <c r="I7">
+        <v>-16.305</v>
+      </c>
+      <c r="J7">
+        <v>-21.331</v>
+      </c>
+      <c r="K7">
+        <v>-26.356999999999999</v>
+      </c>
+      <c r="L7">
+        <v>-32.46</v>
+      </c>
+      <c r="M7">
+        <v>-40.716999999999999</v>
+      </c>
+      <c r="N7">
+        <v>-50.051000000000002</v>
+      </c>
+      <c r="O7">
+        <v>-55.795000000000002</v>
+      </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="16">
+        <v>620.57899999999995</v>
+      </c>
+      <c r="D8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="E8">
+        <v>622.09299999999996</v>
+      </c>
+      <c r="F8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="G8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="H8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="I8">
+        <v>622.09299999999996</v>
+      </c>
+      <c r="J8">
+        <v>622.09299999999996</v>
+      </c>
+      <c r="K8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="L8">
+        <v>620.57899999999995</v>
+      </c>
+      <c r="M8">
+        <v>620.58000000000004</v>
+      </c>
+      <c r="N8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="O8">
+        <v>622.85</v>
+      </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
@@ -23828,19 +23889,45 @@
       <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
+      <c r="C9" s="15">
+        <v>87</v>
+      </c>
+      <c r="D9" s="1">
+        <v>87</v>
+      </c>
+      <c r="E9" s="1">
+        <v>85</v>
+      </c>
+      <c r="F9" s="1">
+        <v>84</v>
+      </c>
+      <c r="G9" s="1">
+        <v>83</v>
+      </c>
+      <c r="H9" s="1">
+        <v>82</v>
+      </c>
+      <c r="I9" s="1">
+        <v>82</v>
+      </c>
+      <c r="J9" s="1">
+        <v>80</v>
+      </c>
+      <c r="K9" s="1">
+        <v>79</v>
+      </c>
+      <c r="L9" s="1">
+        <v>79</v>
+      </c>
+      <c r="M9" s="1">
+        <v>79</v>
+      </c>
+      <c r="N9" s="1">
+        <v>75</v>
+      </c>
+      <c r="O9" s="1">
+        <v>75</v>
+      </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -23869,3175 +23956,44 @@
       <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="30"/>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="1"/>
-      <c r="AI11" s="1"/>
-      <c r="AJ11" s="1"/>
-      <c r="AK11" s="1"/>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="30"/>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="30">
-        <v>249.71</v>
-      </c>
-      <c r="D13">
-        <v>249.71</v>
-      </c>
-      <c r="E13">
-        <v>249.71</v>
-      </c>
-      <c r="F13">
-        <v>249.71</v>
-      </c>
-      <c r="G13">
-        <v>249.71</v>
-      </c>
-      <c r="H13">
-        <v>249.71</v>
-      </c>
-      <c r="I13">
-        <v>249.71</v>
-      </c>
-      <c r="J13">
-        <v>249.71</v>
-      </c>
-      <c r="K13">
-        <v>249.71</v>
-      </c>
-      <c r="L13">
-        <v>249.71</v>
-      </c>
-      <c r="M13">
-        <v>249.71</v>
-      </c>
-      <c r="N13">
-        <v>249.71</v>
-      </c>
-      <c r="O13">
-        <v>249.71</v>
-      </c>
-      <c r="P13">
-        <v>249.71</v>
-      </c>
-      <c r="Q13">
-        <v>249.71</v>
-      </c>
-      <c r="R13">
-        <v>249.71</v>
-      </c>
-      <c r="S13">
-        <v>249.71</v>
-      </c>
-      <c r="T13">
-        <v>249.71</v>
-      </c>
-      <c r="U13">
-        <v>249.71</v>
-      </c>
-      <c r="V13">
-        <v>249.71</v>
-      </c>
-      <c r="W13">
-        <v>249.71</v>
-      </c>
-      <c r="X13">
-        <v>249.71</v>
-      </c>
-      <c r="Y13">
-        <v>249.71</v>
-      </c>
-      <c r="Z13">
-        <v>249.71</v>
-      </c>
-      <c r="AA13">
-        <v>249.71</v>
-      </c>
-      <c r="AB13">
-        <v>249.71</v>
-      </c>
-      <c r="AC13">
-        <v>249.71</v>
-      </c>
-      <c r="AD13">
-        <v>249.71</v>
-      </c>
-      <c r="AE13">
-        <v>249.71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
-      <c r="B14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="30"/>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2"/>
-      <c r="AB15" s="2"/>
-      <c r="AC15" s="2"/>
-      <c r="AD15" s="2"/>
-      <c r="AE15" s="2"/>
-      <c r="AF15" s="2"/>
-      <c r="AG15" s="2"/>
-      <c r="AH15" s="2"/>
-      <c r="AI15" s="2"/>
-      <c r="AJ15" s="2"/>
-      <c r="AK15" s="2"/>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="B16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="30">
-        <f>C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="16">
-        <f t="shared" ref="D16:AE16" si="0">D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="16">
-        <f>F6*SIN(RADIANS(F9+5.15))*F13/1000</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="3"/>
-      <c r="B21" s="21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="3"/>
-      <c r="B27" s="29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
-  <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>485</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <f>C2-C2*0.17</f>
-        <v>402.55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
+      <c r="C10" s="16">
+        <v>404</v>
+      </c>
+      <c r="D10" s="33">
         <v>398</v>
       </c>
-    </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>P5+1</f>
-        <v>15</v>
-      </c>
-      <c r="R5" s="10">
-        <f>Q5+1</f>
-        <v>16</v>
-      </c>
-      <c r="S5" s="10">
-        <f t="shared" ref="S5:AB5" si="0">R5+1</f>
-        <v>17</v>
-      </c>
-      <c r="T5" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="U5" s="10">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V5" s="10">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W5" s="10">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X5" s="10">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Z5" s="10">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA5" s="10">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="10">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AC5" s="10">
-        <f t="shared" ref="AC5:AI5" si="1">AB5+1</f>
-        <v>27</v>
-      </c>
-      <c r="AD5" s="10">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="AE5" s="10">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="AF5" s="10">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AG5" s="10">
-        <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="AH5" s="10">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="AI5" s="10">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>51.203000000000003</v>
-      </c>
-      <c r="D6">
-        <v>48.398000000000003</v>
-      </c>
-      <c r="E6">
-        <v>46.283999999999999</v>
-      </c>
-      <c r="F6">
-        <v>49.966000000000001</v>
-      </c>
-      <c r="G6">
-        <v>46.258000000000003</v>
-      </c>
-      <c r="H6">
-        <v>42.865000000000002</v>
-      </c>
-      <c r="I6">
-        <v>28.888999999999999</v>
-      </c>
-      <c r="J6">
-        <v>24.26</v>
-      </c>
-      <c r="K6">
-        <v>18.155999999999999</v>
-      </c>
-      <c r="L6">
-        <v>10.234</v>
-      </c>
-      <c r="M6">
-        <v>4.266</v>
-      </c>
-      <c r="N6">
-        <v>0.39300000000000002</v>
-      </c>
-      <c r="O6">
-        <v>5.4537000000000004</v>
-      </c>
-      <c r="P6">
-        <v>11.362</v>
-      </c>
-      <c r="Q6">
-        <v>17.478000000000002</v>
-      </c>
-      <c r="R6">
-        <v>24.577000000000002</v>
-      </c>
-      <c r="S6">
-        <v>31.812999999999999</v>
-      </c>
-      <c r="T6">
-        <v>37.369</v>
-      </c>
-      <c r="U6">
-        <v>42.365000000000002</v>
-      </c>
-      <c r="V6">
-        <v>47.408000000000001</v>
-      </c>
-      <c r="W6">
-        <v>50.768000000000001</v>
-      </c>
-      <c r="X6">
-        <v>53.197000000000003</v>
-      </c>
-      <c r="Y6">
-        <v>52.39</v>
-      </c>
-      <c r="Z6">
-        <v>52.238999999999997</v>
-      </c>
-      <c r="AA6">
-        <v>50.945</v>
-      </c>
-      <c r="AB6">
-        <v>46.247</v>
-      </c>
-      <c r="AC6">
-        <v>39.781999999999996</v>
-      </c>
-      <c r="AD6">
-        <v>30.405999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>-5.5</v>
-      </c>
-      <c r="D7">
-        <v>-10.5</v>
-      </c>
-      <c r="E7">
-        <v>-25.5</v>
-      </c>
-      <c r="F7">
-        <v>-4.5</v>
-      </c>
-      <c r="G7">
-        <v>-14.5</v>
-      </c>
-      <c r="H7">
-        <v>-20</v>
-      </c>
-      <c r="I7">
-        <v>-33</v>
-      </c>
-      <c r="J7">
-        <v>-39.5</v>
-      </c>
-      <c r="K7">
-        <v>-43</v>
-      </c>
-      <c r="L7">
-        <v>-50</v>
-      </c>
-      <c r="M7">
-        <v>-62.5</v>
-      </c>
-      <c r="N7">
-        <v>-60</v>
-      </c>
-      <c r="O7">
-        <v>-55</v>
-      </c>
-      <c r="P7">
-        <v>-53.5</v>
-      </c>
-      <c r="Q7">
-        <v>-46</v>
-      </c>
-      <c r="R7">
-        <v>-40</v>
-      </c>
-      <c r="S7">
-        <v>-36.5</v>
-      </c>
-      <c r="T7">
-        <v>-33.5</v>
-      </c>
-      <c r="U7">
-        <v>-29.5</v>
-      </c>
-      <c r="V7">
-        <v>-24.5</v>
-      </c>
-      <c r="W7">
-        <v>-17.5</v>
-      </c>
-      <c r="X7">
-        <v>-14.5</v>
-      </c>
-      <c r="Y7">
-        <v>-5.5</v>
-      </c>
-      <c r="Z7">
-        <v>-3</v>
-      </c>
-      <c r="AA7">
-        <v>-0.5</v>
-      </c>
-      <c r="AB7">
-        <v>3.5</v>
-      </c>
-      <c r="AC7">
-        <v>11.5</v>
-      </c>
-      <c r="AD7">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>87</v>
-      </c>
-      <c r="D8" s="1">
-        <v>82.5</v>
-      </c>
-      <c r="E8" s="1">
-        <v>94.5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>115.1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>114.6</v>
-      </c>
-      <c r="H8" s="1">
-        <v>117.3</v>
-      </c>
-      <c r="I8" s="1">
-        <v>115.4</v>
-      </c>
-      <c r="J8" s="1">
-        <v>116.8</v>
-      </c>
-      <c r="K8" s="1">
-        <v>114.9</v>
-      </c>
-      <c r="L8" s="1">
-        <v>113</v>
-      </c>
-      <c r="M8" s="1">
-        <v>108.9</v>
-      </c>
-      <c r="N8" s="1">
-        <v>110.8</v>
-      </c>
-      <c r="O8" s="1">
-        <v>112.3</v>
-      </c>
-      <c r="P8" s="1">
-        <v>110.5</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>112</v>
-      </c>
-      <c r="R8" s="1">
-        <v>111.3</v>
-      </c>
-      <c r="S8" s="1">
-        <v>115.7</v>
-      </c>
-      <c r="T8" s="1">
-        <v>116.6</v>
-      </c>
-      <c r="U8" s="1">
-        <v>115.4</v>
-      </c>
-      <c r="V8" s="1">
-        <v>113.5</v>
-      </c>
-      <c r="W8" s="1">
-        <v>118.9</v>
-      </c>
-      <c r="X8" s="1">
-        <v>115.5</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>116.5</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>117.7</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>117.4</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>119</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>115.1</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>118.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>461.5</v>
-      </c>
-      <c r="D10">
-        <v>456</v>
-      </c>
-      <c r="E10">
-        <v>450.5</v>
-      </c>
-      <c r="F10">
-        <v>460.5</v>
-      </c>
-      <c r="G10">
-        <v>452</v>
-      </c>
-      <c r="H10">
-        <v>449</v>
-      </c>
-      <c r="I10">
-        <v>432</v>
-      </c>
-      <c r="J10">
-        <v>428</v>
-      </c>
-      <c r="K10">
-        <v>423</v>
-      </c>
-      <c r="L10">
-        <v>415</v>
-      </c>
-      <c r="M10">
-        <v>409.5</v>
-      </c>
-      <c r="N10">
-        <v>406</v>
-      </c>
-      <c r="O10">
+      <c r="E10" s="33">
+        <v>393</v>
+      </c>
+      <c r="F10" s="33">
+        <v>393</v>
+      </c>
+      <c r="G10" s="33">
+        <v>390</v>
+      </c>
+      <c r="H10" s="33">
+        <v>394</v>
+      </c>
+      <c r="I10" s="33">
+        <v>397</v>
+      </c>
+      <c r="J10" s="33">
+        <v>399</v>
+      </c>
+      <c r="K10" s="33">
+        <v>400</v>
+      </c>
+      <c r="L10" s="33">
+        <v>404</v>
+      </c>
+      <c r="M10" s="33">
+        <v>407</v>
+      </c>
+      <c r="N10" s="33">
         <v>410</v>
       </c>
-      <c r="P10">
-        <v>414.5</v>
-      </c>
-      <c r="Q10">
-        <v>420.5</v>
-      </c>
-      <c r="R10">
-        <v>426</v>
-      </c>
-      <c r="S10">
-        <v>430</v>
-      </c>
-      <c r="T10">
-        <v>433.5</v>
-      </c>
-      <c r="U10" s="2">
-        <v>441</v>
-      </c>
-      <c r="V10" s="2">
-        <v>445</v>
-      </c>
-      <c r="W10" s="2">
-        <v>451</v>
-      </c>
-      <c r="X10" s="2">
-        <v>454</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>455.5</v>
-      </c>
-      <c r="Z10" s="2">
-        <v>458.5</v>
-      </c>
-      <c r="AA10" s="2">
-        <v>462</v>
-      </c>
-      <c r="AB10" s="2">
-        <v>461.5</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>465</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>467</v>
-      </c>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>265</v>
-      </c>
-      <c r="D12">
-        <v>265</v>
-      </c>
-      <c r="E12">
-        <v>265</v>
-      </c>
-      <c r="F12">
-        <v>300</v>
-      </c>
-      <c r="G12">
-        <v>300</v>
-      </c>
-      <c r="H12">
-        <v>300</v>
-      </c>
-      <c r="I12">
-        <v>300</v>
-      </c>
-      <c r="J12">
-        <v>300</v>
-      </c>
-      <c r="K12">
-        <v>300</v>
-      </c>
-      <c r="L12">
-        <v>300</v>
-      </c>
-      <c r="M12">
-        <v>300</v>
-      </c>
-      <c r="N12">
-        <v>300</v>
-      </c>
-      <c r="O12">
-        <v>300</v>
-      </c>
-      <c r="P12">
-        <v>300</v>
-      </c>
-      <c r="Q12">
-        <v>300</v>
-      </c>
-      <c r="R12">
-        <v>300</v>
-      </c>
-      <c r="S12">
-        <v>300</v>
-      </c>
-      <c r="T12">
-        <v>310</v>
-      </c>
-      <c r="U12">
-        <v>310</v>
-      </c>
-      <c r="V12">
-        <v>310</v>
-      </c>
-      <c r="W12">
-        <v>310</v>
-      </c>
-      <c r="X12">
-        <v>310</v>
-      </c>
-      <c r="Y12">
-        <v>310</v>
-      </c>
-      <c r="Z12">
-        <v>310</v>
-      </c>
-      <c r="AA12">
-        <v>310</v>
-      </c>
-      <c r="AB12">
-        <v>310</v>
-      </c>
-      <c r="AC12">
-        <v>310</v>
-      </c>
-      <c r="AD12">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>62</v>
-      </c>
-      <c r="D13">
-        <v>74</v>
-      </c>
-      <c r="E13">
-        <v>76</v>
-      </c>
-      <c r="F13">
-        <v>64</v>
-      </c>
-      <c r="G13">
-        <v>72</v>
-      </c>
-      <c r="H13">
-        <v>76</v>
-      </c>
-      <c r="I13">
-        <v>79.5</v>
-      </c>
-      <c r="J13">
-        <v>81.5</v>
-      </c>
-      <c r="K13">
-        <v>77</v>
-      </c>
-      <c r="L13">
-        <v>81</v>
-      </c>
-      <c r="M13">
-        <v>74</v>
-      </c>
-      <c r="N13">
-        <v>68</v>
-      </c>
-      <c r="O13">
-        <v>74</v>
-      </c>
-      <c r="P13">
-        <v>77</v>
-      </c>
-      <c r="Q13">
-        <v>75</v>
-      </c>
-      <c r="R13">
-        <v>79</v>
-      </c>
-      <c r="S13">
-        <v>80</v>
-      </c>
-      <c r="T13">
-        <v>78</v>
-      </c>
-      <c r="U13">
-        <v>79</v>
-      </c>
-      <c r="V13">
-        <v>77</v>
-      </c>
-      <c r="W13">
-        <v>75.5</v>
-      </c>
-      <c r="X13">
-        <v>72</v>
-      </c>
-      <c r="Y13">
-        <v>61.5</v>
-      </c>
-      <c r="Z13">
-        <v>62.5</v>
-      </c>
-      <c r="AA13">
-        <v>54.5</v>
-      </c>
-      <c r="AB13">
-        <v>48</v>
-      </c>
-      <c r="AC13">
-        <v>38.5</v>
-      </c>
-      <c r="AD13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <f t="shared" ref="C15:AI15" si="2">C6*-SIN(RADIANS(C8))*C12/1000</f>
-        <v>-13.550199438030189</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="2"/>
-        <v>-12.715746326203965</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="2"/>
-        <v>-12.227450296743585</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="2"/>
-        <v>-13.574295183417183</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="2"/>
-        <v>-12.617833179689791</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="2"/>
-        <v>-11.427173303326315</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="2"/>
-        <v>-7.8289359826583684</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="2"/>
-        <v>-6.4962395866945686</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="2"/>
-        <v>-4.9404873370427511</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="2"/>
-        <v>-2.8261340010696823</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="2"/>
-        <v>-1.2108000422274927</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="2"/>
-        <v>-0.11021594724709009</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="2"/>
-        <v>-1.5137448723481624</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="2"/>
-        <v>-3.1927408242720881</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="2"/>
-        <v>-4.8615958230354943</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="2"/>
-        <v>-6.8694525901110115</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="2"/>
-        <v>-8.5997889837959107</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="2"/>
-        <v>-10.35823139969961</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="2"/>
-        <v>-11.863637901467659</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="2"/>
-        <v>-13.477555041999489</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="2"/>
-        <v>-13.77813076308844</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="2"/>
-        <v>-14.884597105183458</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="2"/>
-        <v>-14.534539473342328</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="2"/>
-        <v>-14.338144060893327</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="2"/>
-        <v>-14.021223986689929</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="2"/>
-        <v>-12.539046654783448</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="2"/>
-        <v>-11.167854768300959</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="2"/>
-        <v>-8.2836070695559112</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
-  <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>485</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <f>C2-C2*0.17</f>
-        <v>402.55</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>398</v>
-      </c>
-      <c r="L4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>P5+1</f>
-        <v>15</v>
-      </c>
-      <c r="R5" s="10">
-        <f>Q5+1</f>
-        <v>16</v>
-      </c>
-      <c r="S5" s="10">
-        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
-        <v>17</v>
-      </c>
-      <c r="T5" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="U5" s="10">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V5" s="10">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W5" s="10">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X5" s="10">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Z5" s="10">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA5" s="10">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="10">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AC5" s="10">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="AD5" s="10">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="AE5" s="10">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="AF5" s="10">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AG5" s="10">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="AH5" s="10">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="AI5" s="10">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>43.774000000000001</v>
-      </c>
-      <c r="D6">
-        <v>43.682000000000002</v>
-      </c>
-      <c r="E6">
-        <v>45.475000000000001</v>
-      </c>
-      <c r="F6">
-        <v>41.618000000000002</v>
-      </c>
-      <c r="G6">
-        <v>34.204000000000001</v>
-      </c>
-      <c r="H6">
-        <v>27.984999999999999</v>
-      </c>
-      <c r="I6">
-        <v>18.039000000000001</v>
-      </c>
-      <c r="J6">
-        <v>6.0835999999999997</v>
-      </c>
-      <c r="K6">
-        <v>2.9384000000000001</v>
-      </c>
-      <c r="L6">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="M6">
-        <v>7.3449999999999998</v>
-      </c>
-      <c r="N6">
-        <v>15.176</v>
-      </c>
-      <c r="O6">
-        <v>23.530999999999999</v>
-      </c>
-      <c r="P6">
-        <v>29.727</v>
-      </c>
-      <c r="Q6">
-        <v>38.637999999999998</v>
-      </c>
-      <c r="R6">
-        <v>46.064999999999998</v>
-      </c>
-      <c r="S6">
-        <v>50.881999999999998</v>
-      </c>
-      <c r="T6">
-        <v>53.805999999999997</v>
-      </c>
-      <c r="U6">
-        <v>53.527999999999999</v>
-      </c>
-      <c r="V6">
-        <v>48.012999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>5.5</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
-      </c>
-      <c r="F7">
-        <v>-15</v>
-      </c>
-      <c r="G7">
-        <v>-26.6</v>
-      </c>
-      <c r="H7">
-        <v>-35</v>
-      </c>
-      <c r="I7">
-        <v>-42.5</v>
-      </c>
-      <c r="J7">
-        <v>-56</v>
-      </c>
-      <c r="K7">
-        <v>-56</v>
-      </c>
-      <c r="L7">
-        <v>-63</v>
-      </c>
-      <c r="M7">
-        <v>-64</v>
-      </c>
-      <c r="N7">
-        <v>-55</v>
-      </c>
-      <c r="O7">
-        <v>-48</v>
-      </c>
-      <c r="P7">
-        <v>-42</v>
-      </c>
-      <c r="Q7">
-        <v>-35</v>
-      </c>
-      <c r="R7">
-        <v>-26</v>
-      </c>
-      <c r="S7">
-        <v>-19</v>
-      </c>
-      <c r="T7">
-        <v>-11</v>
-      </c>
-      <c r="U7">
-        <v>0.5</v>
-      </c>
-      <c r="V7">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>92.7</v>
-      </c>
-      <c r="D8" s="1">
-        <v>91</v>
-      </c>
-      <c r="E8" s="1">
-        <v>94.5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>93</v>
-      </c>
-      <c r="G8" s="1">
-        <v>95.6</v>
-      </c>
-      <c r="H8" s="1">
-        <v>94.1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>91.9</v>
-      </c>
-      <c r="J8" s="1">
-        <v>91.7</v>
-      </c>
-      <c r="K8" s="1">
-        <v>92.2</v>
-      </c>
-      <c r="L8" s="1">
-        <v>91.1</v>
-      </c>
-      <c r="M8" s="1">
-        <v>90</v>
-      </c>
-      <c r="N8" s="1">
-        <v>92.1</v>
-      </c>
-      <c r="O8" s="1">
-        <v>92.1</v>
-      </c>
-      <c r="P8" s="1">
-        <v>92.6</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>93.7</v>
-      </c>
-      <c r="R8" s="1">
-        <v>93.8</v>
-      </c>
-      <c r="S8" s="1">
-        <v>95.4</v>
-      </c>
-      <c r="T8" s="1">
-        <v>96.9</v>
-      </c>
-      <c r="U8" s="1">
-        <v>94.5</v>
-      </c>
-      <c r="V8" s="1">
-        <v>95.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>467</v>
-      </c>
-      <c r="D10">
-        <v>466</v>
-      </c>
-      <c r="E10">
-        <v>463</v>
-      </c>
-      <c r="F10">
-        <v>450</v>
-      </c>
-      <c r="G10">
-        <v>443</v>
-      </c>
-      <c r="H10">
-        <v>431</v>
-      </c>
-      <c r="I10">
-        <v>423</v>
-      </c>
-      <c r="J10">
-        <v>411</v>
-      </c>
-      <c r="K10">
-        <v>408</v>
-      </c>
-      <c r="L10">
-        <v>404</v>
-      </c>
-      <c r="M10">
-        <v>407</v>
-      </c>
-      <c r="N10">
-        <v>413</v>
-      </c>
-      <c r="O10">
-        <v>420</v>
-      </c>
-      <c r="P10">
-        <v>422</v>
-      </c>
-      <c r="Q10">
-        <v>433</v>
-      </c>
-      <c r="R10">
-        <v>442</v>
-      </c>
-      <c r="S10">
-        <v>448</v>
-      </c>
-      <c r="T10">
-        <v>455</v>
-      </c>
-      <c r="U10" s="2">
-        <v>460</v>
-      </c>
-      <c r="V10" s="2">
-        <v>466</v>
-      </c>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>275</v>
-      </c>
-      <c r="D12">
-        <v>275</v>
-      </c>
-      <c r="E12">
-        <v>275</v>
-      </c>
-      <c r="F12">
-        <v>275</v>
-      </c>
-      <c r="G12">
-        <v>275</v>
-      </c>
-      <c r="H12">
-        <v>275</v>
-      </c>
-      <c r="I12">
-        <v>275</v>
-      </c>
-      <c r="J12">
-        <v>275</v>
-      </c>
-      <c r="K12">
-        <v>275</v>
-      </c>
-      <c r="L12">
-        <v>275</v>
-      </c>
-      <c r="M12">
-        <v>275</v>
-      </c>
-      <c r="N12">
-        <v>275</v>
-      </c>
-      <c r="O12">
-        <v>275</v>
-      </c>
-      <c r="P12">
-        <v>275</v>
-      </c>
-      <c r="Q12">
-        <v>275</v>
-      </c>
-      <c r="R12">
-        <v>275</v>
-      </c>
-      <c r="S12">
-        <v>275</v>
-      </c>
-      <c r="T12">
-        <v>275</v>
-      </c>
-      <c r="U12">
-        <v>275</v>
-      </c>
-      <c r="V12">
-        <v>275</v>
-      </c>
-      <c r="W12">
-        <v>275</v>
-      </c>
-      <c r="X12">
-        <v>275</v>
-      </c>
-      <c r="Y12">
-        <v>275</v>
-      </c>
-      <c r="Z12">
-        <v>275</v>
-      </c>
-      <c r="AA12">
-        <v>275</v>
-      </c>
-      <c r="AB12">
-        <v>275</v>
-      </c>
-      <c r="AC12">
-        <v>275</v>
-      </c>
-      <c r="AD12">
-        <v>275</v>
-      </c>
-      <c r="AE12">
-        <v>275</v>
-      </c>
-      <c r="AF12">
-        <v>275</v>
-      </c>
-      <c r="AG12">
-        <v>275</v>
-      </c>
-      <c r="AH12">
-        <v>275</v>
-      </c>
-      <c r="AI12">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>45</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>55</v>
-      </c>
-      <c r="F13">
-        <v>65</v>
-      </c>
-      <c r="G13">
-        <v>70</v>
-      </c>
-      <c r="H13">
-        <v>74</v>
-      </c>
-      <c r="I13">
-        <v>73</v>
-      </c>
-      <c r="J13">
-        <v>72</v>
-      </c>
-      <c r="K13">
-        <v>65</v>
-      </c>
-      <c r="L13">
-        <v>63</v>
-      </c>
-      <c r="M13">
-        <v>66</v>
-      </c>
-      <c r="N13">
-        <v>71</v>
-      </c>
-      <c r="O13">
-        <v>75</v>
-      </c>
-      <c r="P13">
-        <v>75</v>
-      </c>
-      <c r="Q13">
-        <v>76</v>
-      </c>
-      <c r="R13">
-        <v>75</v>
-      </c>
-      <c r="S13">
-        <v>69</v>
-      </c>
-      <c r="T13">
-        <v>65</v>
-      </c>
-      <c r="U13">
-        <v>56</v>
-      </c>
-      <c r="V13">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
-        <v>-12.024486481310953</v>
-      </c>
-      <c r="D15">
-        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
-        <v>-12.010720430450908</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="1"/>
-        <v>-12.467074331666348</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>-11.429265093789359</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>-9.361208446969103</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>-7.6761795853386783</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>-4.9579976724776733</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>-1.6722536503811283</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>-0.80746439223476663</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>-3.5743411708348779E-3</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="1"/>
-        <v>-2.0198749999999999</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="1"/>
-        <v>-4.1705971185958441</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="1"/>
-        <v>-6.4666790193515293</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="1"/>
-        <v>-8.1665094852463582</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="1"/>
-        <v>-10.603302506170124</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="1"/>
-        <v>-12.640024275140153</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="1"/>
-        <v>-13.930450567806828</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>-14.689482923460329</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="1"/>
-        <v>-14.674822536018389</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="1"/>
-        <v>-13.151302910231001</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="L16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
-      <c r="R29">
-        <f>485*1.03</f>
-        <v>499.55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
-  <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>457</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <f>C2-C2*0.17</f>
-        <v>379.31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>P5+1</f>
-        <v>15</v>
-      </c>
-      <c r="R5" s="10">
-        <f>Q5+1</f>
-        <v>16</v>
-      </c>
-      <c r="S5" s="10">
-        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
-        <v>17</v>
-      </c>
-      <c r="T5" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="U5" s="10">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V5" s="10">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W5" s="10">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X5" s="10">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Z5" s="10">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA5" s="10">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="10">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AC5" s="10">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="AD5" s="10">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="AE5" s="10">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="AF5" s="10">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AG5" s="10">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="AH5" s="10">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="AI5" s="10">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>67.698999999999998</v>
-      </c>
-      <c r="D6">
-        <v>53.807000000000002</v>
-      </c>
-      <c r="E6">
-        <v>40.158999999999999</v>
-      </c>
-      <c r="F6">
-        <v>29.155000000000001</v>
-      </c>
-      <c r="G6">
-        <v>19.347000000000001</v>
-      </c>
-      <c r="H6">
-        <v>18.911000000000001</v>
-      </c>
-      <c r="I6">
-        <v>10.577</v>
-      </c>
-      <c r="J6">
-        <v>6.6810999999999998</v>
-      </c>
-      <c r="K6">
-        <v>3.8237000000000001</v>
-      </c>
-      <c r="L6">
-        <v>2.0994000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>-41</v>
-      </c>
-      <c r="D7">
-        <v>-45</v>
-      </c>
-      <c r="E7">
-        <v>-57</v>
-      </c>
-      <c r="F7">
-        <v>-63</v>
-      </c>
-      <c r="G7">
-        <v>-77</v>
-      </c>
-      <c r="H7">
-        <v>-75</v>
-      </c>
-      <c r="I7">
-        <v>-80</v>
-      </c>
-      <c r="J7">
-        <v>-90</v>
-      </c>
-      <c r="K7">
-        <v>-95</v>
-      </c>
-      <c r="L7">
-        <v>-105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>71.2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>75.3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>72.7</v>
-      </c>
-      <c r="F8" s="1">
-        <v>74.2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>81.599999999999994</v>
-      </c>
-      <c r="H8" s="1">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I8" s="1">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="J8" s="1">
-        <v>79.599999999999994</v>
-      </c>
-      <c r="K8" s="1">
-        <v>78</v>
-      </c>
-      <c r="L8" s="1">
-        <v>76.599999999999994</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>428</v>
-      </c>
-      <c r="D10">
-        <v>418</v>
-      </c>
-      <c r="E10">
-        <v>409.5</v>
-      </c>
-      <c r="F10">
-        <v>405.5</v>
-      </c>
-      <c r="G10">
-        <v>395</v>
-      </c>
-      <c r="H10">
-        <v>396</v>
-      </c>
-      <c r="I10">
-        <v>390</v>
-      </c>
-      <c r="J10">
-        <v>384</v>
-      </c>
-      <c r="K10">
-        <v>381</v>
-      </c>
-      <c r="L10">
-        <v>376</v>
-      </c>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
-      <c r="R10"/>
-      <c r="S10"/>
-      <c r="T10"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>275</v>
-      </c>
-      <c r="D12">
-        <v>275</v>
-      </c>
-      <c r="E12">
-        <v>275</v>
-      </c>
-      <c r="F12">
-        <v>275</v>
-      </c>
-      <c r="G12">
-        <v>275</v>
-      </c>
-      <c r="H12">
-        <v>275</v>
-      </c>
-      <c r="I12">
-        <v>275</v>
-      </c>
-      <c r="J12">
-        <v>275</v>
-      </c>
-      <c r="K12">
-        <v>275</v>
-      </c>
-      <c r="L12">
-        <v>275</v>
-      </c>
-      <c r="M12">
-        <v>275</v>
-      </c>
-      <c r="N12">
-        <v>275</v>
-      </c>
-      <c r="O12">
-        <v>275</v>
-      </c>
-      <c r="P12">
-        <v>275</v>
-      </c>
-      <c r="Q12">
-        <v>275</v>
-      </c>
-      <c r="R12">
-        <v>275</v>
-      </c>
-      <c r="S12">
-        <v>275</v>
-      </c>
-      <c r="T12">
-        <v>275</v>
-      </c>
-      <c r="U12">
-        <v>275</v>
-      </c>
-      <c r="V12">
-        <v>275</v>
-      </c>
-      <c r="W12">
-        <v>275</v>
-      </c>
-      <c r="X12">
-        <v>275</v>
-      </c>
-      <c r="Y12">
-        <v>275</v>
-      </c>
-      <c r="Z12">
-        <v>275</v>
-      </c>
-      <c r="AA12">
-        <v>275</v>
-      </c>
-      <c r="AB12">
-        <v>275</v>
-      </c>
-      <c r="AC12">
-        <v>275</v>
-      </c>
-      <c r="AD12">
-        <v>275</v>
-      </c>
-      <c r="AE12">
-        <v>275</v>
-      </c>
-      <c r="AF12">
-        <v>275</v>
-      </c>
-      <c r="AG12">
-        <v>275</v>
-      </c>
-      <c r="AH12">
-        <v>275</v>
-      </c>
-      <c r="AI12">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>80</v>
-      </c>
-      <c r="D13">
-        <v>81</v>
-      </c>
-      <c r="E13">
-        <v>78</v>
-      </c>
-      <c r="F13">
-        <v>76</v>
-      </c>
-      <c r="G13">
-        <v>62</v>
-      </c>
-      <c r="H13">
-        <v>62.5</v>
-      </c>
-      <c r="I13">
-        <v>60</v>
-      </c>
-      <c r="J13">
-        <v>48</v>
-      </c>
-      <c r="K13">
-        <v>34</v>
-      </c>
-      <c r="L13">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
-        <v>-17.623982271657447</v>
-      </c>
-      <c r="D15">
-        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
-        <v>-14.312588392743191</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="1"/>
-        <v>-10.544115710489031</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>-7.714703040370237</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>-5.2633492521046072</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>-5.0482353303594207</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>-2.8329795466253955</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>-1.807118322254111</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>-1.0285393197546095</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>-0.56161756164602195</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="10:18" x14ac:dyDescent="0.35">
-      <c r="J18">
-        <f>1-348/457</f>
-        <v>0.23851203501094087</v>
-      </c>
-    </row>
-    <row r="29" spans="10:18" x14ac:dyDescent="0.35">
-      <c r="R29">
-        <f>485*1.03</f>
-        <v>499.55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B26E4-CFF3-41E2-8721-B0918FFC9B0E}">
-  <dimension ref="A1:AK36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="3"/>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2">
-        <v>479</v>
-      </c>
-      <c r="E2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3">
-        <v>413</v>
-      </c>
-      <c r="D3">
-        <f>(C3/C2)</f>
-        <v>0.86221294363256784</v>
-      </c>
-      <c r="E3">
-        <f>1-D3</f>
-        <v>0.13778705636743216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" t="s">
-        <v>81</v>
-      </c>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A5" s="10"/>
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="20">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>15</v>
-      </c>
-      <c r="R5" s="10">
-        <v>16</v>
-      </c>
-      <c r="S5" s="10">
-        <v>17</v>
-      </c>
-      <c r="T5" s="10">
-        <v>18</v>
-      </c>
-      <c r="U5" s="10">
-        <v>19</v>
-      </c>
-      <c r="V5" s="10">
-        <v>20</v>
-      </c>
-      <c r="W5" s="10">
-        <v>21</v>
-      </c>
-      <c r="X5" s="10">
-        <v>22</v>
-      </c>
-      <c r="Y5" s="10">
-        <v>23</v>
-      </c>
-      <c r="Z5" s="10">
-        <v>24</v>
-      </c>
-      <c r="AA5" s="10">
-        <v>25</v>
-      </c>
-      <c r="AB5" s="10">
-        <v>26</v>
-      </c>
-      <c r="AC5" s="10">
-        <v>27</v>
-      </c>
-      <c r="AD5" s="10">
-        <v>28</v>
-      </c>
-      <c r="AE5" s="10">
-        <v>29</v>
-      </c>
-      <c r="AF5" s="10"/>
-      <c r="AG5" s="10"/>
-      <c r="AH5" s="10"/>
-      <c r="AI5" s="10"/>
-      <c r="AJ5" s="10"/>
-      <c r="AK5" s="10"/>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="16">
-        <v>7.6539999999999999</v>
-      </c>
-      <c r="D6">
-        <v>16.346</v>
-      </c>
-      <c r="E6">
-        <v>28.263000000000002</v>
-      </c>
-      <c r="F6">
-        <v>41.6</v>
-      </c>
-      <c r="G6">
-        <v>53.704999999999998</v>
-      </c>
-      <c r="H6">
-        <v>59.472000000000001</v>
-      </c>
-      <c r="I6">
-        <v>63.2</v>
-      </c>
-      <c r="J6">
-        <v>65.655000000000001</v>
-      </c>
-      <c r="K6">
-        <v>76.481999999999999</v>
-      </c>
-      <c r="L6">
-        <v>68.266999999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="16">
-        <v>-68.718999999999994</v>
-      </c>
-      <c r="D7">
-        <v>-61.898000000000003</v>
-      </c>
-      <c r="E7">
-        <v>-54.359000000000002</v>
-      </c>
-      <c r="F7">
-        <v>-46.460999999999999</v>
-      </c>
-      <c r="G7">
-        <v>-38.204000000000001</v>
-      </c>
-      <c r="H7">
-        <v>-32.100999999999999</v>
-      </c>
-      <c r="I7">
-        <v>-27.8</v>
-      </c>
-      <c r="J7">
-        <v>-24.202999999999999</v>
-      </c>
-      <c r="K7">
-        <v>-9.125</v>
-      </c>
-      <c r="L7">
-        <v>-21.331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="16">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="D8">
-        <v>623.60699999999997</v>
-      </c>
-      <c r="E8">
-        <v>622.85</v>
-      </c>
-      <c r="F8">
-        <v>622.85</v>
-      </c>
-      <c r="G8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="H8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="I8">
-        <v>623.60699999999997</v>
-      </c>
-      <c r="J8">
-        <v>622.85</v>
-      </c>
-      <c r="K8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="L8">
-        <v>621.36500000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="15">
-        <v>82</v>
-      </c>
-      <c r="D9" s="1">
-        <v>86</v>
-      </c>
-      <c r="E9" s="1">
-        <v>84.5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>98.5</v>
-      </c>
-      <c r="G9" s="1">
-        <v>87</v>
-      </c>
-      <c r="H9" s="1">
-        <v>86</v>
-      </c>
-      <c r="I9" s="1">
-        <v>85</v>
-      </c>
-      <c r="J9" s="1">
-        <v>83</v>
-      </c>
-      <c r="K9" s="1">
-        <v>56</v>
-      </c>
-      <c r="L9" s="1">
-        <v>56</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="1"/>
-      <c r="AI9" s="1"/>
-      <c r="AJ9" s="1"/>
-      <c r="AK9" s="1"/>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="16">
-        <v>408</v>
-      </c>
-      <c r="D10">
+      <c r="O10" s="33">
         <v>410</v>
-      </c>
-      <c r="E10">
-        <v>421</v>
-      </c>
-      <c r="F10">
-        <v>427</v>
-      </c>
-      <c r="G10">
-        <v>437</v>
-      </c>
-      <c r="H10">
-        <v>441</v>
-      </c>
-      <c r="I10">
-        <v>444</v>
-      </c>
-      <c r="J10">
-        <v>447</v>
-      </c>
-      <c r="K10">
-        <v>456</v>
-      </c>
-      <c r="L10">
-        <v>446</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.35">
@@ -27189,34 +24145,44 @@
         <v>11</v>
       </c>
       <c r="C14" s="16">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E14">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F14">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="G14">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="H14">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I14">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="J14">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="K14">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="L14">
-        <v>76</v>
+        <f>510-475</f>
+        <v>35</v>
+      </c>
+      <c r="M14">
+        <v>32</v>
+      </c>
+      <c r="N14">
+        <v>30</v>
+      </c>
+      <c r="O14">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
@@ -27266,6 +24232,3204 @@
         <v>6</v>
       </c>
       <c r="C16" s="16">
+        <f>C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
+        <v>0.17716929126497558</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:AE16" si="0">D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
+        <v>0.23580983133155201</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>0.31887857721722329</v>
+      </c>
+      <c r="F16" s="16">
+        <f>F6*SIN(RADIANS(F9+5.15))*F13/1000</f>
+        <v>0.72357994775830636</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>0.89299667946631711</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>1.9413384783051184</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>2.4204380693667997</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>2.7329938745931397</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="0"/>
+        <v>2.898194169907315</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="0"/>
+        <v>2.9622838327028997</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>3.0909599773855079</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="0"/>
+        <v>3.5556114225204913</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="0"/>
+        <v>3.8508462486362252</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
+  <dimension ref="A1:AJ15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>485</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <f>C2-C2*0.17</f>
+        <v>402.55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <f>P5+1</f>
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <f>Q5+1</f>
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <f t="shared" ref="S5:AB5" si="0">R5+1</f>
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <f t="shared" ref="AC5:AI5" si="1">AB5+1</f>
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AG5" s="10">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="AH5" s="10">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="AI5" s="10">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>51.203000000000003</v>
+      </c>
+      <c r="D6">
+        <v>48.398000000000003</v>
+      </c>
+      <c r="E6">
+        <v>46.283999999999999</v>
+      </c>
+      <c r="F6">
+        <v>49.966000000000001</v>
+      </c>
+      <c r="G6">
+        <v>46.258000000000003</v>
+      </c>
+      <c r="H6">
+        <v>42.865000000000002</v>
+      </c>
+      <c r="I6">
+        <v>28.888999999999999</v>
+      </c>
+      <c r="J6">
+        <v>24.26</v>
+      </c>
+      <c r="K6">
+        <v>18.155999999999999</v>
+      </c>
+      <c r="L6">
+        <v>10.234</v>
+      </c>
+      <c r="M6">
+        <v>4.266</v>
+      </c>
+      <c r="N6">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="O6">
+        <v>5.4537000000000004</v>
+      </c>
+      <c r="P6">
+        <v>11.362</v>
+      </c>
+      <c r="Q6">
+        <v>17.478000000000002</v>
+      </c>
+      <c r="R6">
+        <v>24.577000000000002</v>
+      </c>
+      <c r="S6">
+        <v>31.812999999999999</v>
+      </c>
+      <c r="T6">
+        <v>37.369</v>
+      </c>
+      <c r="U6">
+        <v>42.365000000000002</v>
+      </c>
+      <c r="V6">
+        <v>47.408000000000001</v>
+      </c>
+      <c r="W6">
+        <v>50.768000000000001</v>
+      </c>
+      <c r="X6">
+        <v>53.197000000000003</v>
+      </c>
+      <c r="Y6">
+        <v>52.39</v>
+      </c>
+      <c r="Z6">
+        <v>52.238999999999997</v>
+      </c>
+      <c r="AA6">
+        <v>50.945</v>
+      </c>
+      <c r="AB6">
+        <v>46.247</v>
+      </c>
+      <c r="AC6">
+        <v>39.781999999999996</v>
+      </c>
+      <c r="AD6">
+        <v>30.405999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>-5.5</v>
+      </c>
+      <c r="D7">
+        <v>-10.5</v>
+      </c>
+      <c r="E7">
+        <v>-25.5</v>
+      </c>
+      <c r="F7">
+        <v>-4.5</v>
+      </c>
+      <c r="G7">
+        <v>-14.5</v>
+      </c>
+      <c r="H7">
+        <v>-20</v>
+      </c>
+      <c r="I7">
+        <v>-33</v>
+      </c>
+      <c r="J7">
+        <v>-39.5</v>
+      </c>
+      <c r="K7">
+        <v>-43</v>
+      </c>
+      <c r="L7">
+        <v>-50</v>
+      </c>
+      <c r="M7">
+        <v>-62.5</v>
+      </c>
+      <c r="N7">
+        <v>-60</v>
+      </c>
+      <c r="O7">
+        <v>-55</v>
+      </c>
+      <c r="P7">
+        <v>-53.5</v>
+      </c>
+      <c r="Q7">
+        <v>-46</v>
+      </c>
+      <c r="R7">
+        <v>-40</v>
+      </c>
+      <c r="S7">
+        <v>-36.5</v>
+      </c>
+      <c r="T7">
+        <v>-33.5</v>
+      </c>
+      <c r="U7">
+        <v>-29.5</v>
+      </c>
+      <c r="V7">
+        <v>-24.5</v>
+      </c>
+      <c r="W7">
+        <v>-17.5</v>
+      </c>
+      <c r="X7">
+        <v>-14.5</v>
+      </c>
+      <c r="Y7">
+        <v>-5.5</v>
+      </c>
+      <c r="Z7">
+        <v>-3</v>
+      </c>
+      <c r="AA7">
+        <v>-0.5</v>
+      </c>
+      <c r="AB7">
+        <v>3.5</v>
+      </c>
+      <c r="AC7">
+        <v>11.5</v>
+      </c>
+      <c r="AD7">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>87</v>
+      </c>
+      <c r="D8" s="1">
+        <v>82.5</v>
+      </c>
+      <c r="E8" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>115.1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>114.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>117.3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>115.4</v>
+      </c>
+      <c r="J8" s="1">
+        <v>116.8</v>
+      </c>
+      <c r="K8" s="1">
+        <v>114.9</v>
+      </c>
+      <c r="L8" s="1">
+        <v>113</v>
+      </c>
+      <c r="M8" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="N8" s="1">
+        <v>110.8</v>
+      </c>
+      <c r="O8" s="1">
+        <v>112.3</v>
+      </c>
+      <c r="P8" s="1">
+        <v>110.5</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>112</v>
+      </c>
+      <c r="R8" s="1">
+        <v>111.3</v>
+      </c>
+      <c r="S8" s="1">
+        <v>115.7</v>
+      </c>
+      <c r="T8" s="1">
+        <v>116.6</v>
+      </c>
+      <c r="U8" s="1">
+        <v>115.4</v>
+      </c>
+      <c r="V8" s="1">
+        <v>113.5</v>
+      </c>
+      <c r="W8" s="1">
+        <v>118.9</v>
+      </c>
+      <c r="X8" s="1">
+        <v>115.5</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>116.5</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>117.7</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>117.4</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>119</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>115.1</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>461.5</v>
+      </c>
+      <c r="D10">
+        <v>456</v>
+      </c>
+      <c r="E10">
+        <v>450.5</v>
+      </c>
+      <c r="F10">
+        <v>460.5</v>
+      </c>
+      <c r="G10">
+        <v>452</v>
+      </c>
+      <c r="H10">
+        <v>449</v>
+      </c>
+      <c r="I10">
+        <v>432</v>
+      </c>
+      <c r="J10">
+        <v>428</v>
+      </c>
+      <c r="K10">
+        <v>423</v>
+      </c>
+      <c r="L10">
+        <v>415</v>
+      </c>
+      <c r="M10">
+        <v>409.5</v>
+      </c>
+      <c r="N10">
+        <v>406</v>
+      </c>
+      <c r="O10">
+        <v>410</v>
+      </c>
+      <c r="P10">
+        <v>414.5</v>
+      </c>
+      <c r="Q10">
+        <v>420.5</v>
+      </c>
+      <c r="R10">
+        <v>426</v>
+      </c>
+      <c r="S10">
+        <v>430</v>
+      </c>
+      <c r="T10">
+        <v>433.5</v>
+      </c>
+      <c r="U10" s="2">
+        <v>441</v>
+      </c>
+      <c r="V10" s="2">
+        <v>445</v>
+      </c>
+      <c r="W10" s="2">
+        <v>451</v>
+      </c>
+      <c r="X10" s="2">
+        <v>454</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>455.5</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>458.5</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>462</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>461.5</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>465</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>467</v>
+      </c>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>265</v>
+      </c>
+      <c r="D12">
+        <v>265</v>
+      </c>
+      <c r="E12">
+        <v>265</v>
+      </c>
+      <c r="F12">
+        <v>300</v>
+      </c>
+      <c r="G12">
+        <v>300</v>
+      </c>
+      <c r="H12">
+        <v>300</v>
+      </c>
+      <c r="I12">
+        <v>300</v>
+      </c>
+      <c r="J12">
+        <v>300</v>
+      </c>
+      <c r="K12">
+        <v>300</v>
+      </c>
+      <c r="L12">
+        <v>300</v>
+      </c>
+      <c r="M12">
+        <v>300</v>
+      </c>
+      <c r="N12">
+        <v>300</v>
+      </c>
+      <c r="O12">
+        <v>300</v>
+      </c>
+      <c r="P12">
+        <v>300</v>
+      </c>
+      <c r="Q12">
+        <v>300</v>
+      </c>
+      <c r="R12">
+        <v>300</v>
+      </c>
+      <c r="S12">
+        <v>300</v>
+      </c>
+      <c r="T12">
+        <v>310</v>
+      </c>
+      <c r="U12">
+        <v>310</v>
+      </c>
+      <c r="V12">
+        <v>310</v>
+      </c>
+      <c r="W12">
+        <v>310</v>
+      </c>
+      <c r="X12">
+        <v>310</v>
+      </c>
+      <c r="Y12">
+        <v>310</v>
+      </c>
+      <c r="Z12">
+        <v>310</v>
+      </c>
+      <c r="AA12">
+        <v>310</v>
+      </c>
+      <c r="AB12">
+        <v>310</v>
+      </c>
+      <c r="AC12">
+        <v>310</v>
+      </c>
+      <c r="AD12">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>62</v>
+      </c>
+      <c r="D13">
+        <v>74</v>
+      </c>
+      <c r="E13">
+        <v>76</v>
+      </c>
+      <c r="F13">
+        <v>64</v>
+      </c>
+      <c r="G13">
+        <v>72</v>
+      </c>
+      <c r="H13">
+        <v>76</v>
+      </c>
+      <c r="I13">
+        <v>79.5</v>
+      </c>
+      <c r="J13">
+        <v>81.5</v>
+      </c>
+      <c r="K13">
+        <v>77</v>
+      </c>
+      <c r="L13">
+        <v>81</v>
+      </c>
+      <c r="M13">
+        <v>74</v>
+      </c>
+      <c r="N13">
+        <v>68</v>
+      </c>
+      <c r="O13">
+        <v>74</v>
+      </c>
+      <c r="P13">
+        <v>77</v>
+      </c>
+      <c r="Q13">
+        <v>75</v>
+      </c>
+      <c r="R13">
+        <v>79</v>
+      </c>
+      <c r="S13">
+        <v>80</v>
+      </c>
+      <c r="T13">
+        <v>78</v>
+      </c>
+      <c r="U13">
+        <v>79</v>
+      </c>
+      <c r="V13">
+        <v>77</v>
+      </c>
+      <c r="W13">
+        <v>75.5</v>
+      </c>
+      <c r="X13">
+        <v>72</v>
+      </c>
+      <c r="Y13">
+        <v>61.5</v>
+      </c>
+      <c r="Z13">
+        <v>62.5</v>
+      </c>
+      <c r="AA13">
+        <v>54.5</v>
+      </c>
+      <c r="AB13">
+        <v>48</v>
+      </c>
+      <c r="AC13">
+        <v>38.5</v>
+      </c>
+      <c r="AD13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:AI15" si="2">C6*-SIN(RADIANS(C8))*C12/1000</f>
+        <v>-13.550199438030189</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>-12.715746326203965</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>-12.227450296743585</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>-13.574295183417183</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>-12.617833179689791</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>-11.427173303326315</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>-7.8289359826583684</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="2"/>
+        <v>-6.4962395866945686</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>-4.9404873370427511</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>-2.8261340010696823</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="2"/>
+        <v>-1.2108000422274927</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="2"/>
+        <v>-0.11021594724709009</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="2"/>
+        <v>-1.5137448723481624</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="2"/>
+        <v>-3.1927408242720881</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="2"/>
+        <v>-4.8615958230354943</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="2"/>
+        <v>-6.8694525901110115</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="2"/>
+        <v>-8.5997889837959107</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="2"/>
+        <v>-10.35823139969961</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="2"/>
+        <v>-11.863637901467659</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="2"/>
+        <v>-13.477555041999489</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="2"/>
+        <v>-13.77813076308844</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="2"/>
+        <v>-14.884597105183458</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="2"/>
+        <v>-14.534539473342328</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="2"/>
+        <v>-14.338144060893327</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="2"/>
+        <v>-14.021223986689929</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="2"/>
+        <v>-12.539046654783448</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="2"/>
+        <v>-11.167854768300959</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="2"/>
+        <v>-8.2836070695559112</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
+  <dimension ref="A1:AJ29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>485</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <f>C2-C2*0.17</f>
+        <v>402.55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>398</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <f>P5+1</f>
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <f>Q5+1</f>
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AG5" s="10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AH5" s="10">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="AI5" s="10">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>43.774000000000001</v>
+      </c>
+      <c r="D6">
+        <v>43.682000000000002</v>
+      </c>
+      <c r="E6">
+        <v>45.475000000000001</v>
+      </c>
+      <c r="F6">
+        <v>41.618000000000002</v>
+      </c>
+      <c r="G6">
+        <v>34.204000000000001</v>
+      </c>
+      <c r="H6">
+        <v>27.984999999999999</v>
+      </c>
+      <c r="I6">
+        <v>18.039000000000001</v>
+      </c>
+      <c r="J6">
+        <v>6.0835999999999997</v>
+      </c>
+      <c r="K6">
+        <v>2.9384000000000001</v>
+      </c>
+      <c r="L6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="M6">
+        <v>7.3449999999999998</v>
+      </c>
+      <c r="N6">
+        <v>15.176</v>
+      </c>
+      <c r="O6">
+        <v>23.530999999999999</v>
+      </c>
+      <c r="P6">
+        <v>29.727</v>
+      </c>
+      <c r="Q6">
+        <v>38.637999999999998</v>
+      </c>
+      <c r="R6">
+        <v>46.064999999999998</v>
+      </c>
+      <c r="S6">
+        <v>50.881999999999998</v>
+      </c>
+      <c r="T6">
+        <v>53.805999999999997</v>
+      </c>
+      <c r="U6">
+        <v>53.527999999999999</v>
+      </c>
+      <c r="V6">
+        <v>48.012999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>5.5</v>
+      </c>
+      <c r="E7">
+        <v>-1</v>
+      </c>
+      <c r="F7">
+        <v>-15</v>
+      </c>
+      <c r="G7">
+        <v>-26.6</v>
+      </c>
+      <c r="H7">
+        <v>-35</v>
+      </c>
+      <c r="I7">
+        <v>-42.5</v>
+      </c>
+      <c r="J7">
+        <v>-56</v>
+      </c>
+      <c r="K7">
+        <v>-56</v>
+      </c>
+      <c r="L7">
+        <v>-63</v>
+      </c>
+      <c r="M7">
+        <v>-64</v>
+      </c>
+      <c r="N7">
+        <v>-55</v>
+      </c>
+      <c r="O7">
+        <v>-48</v>
+      </c>
+      <c r="P7">
+        <v>-42</v>
+      </c>
+      <c r="Q7">
+        <v>-35</v>
+      </c>
+      <c r="R7">
+        <v>-26</v>
+      </c>
+      <c r="S7">
+        <v>-19</v>
+      </c>
+      <c r="T7">
+        <v>-11</v>
+      </c>
+      <c r="U7">
+        <v>0.5</v>
+      </c>
+      <c r="V7">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>92.7</v>
+      </c>
+      <c r="D8" s="1">
+        <v>91</v>
+      </c>
+      <c r="E8" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>93</v>
+      </c>
+      <c r="G8" s="1">
+        <v>95.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>94.1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>91.9</v>
+      </c>
+      <c r="J8" s="1">
+        <v>91.7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>92.2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>91.1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>90</v>
+      </c>
+      <c r="N8" s="1">
+        <v>92.1</v>
+      </c>
+      <c r="O8" s="1">
+        <v>92.1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>92.6</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>93.7</v>
+      </c>
+      <c r="R8" s="1">
+        <v>93.8</v>
+      </c>
+      <c r="S8" s="1">
+        <v>95.4</v>
+      </c>
+      <c r="T8" s="1">
+        <v>96.9</v>
+      </c>
+      <c r="U8" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="V8" s="1">
+        <v>95.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>467</v>
+      </c>
+      <c r="D10">
+        <v>466</v>
+      </c>
+      <c r="E10">
+        <v>463</v>
+      </c>
+      <c r="F10">
+        <v>450</v>
+      </c>
+      <c r="G10">
+        <v>443</v>
+      </c>
+      <c r="H10">
+        <v>431</v>
+      </c>
+      <c r="I10">
+        <v>423</v>
+      </c>
+      <c r="J10">
+        <v>411</v>
+      </c>
+      <c r="K10">
+        <v>408</v>
+      </c>
+      <c r="L10">
+        <v>404</v>
+      </c>
+      <c r="M10">
+        <v>407</v>
+      </c>
+      <c r="N10">
+        <v>413</v>
+      </c>
+      <c r="O10">
+        <v>420</v>
+      </c>
+      <c r="P10">
+        <v>422</v>
+      </c>
+      <c r="Q10">
+        <v>433</v>
+      </c>
+      <c r="R10">
+        <v>442</v>
+      </c>
+      <c r="S10">
+        <v>448</v>
+      </c>
+      <c r="T10">
+        <v>455</v>
+      </c>
+      <c r="U10" s="2">
+        <v>460</v>
+      </c>
+      <c r="V10" s="2">
+        <v>466</v>
+      </c>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>275</v>
+      </c>
+      <c r="D12">
+        <v>275</v>
+      </c>
+      <c r="E12">
+        <v>275</v>
+      </c>
+      <c r="F12">
+        <v>275</v>
+      </c>
+      <c r="G12">
+        <v>275</v>
+      </c>
+      <c r="H12">
+        <v>275</v>
+      </c>
+      <c r="I12">
+        <v>275</v>
+      </c>
+      <c r="J12">
+        <v>275</v>
+      </c>
+      <c r="K12">
+        <v>275</v>
+      </c>
+      <c r="L12">
+        <v>275</v>
+      </c>
+      <c r="M12">
+        <v>275</v>
+      </c>
+      <c r="N12">
+        <v>275</v>
+      </c>
+      <c r="O12">
+        <v>275</v>
+      </c>
+      <c r="P12">
+        <v>275</v>
+      </c>
+      <c r="Q12">
+        <v>275</v>
+      </c>
+      <c r="R12">
+        <v>275</v>
+      </c>
+      <c r="S12">
+        <v>275</v>
+      </c>
+      <c r="T12">
+        <v>275</v>
+      </c>
+      <c r="U12">
+        <v>275</v>
+      </c>
+      <c r="V12">
+        <v>275</v>
+      </c>
+      <c r="W12">
+        <v>275</v>
+      </c>
+      <c r="X12">
+        <v>275</v>
+      </c>
+      <c r="Y12">
+        <v>275</v>
+      </c>
+      <c r="Z12">
+        <v>275</v>
+      </c>
+      <c r="AA12">
+        <v>275</v>
+      </c>
+      <c r="AB12">
+        <v>275</v>
+      </c>
+      <c r="AC12">
+        <v>275</v>
+      </c>
+      <c r="AD12">
+        <v>275</v>
+      </c>
+      <c r="AE12">
+        <v>275</v>
+      </c>
+      <c r="AF12">
+        <v>275</v>
+      </c>
+      <c r="AG12">
+        <v>275</v>
+      </c>
+      <c r="AH12">
+        <v>275</v>
+      </c>
+      <c r="AI12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>45</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>55</v>
+      </c>
+      <c r="F13">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>70</v>
+      </c>
+      <c r="H13">
+        <v>74</v>
+      </c>
+      <c r="I13">
+        <v>73</v>
+      </c>
+      <c r="J13">
+        <v>72</v>
+      </c>
+      <c r="K13">
+        <v>65</v>
+      </c>
+      <c r="L13">
+        <v>63</v>
+      </c>
+      <c r="M13">
+        <v>66</v>
+      </c>
+      <c r="N13">
+        <v>71</v>
+      </c>
+      <c r="O13">
+        <v>75</v>
+      </c>
+      <c r="P13">
+        <v>75</v>
+      </c>
+      <c r="Q13">
+        <v>76</v>
+      </c>
+      <c r="R13">
+        <v>75</v>
+      </c>
+      <c r="S13">
+        <v>69</v>
+      </c>
+      <c r="T13">
+        <v>65</v>
+      </c>
+      <c r="U13">
+        <v>56</v>
+      </c>
+      <c r="V13">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
+        <v>-12.024486481310953</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
+        <v>-12.010720430450908</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>-12.467074331666348</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>-11.429265093789359</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>-9.361208446969103</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>-7.6761795853386783</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>-4.9579976724776733</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>-1.6722536503811283</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>-0.80746439223476663</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>-3.5743411708348779E-3</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="1"/>
+        <v>-2.0198749999999999</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>-4.1705971185958441</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="1"/>
+        <v>-6.4666790193515293</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>-8.1665094852463582</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="1"/>
+        <v>-10.603302506170124</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>-12.640024275140153</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>-13.930450567806828</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="1"/>
+        <v>-14.689482923460329</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="1"/>
+        <v>-14.674822536018389</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="1"/>
+        <v>-13.151302910231001</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
+      <c r="R29">
+        <f>485*1.03</f>
+        <v>499.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
+  <dimension ref="A1:AJ29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>457</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <f>C2-C2*0.17</f>
+        <v>379.31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <f>P5+1</f>
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <f>Q5+1</f>
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AG5" s="10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AH5" s="10">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="AI5" s="10">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>67.698999999999998</v>
+      </c>
+      <c r="D6">
+        <v>53.807000000000002</v>
+      </c>
+      <c r="E6">
+        <v>40.158999999999999</v>
+      </c>
+      <c r="F6">
+        <v>29.155000000000001</v>
+      </c>
+      <c r="G6">
+        <v>19.347000000000001</v>
+      </c>
+      <c r="H6">
+        <v>18.911000000000001</v>
+      </c>
+      <c r="I6">
+        <v>10.577</v>
+      </c>
+      <c r="J6">
+        <v>6.6810999999999998</v>
+      </c>
+      <c r="K6">
+        <v>3.8237000000000001</v>
+      </c>
+      <c r="L6">
+        <v>2.0994000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>-41</v>
+      </c>
+      <c r="D7">
+        <v>-45</v>
+      </c>
+      <c r="E7">
+        <v>-57</v>
+      </c>
+      <c r="F7">
+        <v>-63</v>
+      </c>
+      <c r="G7">
+        <v>-77</v>
+      </c>
+      <c r="H7">
+        <v>-75</v>
+      </c>
+      <c r="I7">
+        <v>-80</v>
+      </c>
+      <c r="J7">
+        <v>-90</v>
+      </c>
+      <c r="K7">
+        <v>-95</v>
+      </c>
+      <c r="L7">
+        <v>-105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>71.2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>75.3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>72.7</v>
+      </c>
+      <c r="F8" s="1">
+        <v>74.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="H8" s="1">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I8" s="1">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="J8" s="1">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="K8" s="1">
+        <v>78</v>
+      </c>
+      <c r="L8" s="1">
+        <v>76.599999999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>428</v>
+      </c>
+      <c r="D10">
+        <v>418</v>
+      </c>
+      <c r="E10">
+        <v>409.5</v>
+      </c>
+      <c r="F10">
+        <v>405.5</v>
+      </c>
+      <c r="G10">
+        <v>395</v>
+      </c>
+      <c r="H10">
+        <v>396</v>
+      </c>
+      <c r="I10">
+        <v>390</v>
+      </c>
+      <c r="J10">
+        <v>384</v>
+      </c>
+      <c r="K10">
+        <v>381</v>
+      </c>
+      <c r="L10">
+        <v>376</v>
+      </c>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>275</v>
+      </c>
+      <c r="D12">
+        <v>275</v>
+      </c>
+      <c r="E12">
+        <v>275</v>
+      </c>
+      <c r="F12">
+        <v>275</v>
+      </c>
+      <c r="G12">
+        <v>275</v>
+      </c>
+      <c r="H12">
+        <v>275</v>
+      </c>
+      <c r="I12">
+        <v>275</v>
+      </c>
+      <c r="J12">
+        <v>275</v>
+      </c>
+      <c r="K12">
+        <v>275</v>
+      </c>
+      <c r="L12">
+        <v>275</v>
+      </c>
+      <c r="M12">
+        <v>275</v>
+      </c>
+      <c r="N12">
+        <v>275</v>
+      </c>
+      <c r="O12">
+        <v>275</v>
+      </c>
+      <c r="P12">
+        <v>275</v>
+      </c>
+      <c r="Q12">
+        <v>275</v>
+      </c>
+      <c r="R12">
+        <v>275</v>
+      </c>
+      <c r="S12">
+        <v>275</v>
+      </c>
+      <c r="T12">
+        <v>275</v>
+      </c>
+      <c r="U12">
+        <v>275</v>
+      </c>
+      <c r="V12">
+        <v>275</v>
+      </c>
+      <c r="W12">
+        <v>275</v>
+      </c>
+      <c r="X12">
+        <v>275</v>
+      </c>
+      <c r="Y12">
+        <v>275</v>
+      </c>
+      <c r="Z12">
+        <v>275</v>
+      </c>
+      <c r="AA12">
+        <v>275</v>
+      </c>
+      <c r="AB12">
+        <v>275</v>
+      </c>
+      <c r="AC12">
+        <v>275</v>
+      </c>
+      <c r="AD12">
+        <v>275</v>
+      </c>
+      <c r="AE12">
+        <v>275</v>
+      </c>
+      <c r="AF12">
+        <v>275</v>
+      </c>
+      <c r="AG12">
+        <v>275</v>
+      </c>
+      <c r="AH12">
+        <v>275</v>
+      </c>
+      <c r="AI12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>80</v>
+      </c>
+      <c r="D13">
+        <v>81</v>
+      </c>
+      <c r="E13">
+        <v>78</v>
+      </c>
+      <c r="F13">
+        <v>76</v>
+      </c>
+      <c r="G13">
+        <v>62</v>
+      </c>
+      <c r="H13">
+        <v>62.5</v>
+      </c>
+      <c r="I13">
+        <v>60</v>
+      </c>
+      <c r="J13">
+        <v>48</v>
+      </c>
+      <c r="K13">
+        <v>34</v>
+      </c>
+      <c r="L13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
+        <v>-17.623982271657447</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
+        <v>-14.312588392743191</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>-10.544115710489031</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>-7.714703040370237</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>-5.2633492521046072</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>-5.0482353303594207</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>-2.8329795466253955</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>-1.807118322254111</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>-1.0285393197546095</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>-0.56161756164602195</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="10:18" x14ac:dyDescent="0.35">
+      <c r="J18">
+        <f>1-348/457</f>
+        <v>0.23851203501094087</v>
+      </c>
+    </row>
+    <row r="29" spans="10:18" x14ac:dyDescent="0.35">
+      <c r="R29">
+        <f>485*1.03</f>
+        <v>499.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B26E4-CFF3-41E2-8721-B0918FFC9B0E}">
+  <dimension ref="A1:AK36"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2">
+        <v>479</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3">
+        <v>413</v>
+      </c>
+      <c r="D3">
+        <f>(C3/C2)</f>
+        <v>0.86221294363256784</v>
+      </c>
+      <c r="E3">
+        <f>1-D3</f>
+        <v>0.13778705636743216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A5" s="10"/>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>7.6539999999999999</v>
+      </c>
+      <c r="D6">
+        <v>16.346</v>
+      </c>
+      <c r="E6">
+        <v>28.263000000000002</v>
+      </c>
+      <c r="F6">
+        <v>41.6</v>
+      </c>
+      <c r="G6">
+        <v>53.704999999999998</v>
+      </c>
+      <c r="H6">
+        <v>59.472000000000001</v>
+      </c>
+      <c r="I6">
+        <v>63.2</v>
+      </c>
+      <c r="J6">
+        <v>65.655000000000001</v>
+      </c>
+      <c r="K6">
+        <v>76.481999999999999</v>
+      </c>
+      <c r="L6">
+        <v>68.266999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="16">
+        <v>-68.718999999999994</v>
+      </c>
+      <c r="D7">
+        <v>-61.898000000000003</v>
+      </c>
+      <c r="E7">
+        <v>-54.359000000000002</v>
+      </c>
+      <c r="F7">
+        <v>-46.460999999999999</v>
+      </c>
+      <c r="G7">
+        <v>-38.204000000000001</v>
+      </c>
+      <c r="H7">
+        <v>-32.100999999999999</v>
+      </c>
+      <c r="I7">
+        <v>-27.8</v>
+      </c>
+      <c r="J7">
+        <v>-24.202999999999999</v>
+      </c>
+      <c r="K7">
+        <v>-9.125</v>
+      </c>
+      <c r="L7">
+        <v>-21.331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="D8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="E8">
+        <v>622.85</v>
+      </c>
+      <c r="F8">
+        <v>622.85</v>
+      </c>
+      <c r="G8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="H8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="I8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="J8">
+        <v>622.85</v>
+      </c>
+      <c r="K8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="L8">
+        <v>621.36500000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="15">
+        <v>82</v>
+      </c>
+      <c r="D9" s="1">
+        <v>86</v>
+      </c>
+      <c r="E9" s="1">
+        <v>84.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>98.5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>87</v>
+      </c>
+      <c r="H9" s="1">
+        <v>86</v>
+      </c>
+      <c r="I9" s="1">
+        <v>85</v>
+      </c>
+      <c r="J9" s="1">
+        <v>83</v>
+      </c>
+      <c r="K9" s="1">
+        <v>56</v>
+      </c>
+      <c r="L9" s="1">
+        <v>56</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16">
+        <v>408</v>
+      </c>
+      <c r="D10">
+        <v>410</v>
+      </c>
+      <c r="E10">
+        <v>421</v>
+      </c>
+      <c r="F10">
+        <v>427</v>
+      </c>
+      <c r="G10">
+        <v>437</v>
+      </c>
+      <c r="H10">
+        <v>441</v>
+      </c>
+      <c r="I10">
+        <v>444</v>
+      </c>
+      <c r="J10">
+        <v>447</v>
+      </c>
+      <c r="K10">
+        <v>456</v>
+      </c>
+      <c r="L10">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="16">
+        <v>249.71</v>
+      </c>
+      <c r="D13">
+        <v>249.71</v>
+      </c>
+      <c r="E13">
+        <v>249.71</v>
+      </c>
+      <c r="F13">
+        <v>249.71</v>
+      </c>
+      <c r="G13">
+        <v>249.71</v>
+      </c>
+      <c r="H13">
+        <v>249.71</v>
+      </c>
+      <c r="I13">
+        <v>249.71</v>
+      </c>
+      <c r="J13">
+        <v>249.71</v>
+      </c>
+      <c r="K13">
+        <v>249.71</v>
+      </c>
+      <c r="L13">
+        <v>249.71</v>
+      </c>
+      <c r="M13">
+        <v>249.71</v>
+      </c>
+      <c r="N13">
+        <v>249.71</v>
+      </c>
+      <c r="O13">
+        <v>249.71</v>
+      </c>
+      <c r="P13">
+        <v>249.71</v>
+      </c>
+      <c r="Q13">
+        <v>249.71</v>
+      </c>
+      <c r="R13">
+        <v>249.71</v>
+      </c>
+      <c r="S13">
+        <v>249.71</v>
+      </c>
+      <c r="T13">
+        <v>249.71</v>
+      </c>
+      <c r="U13">
+        <v>249.71</v>
+      </c>
+      <c r="V13">
+        <v>249.71</v>
+      </c>
+      <c r="W13">
+        <v>249.71</v>
+      </c>
+      <c r="X13">
+        <v>249.71</v>
+      </c>
+      <c r="Y13">
+        <v>249.71</v>
+      </c>
+      <c r="Z13">
+        <v>249.71</v>
+      </c>
+      <c r="AA13">
+        <v>249.71</v>
+      </c>
+      <c r="AB13">
+        <v>249.71</v>
+      </c>
+      <c r="AC13">
+        <v>249.71</v>
+      </c>
+      <c r="AD13">
+        <v>249.71</v>
+      </c>
+      <c r="AE13">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16">
+        <v>62</v>
+      </c>
+      <c r="D14">
+        <v>71</v>
+      </c>
+      <c r="E14">
+        <v>72</v>
+      </c>
+      <c r="F14">
+        <v>82</v>
+      </c>
+      <c r="G14">
+        <v>82</v>
+      </c>
+      <c r="H14">
+        <v>80</v>
+      </c>
+      <c r="I14">
+        <v>79</v>
+      </c>
+      <c r="J14">
+        <v>77</v>
+      </c>
+      <c r="K14">
+        <v>67</v>
+      </c>
+      <c r="L14">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="16">
         <f>-C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
         <v>-1.9089163300292105</v>
       </c>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C53A715-A518-499E-84CF-594F33F4204D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A3E813-9C1F-4DCB-941F-46896A883EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41085" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="11" activeTab="12" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
@@ -349,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="87">
   <si>
     <t>Test #</t>
   </si>
@@ -604,6 +604,12 @@
   </si>
   <si>
     <t>Ext Test 12</t>
+  </si>
+  <si>
+    <t>* Pretensioned to 0.935 N</t>
+  </si>
+  <si>
+    <t>* Pretensioned to 0.975 N</t>
   </si>
 </sst>
 </file>
@@ -3098,10 +3104,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>ExtTest10mm_13!$C$7:$S$7</c:f>
+              <c:f>ExtTest10mm_13!$C$7:$AE$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>23.184999999999999</c:v>
                 </c:pt>
@@ -3140,6 +3146,45 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-55.795000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-60.820999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-67.641999999999996</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-73.385999999999996</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-84.156000000000006</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-90.259</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-75.180999999999997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-65.846999999999994</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-51.487000000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-33.896000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-17.023</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-4.0990000000000002</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.3120000000000003</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>16.004999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3190,43 +3235,43 @@
                   <c:v>3.8508462486362252</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>3.6291506505175044</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>4.1829161707816302</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>4.4642414453654187</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>5.3517587170964296</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>5.5243356546689117</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>4.6434882022501975</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>3.9337462112650874</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>3.2362035092330919</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>2.4284517189520791</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>1.7953494471509861</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>0.66240942939085234</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>0.27714759903786063</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>0.23872194191046633</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -23598,6 +23643,8 @@
     <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
@@ -23791,6 +23838,45 @@
       <c r="O6">
         <v>15.651999999999999</v>
       </c>
+      <c r="P6">
+        <v>14.798</v>
+      </c>
+      <c r="Q6">
+        <v>17.056000000000001</v>
+      </c>
+      <c r="R6">
+        <v>18.266999999999999</v>
+      </c>
+      <c r="S6">
+        <v>21.821999999999999</v>
+      </c>
+      <c r="T6">
+        <v>22.454000000000001</v>
+      </c>
+      <c r="U6">
+        <v>18.934000000000001</v>
+      </c>
+      <c r="V6">
+        <v>16.04</v>
+      </c>
+      <c r="W6">
+        <v>13.116</v>
+      </c>
+      <c r="X6">
+        <v>9.7759999999999998</v>
+      </c>
+      <c r="Y6">
+        <v>7.2060000000000004</v>
+      </c>
+      <c r="Z6">
+        <v>2.6560000000000001</v>
+      </c>
+      <c r="AA6">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AB6">
+        <v>0.95599999999999996</v>
+      </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
@@ -23836,6 +23922,45 @@
       <c r="O7">
         <v>-55.795000000000002</v>
       </c>
+      <c r="P7">
+        <v>-60.820999999999998</v>
+      </c>
+      <c r="Q7">
+        <v>-67.641999999999996</v>
+      </c>
+      <c r="R7">
+        <v>-73.385999999999996</v>
+      </c>
+      <c r="S7">
+        <v>-84.156000000000006</v>
+      </c>
+      <c r="T7">
+        <v>-90.259</v>
+      </c>
+      <c r="U7">
+        <v>-75.180999999999997</v>
+      </c>
+      <c r="V7">
+        <v>-65.846999999999994</v>
+      </c>
+      <c r="W7">
+        <v>-51.487000000000002</v>
+      </c>
+      <c r="X7">
+        <v>-33.896000000000001</v>
+      </c>
+      <c r="Y7">
+        <v>-17.023</v>
+      </c>
+      <c r="Z7">
+        <v>-4.0990000000000002</v>
+      </c>
+      <c r="AA7">
+        <v>6.3120000000000003</v>
+      </c>
+      <c r="AB7">
+        <v>16.004999999999999</v>
+      </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
@@ -23881,6 +24006,45 @@
       <c r="O8">
         <v>622.85</v>
       </c>
+      <c r="P8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="Q8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="R8">
+        <v>622.096</v>
+      </c>
+      <c r="S8">
+        <v>620.57899999999995</v>
+      </c>
+      <c r="T8">
+        <v>622.85</v>
+      </c>
+      <c r="U8">
+        <v>623.85</v>
+      </c>
+      <c r="V8">
+        <v>622.85</v>
+      </c>
+      <c r="W8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="X8">
+        <v>622.09299999999996</v>
+      </c>
+      <c r="Y8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="Z8">
+        <v>622.85</v>
+      </c>
+      <c r="AA8">
+        <v>622.09299999999996</v>
+      </c>
+      <c r="AB8">
+        <v>621.33600000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
@@ -23928,19 +24092,45 @@
       <c r="O9" s="1">
         <v>75</v>
       </c>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
+      <c r="P9" s="1">
+        <v>74</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>74</v>
+      </c>
+      <c r="R9" s="1">
+        <v>73</v>
+      </c>
+      <c r="S9" s="1">
+        <v>74</v>
+      </c>
+      <c r="T9" s="1">
+        <v>75</v>
+      </c>
+      <c r="U9" s="1">
+        <v>74</v>
+      </c>
+      <c r="V9" s="1">
+        <v>74</v>
+      </c>
+      <c r="W9" s="1">
+        <v>76</v>
+      </c>
+      <c r="X9" s="1">
+        <v>79</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>81</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>82</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>84</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>85</v>
+      </c>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
@@ -23959,41 +24149,80 @@
       <c r="C10" s="16">
         <v>404</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10">
         <v>398</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10">
         <v>393</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10">
         <v>393</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10">
         <v>390</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10">
         <v>394</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10">
         <v>397</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10">
         <v>399</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10">
         <v>400</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10">
         <v>404</v>
       </c>
-      <c r="M10" s="33">
+      <c r="M10">
         <v>407</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10">
         <v>410</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10">
         <v>410</v>
+      </c>
+      <c r="P10" s="33">
+        <v>414</v>
+      </c>
+      <c r="Q10" s="33">
+        <v>415</v>
+      </c>
+      <c r="R10" s="33">
+        <v>416</v>
+      </c>
+      <c r="S10" s="33">
+        <v>423</v>
+      </c>
+      <c r="T10" s="33">
+        <v>424</v>
+      </c>
+      <c r="U10" s="33">
+        <v>418</v>
+      </c>
+      <c r="V10" s="33">
+        <v>417</v>
+      </c>
+      <c r="W10" s="33">
+        <v>410</v>
+      </c>
+      <c r="X10" s="33">
+        <v>404</v>
+      </c>
+      <c r="Y10" s="33">
+        <v>396</v>
+      </c>
+      <c r="Z10" s="33">
+        <v>387</v>
+      </c>
+      <c r="AA10" s="33">
+        <v>388</v>
+      </c>
+      <c r="AB10" s="33">
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.35">
@@ -24184,6 +24413,45 @@
       <c r="O14">
         <v>30</v>
       </c>
+      <c r="P14">
+        <v>28</v>
+      </c>
+      <c r="Q14">
+        <v>28</v>
+      </c>
+      <c r="R14">
+        <v>28</v>
+      </c>
+      <c r="S14">
+        <v>28</v>
+      </c>
+      <c r="T14">
+        <v>27</v>
+      </c>
+      <c r="U14">
+        <v>30</v>
+      </c>
+      <c r="V14">
+        <v>29</v>
+      </c>
+      <c r="W14">
+        <v>33</v>
+      </c>
+      <c r="X14">
+        <v>37</v>
+      </c>
+      <c r="Y14">
+        <v>44</v>
+      </c>
+      <c r="Z14">
+        <v>50</v>
+      </c>
+      <c r="AA14">
+        <v>59</v>
+      </c>
+      <c r="AB14">
+        <v>72</v>
+      </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
@@ -24285,138 +24553,144 @@
       </c>
       <c r="P16" s="16">
         <f t="shared" si="0"/>
+        <v>3.6291506505175044</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>4.1829161707816302</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>4.4642414453654187</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>5.3517587170964296</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>5.5243356546689117</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>4.6434882022501975</v>
+      </c>
+      <c r="V16" s="16">
+        <f>V6*SIN(RADIANS(V9+5.15))*V13/1000</f>
+        <v>3.9337462112650874</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>3.2362035092330919</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>2.4284517189520791</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>1.7953494471509861</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>0.66240942939085234</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0.27714759903786063</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0.23872194191046633</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="AD16" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R16" s="16">
+      <c r="AE16" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="S17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="29" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
     </row>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A3E813-9C1F-4DCB-941F-46896A883EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FF203A-7CD3-4B49-94A4-E0C6A4A9F528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41085" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="11" activeTab="12" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="16" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -25,11 +25,12 @@
     <sheet name="ExtTest10mm_10" sheetId="20" r:id="rId10"/>
     <sheet name="ExtTest10mm_11" sheetId="21" r:id="rId11"/>
     <sheet name="ExtTest10mm_12" sheetId="22" r:id="rId12"/>
-    <sheet name="ExtTest10mm_13" sheetId="24" r:id="rId13"/>
+    <sheet name="ExtTest10mm_13" sheetId="25" r:id="rId13"/>
     <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId14"/>
     <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId15"/>
     <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId16"/>
     <sheet name="FlxTest10mm_4" sheetId="23" r:id="rId17"/>
+    <sheet name="FlxTest10mm_5" sheetId="24" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -243,14 +244,14 @@
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={A0F37F35-3C02-4428-95DF-F39F668FABAB}</author>
-    <author>tc={B330029E-0838-474A-A917-D75DCA8B89DE}</author>
-    <author>tc={54C76319-676A-40FF-BA34-557807290B63}</author>
-    <author>tc={3503805A-53F9-44E7-B5DE-1E572B8A5B05}</author>
-    <author>tc={1C8E06FF-9847-46B8-831A-746E2073BD30}</author>
+    <author>tc={EDD4A2EB-AC41-41F5-AEBA-BA83D6D066BB}</author>
+    <author>tc={E30E01B8-EB61-46FD-9E73-DB8665781EAE}</author>
+    <author>tc={FBA43358-59F0-4FFB-BDC7-3AEDE0ADFC53}</author>
+    <author>tc={29559212-EFFD-4F4F-810E-B5C644E22194}</author>
+    <author>tc={09557C74-D39F-48D9-9B0F-33C529B18E89}</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{A0F37F35-3C02-4428-95DF-F39F668FABAB}">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{EDD4A2EB-AC41-41F5-AEBA-BA83D6D066BB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -258,7 +259,7 @@
     Recheck after test</t>
       </text>
     </comment>
-    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{B330029E-0838-474A-A917-D75DCA8B89DE}">
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{E30E01B8-EB61-46FD-9E73-DB8665781EAE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -266,7 +267,7 @@
     Recheck after test</t>
       </text>
     </comment>
-    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{54C76319-676A-40FF-BA34-557807290B63}">
+    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{FBA43358-59F0-4FFB-BDC7-3AEDE0ADFC53}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -274,7 +275,7 @@
     Max contracted length normalized by resting length</t>
       </text>
     </comment>
-    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{3503805A-53F9-44E7-B5DE-1E572B8A5B05}">
+    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{29559212-EFFD-4F4F-810E-B5C644E22194}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -282,7 +283,7 @@
     Kmax</t>
       </text>
     </comment>
-    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{1C8E06FF-9847-46B8-831A-746E2073BD30}">
+    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{09557C74-D39F-48D9-9B0F-33C529B18E89}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -348,8 +349,62 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={1412A674-61A3-4D66-9D3E-5374366576D7}</author>
+    <author>tc={7BAEFA08-D790-466D-A190-320CBA26570E}</author>
+    <author>tc={E1852E19-B84C-463E-A0CB-BF0ADA1DC1BE}</author>
+    <author>tc={13B25287-2F50-4E04-AC48-02AB262B1DE9}</author>
+    <author>tc={50243B4E-1A69-4602-BC70-D861CF3BE17E}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{1412A674-61A3-4D66-9D3E-5374366576D7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{7BAEFA08-D790-466D-A190-320CBA26570E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{E1852E19-B84C-463E-A0CB-BF0ADA1DC1BE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Max contracted length normalized by resting length</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{13B25287-2F50-4E04-AC48-02AB262B1DE9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kmax</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{50243B4E-1A69-4602-BC70-D861CF3BE17E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="105">
   <si>
     <t>Test #</t>
   </si>
@@ -594,16 +649,55 @@
     <t>^Collected by Moe &amp; Ben</t>
   </si>
   <si>
-    <t>*pretension 9.50N</t>
+    <t>Flex test 5</t>
   </si>
   <si>
-    <t>v</t>
+    <t>*4 N pretension</t>
+  </si>
+  <si>
+    <t>*/**</t>
+  </si>
+  <si>
+    <t>**noticed tendon is actually 35 mm. Possible plastic deformation or incorrect initial measurement.</t>
+  </si>
+  <si>
+    <t>tendon 37 mm under load</t>
+  </si>
+  <si>
+    <t>****</t>
+  </si>
+  <si>
+    <t>5 N pretension, Lm = 406</t>
+  </si>
+  <si>
+    <t>11.43N pretension</t>
+  </si>
+  <si>
+    <t>tendon 38mm</t>
+  </si>
+  <si>
+    <t>18.7 N pretension</t>
+  </si>
+  <si>
+    <t>tendon 39mm</t>
+  </si>
+  <si>
+    <t>23.5 N pretension</t>
+  </si>
+  <si>
+    <t>avg pressure</t>
+  </si>
+  <si>
+    <t>Average pressure</t>
+  </si>
+  <si>
+    <t>Noticed that bracket was shifting under higher loads.</t>
+  </si>
+  <si>
+    <t>Bracket failed material pull out.</t>
   </si>
   <si>
     <t>Ext Test 13</t>
-  </si>
-  <si>
-    <t>Ext Test 12</t>
   </si>
   <si>
     <t>* Pretensioned to 0.935 N</t>
@@ -611,12 +705,27 @@
   <si>
     <t>* Pretensioned to 0.975 N</t>
   </si>
+  <si>
+    <t>Ext Test 12</t>
+  </si>
+  <si>
+    <t>min length test</t>
+  </si>
+  <si>
+    <t>min length (test)</t>
+  </si>
+  <si>
+    <t>max length test</t>
+  </si>
+  <si>
+    <t>max length (test)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -659,8 +768,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -681,12 +796,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,7 +945,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -867,10 +976,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1044,123 +1150,7 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.60346456692913386"/>
-                  <c:y val="-0.28313193524076818"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="3"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.40464027934008251"/>
-                  <c:y val="-1.2615056781268678E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="log"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="5"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
@@ -1240,7 +1230,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>0.26363819717520748</c:v>
+                  <c:v>4.6268503604248918</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4.503204045949718</c:v>
@@ -2635,7 +2625,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>ExtTest10mm_12!$D$7:$S$7</c:f>
+              <c:f>ExtTest10mm_12!$C$7:$R$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -2692,7 +2682,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ExtTest10mm_12!$D$16:$AB$16</c:f>
+              <c:f>ExtTest10mm_12!$C$16:$AA$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
@@ -2982,6 +2972,36 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -2991,6 +3011,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>result</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -3104,10 +3127,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>ExtTest10mm_13!$C$7:$AE$7</c:f>
+              <c:f>ExtTest10mm_13!$C$7:$R$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>23.184999999999999</c:v>
                 </c:pt>
@@ -3155,46 +3178,16 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>-73.385999999999996</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-84.156000000000006</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-90.259</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-75.180999999999997</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-65.846999999999994</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-51.487000000000002</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-33.896000000000001</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-17.023</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-4.0990000000000002</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>6.3120000000000003</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>16.004999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ExtTest10mm_13!$C$16:$AB$16</c:f>
+              <c:f>ExtTest10mm_13!$C$16:$AA$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.17716929126497558</c:v>
                 </c:pt>
@@ -3269,9 +3262,6 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.27714759903786063</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.23872194191046633</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3279,7 +3269,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-DE63-4F26-BE26-45C392EB0915}"/>
+              <c16:uniqueId val="{00000002-5481-4BFF-B721-CA615FBF0E12}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3484,79 +3474,9 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Flexor 10mm</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Knee Torque</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.4158344861650378E-2"/>
-          <c:y val="0.17072497123130037"/>
-          <c:w val="0.91627572927286405"/>
-          <c:h val="0.77864211737629463"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -3564,7 +3484,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:noFill/>
               <a:round/>
             </a:ln>
@@ -3595,44 +3515,10 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="log"/>
             <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.60346456692913386"/>
-                  <c:y val="-0.28313193524076818"/>
-                </c:manualLayout>
-              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -3673,31 +3559,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="log"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="poly"/>
             <c:order val="3"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.27899278215223094"/>
-                  <c:y val="0.3201971535736251"/>
-                </c:manualLayout>
-              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -3730,201 +3596,174 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
+              <c:f>ExtTest10mm_13!$C$7:$AE$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>-5.5</c:v>
+                  <c:v>23.184999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10.5</c:v>
+                  <c:v>17.440999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-25.5</c:v>
+                  <c:v>9.1839999999999993</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.5</c:v>
+                  <c:v>2.004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-14.5</c:v>
+                  <c:v>-4.8170000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-20</c:v>
+                  <c:v>-10.561</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-33</c:v>
+                  <c:v>-16.305</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-39.5</c:v>
+                  <c:v>-21.331</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-43</c:v>
+                  <c:v>-26.356999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-50</c:v>
+                  <c:v>-32.46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-62.5</c:v>
+                  <c:v>-40.716999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-60</c:v>
+                  <c:v>-50.051000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-55</c:v>
+                  <c:v>-55.795000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-53.5</c:v>
+                  <c:v>-60.820999999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-46</c:v>
+                  <c:v>-67.641999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-40</c:v>
+                  <c:v>-73.385999999999996</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-36.5</c:v>
+                  <c:v>-84.156000000000006</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-33.5</c:v>
+                  <c:v>-90.259</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-29.5</c:v>
+                  <c:v>-75.180999999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-24.5</c:v>
+                  <c:v>-65.846999999999994</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-17.5</c:v>
+                  <c:v>-51.487000000000002</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-14.5</c:v>
+                  <c:v>-33.896000000000001</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-5.5</c:v>
+                  <c:v>-17.023</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-3</c:v>
+                  <c:v>-4.0990000000000002</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-0.5</c:v>
+                  <c:v>6.3120000000000003</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>11.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>19.5</c:v>
+                  <c:v>16.004999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
+              <c:f>ExtTest10mm_13!$C$16:$AB$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>-13.550199438030189</c:v>
+                  <c:v>0.17716929126497558</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.715746326203965</c:v>
+                  <c:v>0.23580983133155201</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-12.227450296743585</c:v>
+                  <c:v>0.31887857721722329</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-13.574295183417183</c:v>
+                  <c:v>0.72357994775830636</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-12.617833179689791</c:v>
+                  <c:v>0.89299667946631711</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11.427173303326315</c:v>
+                  <c:v>1.9413384783051184</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-7.8289359826583684</c:v>
+                  <c:v>2.4204380693667997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-6.4962395866945686</c:v>
+                  <c:v>2.7329938745931397</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-4.9404873370427511</c:v>
+                  <c:v>2.898194169907315</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.8261340010696823</c:v>
+                  <c:v>2.9622838327028997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.2108000422274927</c:v>
+                  <c:v>3.0909599773855079</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.11021594724709009</c:v>
+                  <c:v>3.5556114225204913</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.5137448723481624</c:v>
+                  <c:v>3.8508462486362252</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-3.1927408242720881</c:v>
+                  <c:v>3.6291506505175044</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-4.8615958230354943</c:v>
+                  <c:v>4.1829161707816302</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-6.8694525901110115</c:v>
+                  <c:v>4.4642414453654187</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-8.5997889837959107</c:v>
+                  <c:v>5.3517587170964296</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-10.35823139969961</c:v>
+                  <c:v>5.5243356546689117</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-11.863637901467659</c:v>
+                  <c:v>4.6434882022501975</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-13.477555041999489</c:v>
+                  <c:v>3.9337462112650874</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-13.77813076308844</c:v>
+                  <c:v>3.2362035092330919</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-14.884597105183458</c:v>
+                  <c:v>2.4284517189520791</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-14.534539473342328</c:v>
+                  <c:v>1.7953494471509861</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-14.338144060893327</c:v>
+                  <c:v>0.66240942939085234</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-14.021223986689929</c:v>
+                  <c:v>0.27714759903786063</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-12.539046654783448</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>-11.167854768300959</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>-8.2836070695559112</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
+                  <c:v>0.23872194191046633</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3932,7 +3771,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
+              <c16:uniqueId val="{00000002-F984-4DF4-A620-B2C7DC507809}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3944,11 +3783,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1394438799"/>
-        <c:axId val="1190584639"/>
+        <c:axId val="1567646591"/>
+        <c:axId val="1566330175"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1394438799"/>
+        <c:axId val="1567646591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4005,12 +3844,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1190584639"/>
+        <c:crossAx val="1566330175"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1190584639"/>
+        <c:axId val="1566330175"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4067,7 +3906,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1394438799"/>
+        <c:crossAx val="1567646591"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4347,8 +4186,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.40762374401637524"/>
-                  <c:y val="4.5584595515824444E-2"/>
+                  <c:x val="-0.27899278215223094"/>
+                  <c:y val="0.3201971535736251"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -4383,162 +4222,186 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest10mm_2!$C$7:$AI$7</c:f>
+              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>-5.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>-10.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1</c:v>
+                  <c:v>-25.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-15</c:v>
+                  <c:v>-4.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-26.6</c:v>
+                  <c:v>-14.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-35</c:v>
+                  <c:v>-20</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-42.5</c:v>
+                  <c:v>-33</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-56</c:v>
+                  <c:v>-39.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-56</c:v>
+                  <c:v>-43</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-63</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-64</c:v>
+                  <c:v>-62.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>-60</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>-55</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>-48</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>-42</c:v>
+                  <c:v>-53.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-35</c:v>
+                  <c:v>-46</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-26</c:v>
+                  <c:v>-40</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-19</c:v>
+                  <c:v>-36.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-11</c:v>
+                  <c:v>-33.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.5</c:v>
+                  <c:v>-29.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>-24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-17.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-14.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>19.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest10mm_2!$C$15:$AI$15</c:f>
+              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>-12.024486481310953</c:v>
+                  <c:v>-13.550199438030189</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.010720430450908</c:v>
+                  <c:v>-12.715746326203965</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-12.467074331666348</c:v>
+                  <c:v>-12.227450296743585</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-11.429265093789359</c:v>
+                  <c:v>-13.574295183417183</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-9.361208446969103</c:v>
+                  <c:v>-12.617833179689791</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-7.6761795853386783</c:v>
+                  <c:v>-11.427173303326315</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-4.9579976724776733</c:v>
+                  <c:v>-7.8289359826583684</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.6722536503811283</c:v>
+                  <c:v>-6.4962395866945686</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.80746439223476663</c:v>
+                  <c:v>-4.9404873370427511</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-3.5743411708348779E-3</c:v>
+                  <c:v>-2.8261340010696823</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2.0198749999999999</c:v>
+                  <c:v>-1.2108000422274927</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-4.1705971185958441</c:v>
+                  <c:v>-0.11021594724709009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-6.4666790193515293</c:v>
+                  <c:v>-1.5137448723481624</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-8.1665094852463582</c:v>
+                  <c:v>-3.1927408242720881</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-10.603302506170124</c:v>
+                  <c:v>-4.8615958230354943</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-12.640024275140153</c:v>
+                  <c:v>-6.8694525901110115</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-13.930450567806828</c:v>
+                  <c:v>-8.5997889837959107</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-14.689482923460329</c:v>
+                  <c:v>-10.35823139969961</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-14.674822536018389</c:v>
+                  <c:v>-11.863637901467659</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-13.151302910231001</c:v>
+                  <c:v>-13.477555041999489</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>-13.77813076308844</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>-14.884597105183458</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>-14.534539473342328</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>-14.338144060893327</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>-14.021223986689929</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>-12.539046654783448</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>-11.167854768300959</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0</c:v>
+                  <c:v>-8.2836070695559112</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -4561,7 +4424,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-9D05-4463-B8B4-EFE1AE46B75E}"/>
+              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4767,6 +4630,635 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Flexor 10mm</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Knee Torque</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.4158344861650378E-2"/>
+          <c:y val="0.17072497123130037"/>
+          <c:w val="0.91627572927286405"/>
+          <c:h val="0.77864211737629463"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="power"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.60346456692913386"/>
+                  <c:y val="-0.28313193524076818"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.40762374401637524"/>
+                  <c:y val="4.5584595515824444E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_2!$C$7:$AI$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-26.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-42.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-56</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-56</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-64</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-55</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-48</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-42</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-35</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-26</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-19</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_2!$C$15:$AI$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>-12.024486481310953</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-12.010720430450908</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-12.467074331666348</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-11.429265093789359</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-9.361208446969103</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-7.6761795853386783</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.9579976724776733</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.6722536503811283</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.80746439223476663</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-3.5743411708348779E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-2.0198749999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-4.1705971185958441</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-6.4666790193515293</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-8.1665094852463582</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-10.603302506170124</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-12.640024275140153</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-13.930450567806828</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-14.689482923460329</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-14.674822536018389</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-13.151302910231001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-9D05-4463-B8B4-EFE1AE46B75E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1394438799"/>
+        <c:axId val="1190584639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1394438799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1190584639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1190584639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1394438799"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5200,7 +5692,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5285,42 +5777,100 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="poly"/>
             <c:order val="3"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.0034120734908135E-2"/>
+                  <c:y val="-0.32664344174194992"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>y = 0.0001x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="30000">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>3</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t> + 0.024x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="30000">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>2</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t> + 0.9144x - 5.9593</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>R² = 0.9885</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </c:rich>
+              </c:tx>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:noFill/>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
                 <a:ln>
                   <a:noFill/>
                 </a:ln>
@@ -5333,10 +5883,7 @@
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
+                        <a:schemeClr val="bg1"/>
                       </a:solidFill>
                       <a:latin typeface="+mn-lt"/>
                       <a:ea typeface="+mn-ea"/>
@@ -5379,10 +5926,34 @@
                   <c:v>-24.202999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-9.125</c:v>
+                  <c:v>-25.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-21.331</c:v>
+                  <c:v>-16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-20.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-70.81</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-53.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-39.280999999999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-29.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-16.3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-10.199999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5394,58 +5965,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>-1.9089163300292105</c:v>
+                  <c:v>-1.9888446022622024</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-4.0809375058192954</c:v>
+                  <c:v>-4.2527956349925518</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-7.0574220518637798</c:v>
+                  <c:v>-7.3539886035989408</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-10.09453321766197</c:v>
+                  <c:v>-10.527409285407064</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-13.401234911810583</c:v>
+                  <c:v>-13.966402193997661</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-14.847761858930939</c:v>
+                  <c:v>-15.473036951197667</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-15.781617917093591</c:v>
+                  <c:v>-16.445267992387105</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-16.386164614410578</c:v>
+                  <c:v>-17.07325998043143</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-16.727950101680829</c:v>
+                  <c:v>-14.697192119709124</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-14.931186025358189</c:v>
+                  <c:v>-15.358895091501429</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>-15.042937875530633</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>-0.56433407059449248</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>-2.4445410159422072</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>-5.2402184740344895</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>-10.95843156495609</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>-13.902438921694182</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>-16.846155017276384</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>-9.9320795468220986</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -5466,6 +6037,480 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-CE28-4152-9B9D-F4BE9A57F41C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1604021071"/>
+        <c:axId val="1604018671"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1604021071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604018671"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1604018671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604021071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.21909860469440826"/>
+                  <c:y val="1.901586316257094E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_5!$C$7:$AE$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>-113.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-102</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-94.207999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-87.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-80.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-112.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-102.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-92</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-86</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-77.694000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-70.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-65.129000000000005</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-60.462000000000003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-50.768999999999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-45.74</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-40.716999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-34.972999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-29.228999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_5!$C$16:$X$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>-4.9109379769919088E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.83403244093913598</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.7200073984477242</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.900103689581238</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.5474653742290858</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-18.319240363209158</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.14749659592534689</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.77675624770615737</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1.8437074490668364</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.9228908759206247</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-5.0559532620861303</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-7.5053908133297975</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-10.014296277159817</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-12.137120802638771</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-16.328074980556799</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-18.009994411252876</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-19.562355739823911</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-20.200690671447745</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-19.951096115672847</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8ECD-4C0F-A506-F9E8935F6B6D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10065,6 +11110,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors18.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors19.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -15029,6 +16154,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style19.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -19347,7 +21504,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8654B586-951D-46F4-A8A5-47D952B66B32}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8785E2B1-AD7C-4F3D-8ACA-E05BF9DD0DFB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19367,6 +21524,44 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>329710</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>108439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1340825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>41276</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB34F374-DD15-4C88-9542-E5D6B2DBF67D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -19374,16 +21569,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>740833</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>7937</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>672253</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>68897</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>131233</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>36512</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>496993</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>97472</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -19417,16 +21612,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>74612</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>112712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>331258</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>277918</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -19538,6 +21733,49 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>49770</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>8515</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>329917</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>40264</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58E722E8-FDD3-4A7B-AD3B-C615A565B17C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -19585,16 +21823,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>740833</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>7937</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>363643</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>86042</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>131233</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>36512</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>868468</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>112712</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -19672,15 +21910,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>895350</xdr:colOff>
+      <xdr:colOff>643890</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -19712,16 +21950,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>338137</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>517207</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>80962</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>111442</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -19753,16 +21991,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>338137</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>677694</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>60169</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>80962</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>702891</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>136369</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20252,19 +22490,19 @@
 
 <file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{A0F37F35-3C02-4428-95DF-F39F668FABAB}">
+  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{EDD4A2EB-AC41-41F5-AEBA-BA83D6D066BB}">
     <text>Recheck after test</text>
   </threadedComment>
-  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{B330029E-0838-474A-A917-D75DCA8B89DE}">
+  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{E30E01B8-EB61-46FD-9E73-DB8665781EAE}">
     <text>Recheck after test</text>
   </threadedComment>
-  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{54C76319-676A-40FF-BA34-557807290B63}">
+  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{FBA43358-59F0-4FFB-BDC7-3AEDE0ADFC53}">
     <text>Max contracted length normalized by resting length</text>
   </threadedComment>
-  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{3503805A-53F9-44E7-B5DE-1E572B8A5B05}">
+  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{29559212-EFFD-4F4F-810E-B5C644E22194}">
     <text>Kmax</text>
   </threadedComment>
-  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{1C8E06FF-9847-46B8-831A-746E2073BD30}">
+  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{09557C74-D39F-48D9-9B0F-33C529B18E89}">
     <text>So it can reach -114 degrees</text>
   </threadedComment>
 </ThreadedComments>
@@ -20290,27 +22528,47 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment7.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{1412A674-61A3-4D66-9D3E-5374366576D7}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{7BAEFA08-D790-466D-A190-320CBA26570E}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{E1852E19-B84C-463E-A0CB-BF0ADA1DC1BE}">
+    <text>Max contracted length normalized by resting length</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{13B25287-2F50-4E04-AC48-02AB262B1DE9}">
+    <text>Kmax</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{50243B4E-1A69-4602-BC70-D861CF3BE17E}">
+    <text>Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C83896A-0586-4C90-B5FD-474633C66A37}">
   <dimension ref="A1:AJ27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -20321,7 +22579,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -20330,7 +22588,7 @@
         <v>403.38</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -20338,7 +22596,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -20461,12 +22719,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>17.55</v>
       </c>
       <c r="D6">
         <v>17.081</v>
@@ -20526,7 +22784,7 @@
         <v>23.167999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -20591,7 +22849,7 @@
         <v>-123</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -20659,13 +22917,13 @@
         <v>84.4</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -20745,7 +23003,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -20771,7 +23029,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -20846,7 +23104,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -20912,19 +23170,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C15">
         <f>C6*SIN(RADIANS(C8))*C12/1000</f>
-        <v>0.26363819717520748</v>
+        <v>4.6268503604248918</v>
       </c>
       <c r="D15">
         <f t="shared" ref="D15:K15" si="1">D6*SIN(RADIANS(D8))*D12/1000</f>
@@ -21055,15 +23313,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C18">
         <f>C6+4.6262</f>
-        <v>5.6261999999999999</v>
+        <v>22.176200000000001</v>
       </c>
       <c r="D18">
         <f t="shared" ref="D18:K18" si="4">D6+4.6262</f>
@@ -21098,7 +23356,7 @@
         <v>6.3061999999999996</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C19">
         <v>22.176200000000001</v>
       </c>
@@ -21127,12 +23385,12 @@
         <v>6.3061999999999996</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C21">
         <v>17.55</v>
       </c>
@@ -21160,8 +23418,14 @@
       <c r="K21">
         <v>1.68</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
+      <c r="Z21" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.3">
       <c r="T22">
         <v>480</v>
       </c>
@@ -21177,8 +23441,16 @@
       <c r="X22">
         <v>405</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
+      <c r="Z22">
+        <f>MIN(C10:AN10)</f>
+        <v>409.5</v>
+      </c>
+      <c r="AB22">
+        <f>MAX(C10:AP10)</f>
+        <v>463</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.3">
       <c r="S23" t="s">
         <v>30</v>
       </c>
@@ -21203,7 +23475,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.3">
       <c r="S24" t="s">
         <v>31</v>
       </c>
@@ -21228,7 +23500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.3">
       <c r="S27" t="s">
         <v>32</v>
       </c>
@@ -21246,28 +23518,28 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA3ACFF-8EC2-4AAF-BDC7-460D102A0BEE}">
-  <dimension ref="A1:AE21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -21278,7 +23550,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -21294,7 +23566,7 @@
         <v>0.14749999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -21314,7 +23586,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -21406,7 +23678,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -21450,7 +23722,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -21494,7 +23766,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -21538,7 +23810,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -21585,7 +23857,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -21630,7 +23902,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -21639,14 +23911,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -21739,7 +24011,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -21784,14 +24056,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -21912,7 +24184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="L17" t="s">
         <v>55</v>
       </c>
@@ -21923,9 +24195,32 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" s="21" t="s">
         <v>52</v>
+      </c>
+      <c r="N21" t="s">
+        <v>93</v>
+      </c>
+      <c r="P21" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N22">
+        <f>AVERAGE(C8:O8)</f>
+        <v>618.36923076923074</v>
+      </c>
+      <c r="P22">
+        <f>MIN(B10:AA10)</f>
+        <v>337</v>
+      </c>
+      <c r="Q22">
+        <f>MAX(C10:AB10)</f>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -21939,27 +24234,27 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9CE551-57A5-4045-B5A9-E0D9326386C2}">
   <dimension ref="A1:AE27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -21970,7 +24265,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -21986,7 +24281,7 @@
         <v>0.15046296296296291</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -21998,7 +24293,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -22090,7 +24385,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -22137,7 +24432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -22184,7 +24479,7 @@
         <v>-106.5</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -22231,7 +24526,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -22281,7 +24576,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -22329,7 +24624,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -22338,14 +24633,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -22438,7 +24733,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -22486,14 +24781,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -22614,16 +24909,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O21" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>101</v>
+      </c>
+      <c r="R21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="O22">
+        <f>AVERAGE(C8:P8)</f>
+        <v>622.92857142857144</v>
+      </c>
+      <c r="Q22">
+        <f>MIN(C10:AB10)</f>
+        <v>356</v>
+      </c>
+      <c r="R22">
+        <f>MAX(C10:AC10)</f>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B27" s="29" t="s">
         <v>67</v>
       </c>
@@ -22639,23 +24957,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605CE535-3534-4BC1-886C-868F03FBDC68}">
   <dimension ref="A1:AK36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>71</v>
       </c>
@@ -22667,7 +24984,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
@@ -22684,7 +25001,7 @@
         <v>0.1490825688073395</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -22714,7 +25031,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="4" t="s">
         <v>0</v>
@@ -22813,232 +25130,231 @@
       <c r="AJ5" s="10"/>
       <c r="AK5" s="10"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6">
+        <v>1.56</v>
+      </c>
       <c r="D6">
-        <v>1.56</v>
+        <v>7.27</v>
       </c>
       <c r="E6">
-        <v>7.27</v>
+        <v>18.05</v>
       </c>
       <c r="F6">
-        <v>18.05</v>
+        <v>22.13</v>
       </c>
       <c r="G6">
-        <v>22.13</v>
+        <v>24.334</v>
       </c>
       <c r="H6">
-        <v>24.334</v>
+        <v>23.155999999999999</v>
       </c>
       <c r="I6">
-        <v>23.155999999999999</v>
+        <v>25.13</v>
       </c>
       <c r="J6">
-        <v>25.13</v>
+        <v>25.15</v>
       </c>
       <c r="K6">
-        <v>25.15</v>
+        <v>26.1</v>
       </c>
       <c r="L6">
-        <v>26.1</v>
+        <v>29.18</v>
       </c>
       <c r="M6">
-        <v>29.18</v>
+        <v>31.68</v>
       </c>
       <c r="N6">
-        <v>31.68</v>
+        <v>32.74</v>
       </c>
       <c r="O6">
-        <v>32.74</v>
+        <v>34.68</v>
       </c>
       <c r="P6">
-        <v>34.68</v>
+        <v>38.82</v>
       </c>
       <c r="Q6">
-        <v>38.82</v>
+        <v>29.24</v>
       </c>
       <c r="R6">
-        <v>29.24</v>
+        <v>22.6</v>
       </c>
       <c r="S6">
-        <v>22.6</v>
+        <v>20.248000000000001</v>
       </c>
       <c r="T6">
-        <v>20.248000000000001</v>
+        <v>19.89</v>
       </c>
       <c r="U6">
-        <v>19.89</v>
+        <v>18.373999999999999</v>
       </c>
       <c r="V6">
-        <v>18.373999999999999</v>
-      </c>
-      <c r="W6">
         <v>0.40200000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="30"/>
+      <c r="C7">
+        <v>28.29</v>
+      </c>
       <c r="D7">
-        <v>28.29</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="E7">
-        <v>18.149999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="F7">
-        <v>1.29</v>
+        <v>-14.86</v>
       </c>
       <c r="G7">
-        <v>-14.86</v>
+        <v>-25.64</v>
       </c>
       <c r="H7">
-        <v>-25.64</v>
+        <v>-36.76</v>
       </c>
       <c r="I7">
-        <v>-36.76</v>
+        <v>-42.87</v>
       </c>
       <c r="J7">
-        <v>-42.87</v>
+        <v>-49.33</v>
       </c>
       <c r="K7">
-        <v>-49.33</v>
+        <v>-56.87</v>
       </c>
       <c r="L7">
-        <v>-56.87</v>
+        <v>-68.36</v>
       </c>
       <c r="M7">
-        <v>-68.36</v>
+        <v>-77.69</v>
       </c>
       <c r="N7">
-        <v>-77.69</v>
+        <v>-84.16</v>
       </c>
       <c r="O7">
-        <v>-84.16</v>
+        <v>-90.1</v>
       </c>
       <c r="P7">
-        <v>-90.1</v>
+        <v>-99.233999999999995</v>
       </c>
       <c r="Q7">
-        <v>-99.233999999999995</v>
+        <v>-82</v>
       </c>
       <c r="R7">
-        <v>-82</v>
+        <v>-65.48</v>
       </c>
       <c r="S7">
-        <v>-65.48</v>
+        <v>-47.537999999999997</v>
       </c>
       <c r="T7">
-        <v>-47.537999999999997</v>
+        <v>-26.72</v>
       </c>
       <c r="U7">
-        <v>-26.72</v>
+        <v>-6.2530000000000001</v>
       </c>
       <c r="V7">
-        <v>-6.2530000000000001</v>
-      </c>
-      <c r="W7">
         <v>31.442</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8">
+        <v>622.09299999999996</v>
+      </c>
       <c r="D8">
+        <v>620.57899999999995</v>
+      </c>
+      <c r="E8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="F8">
+        <v>621.34</v>
+      </c>
+      <c r="G8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="H8">
+        <v>620.58000000000004</v>
+      </c>
+      <c r="I8">
+        <v>622.85</v>
+      </c>
+      <c r="J8">
         <v>622.09299999999996</v>
       </c>
-      <c r="E8">
+      <c r="K8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="L8">
+        <v>623.04999999999995</v>
+      </c>
+      <c r="M8">
+        <v>623.33600000000001</v>
+      </c>
+      <c r="N8">
         <v>620.57899999999995</v>
       </c>
-      <c r="F8">
+      <c r="O8">
+        <v>622.85</v>
+      </c>
+      <c r="P8">
         <v>621.33600000000001</v>
-      </c>
-      <c r="G8">
-        <v>621.34</v>
-      </c>
-      <c r="H8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="I8">
-        <v>620.58000000000004</v>
-      </c>
-      <c r="J8">
-        <v>622.85</v>
-      </c>
-      <c r="K8">
-        <v>622.09299999999996</v>
-      </c>
-      <c r="L8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="M8">
-        <v>623.04999999999995</v>
-      </c>
-      <c r="N8">
-        <v>623.33600000000001</v>
-      </c>
-      <c r="O8">
-        <v>620.57899999999995</v>
-      </c>
-      <c r="P8">
-        <v>622.85</v>
       </c>
       <c r="Q8">
         <v>621.33600000000001</v>
       </c>
       <c r="R8">
+        <v>622.09</v>
+      </c>
+      <c r="S8">
+        <v>622.6</v>
+      </c>
+      <c r="T8">
+        <v>622.85</v>
+      </c>
+      <c r="U8">
         <v>621.33600000000001</v>
       </c>
-      <c r="S8">
-        <v>622.09</v>
-      </c>
-      <c r="T8">
-        <v>622.6</v>
-      </c>
-      <c r="U8">
-        <v>622.85</v>
-      </c>
       <c r="V8">
-        <v>621.33600000000001</v>
-      </c>
-      <c r="W8">
         <v>620.57899999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="31"/>
+      <c r="C9" s="1">
+        <v>83</v>
+      </c>
       <c r="D9" s="1">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E9" s="1">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G9" s="1">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H9" s="1">
         <v>73</v>
       </c>
       <c r="I9" s="1">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J9" s="1">
         <v>71</v>
@@ -23047,41 +25363,39 @@
         <v>71</v>
       </c>
       <c r="L9" s="1">
+        <v>69</v>
+      </c>
+      <c r="M9" s="1">
+        <v>68</v>
+      </c>
+      <c r="N9" s="1">
         <v>71</v>
       </c>
-      <c r="M9" s="1">
+      <c r="O9" s="1">
         <v>69</v>
       </c>
-      <c r="N9" s="1">
-        <v>68</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
+        <v>70</v>
+      </c>
+      <c r="Q9" s="1">
         <v>71</v>
-      </c>
-      <c r="P9" s="1">
-        <v>69</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>70</v>
       </c>
       <c r="R9" s="1">
         <v>71</v>
       </c>
       <c r="S9" s="1">
-        <v>71</v>
+        <v>73.5</v>
       </c>
       <c r="T9" s="1">
-        <v>73.5</v>
+        <v>75</v>
       </c>
       <c r="U9" s="1">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="V9" s="1">
-        <v>77.5</v>
-      </c>
-      <c r="W9" s="1">
         <v>84</v>
       </c>
+      <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
@@ -23095,83 +25409,81 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
-      <c r="AK9" s="1"/>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="30"/>
+      <c r="C10">
+        <v>367</v>
+      </c>
       <c r="D10">
         <v>367</v>
       </c>
       <c r="E10">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="F10">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="G10">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H10">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="I10">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="J10">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="K10">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="L10">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="M10">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="N10">
         <v>428</v>
       </c>
       <c r="O10">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="P10">
         <v>434</v>
       </c>
       <c r="Q10">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="R10">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="S10">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="T10">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="U10">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="V10">
-        <v>386</v>
-      </c>
-      <c r="W10">
         <v>366</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="31"/>
+      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -23205,21 +25517,19 @@
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
-      <c r="AK11" s="1"/>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="30"/>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13">
         <v>249.71</v>
       </c>
       <c r="D13">
@@ -23303,33 +25613,32 @@
       <c r="AD13">
         <v>249.71</v>
       </c>
-      <c r="AE13">
-        <v>249.71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="30"/>
+      <c r="C14">
+        <v>78</v>
+      </c>
       <c r="D14">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E14">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G14">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J14">
         <v>30</v>
@@ -23338,48 +25647,45 @@
         <v>30</v>
       </c>
       <c r="L14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P14">
         <v>23</v>
       </c>
       <c r="Q14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="S14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="U14">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="V14">
-        <v>50</v>
-      </c>
-      <c r="W14">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="32"/>
+      <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -23413,96 +25719,95 @@
       <c r="AH15" s="2"/>
       <c r="AI15" s="2"/>
       <c r="AJ15" s="2"/>
-      <c r="AK15" s="2"/>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="30">
-        <f>C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
-        <v>0</v>
+      <c r="C16" s="16">
+        <f t="shared" ref="C16:AD16" si="0">C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
+        <v>0.38934455560856757</v>
       </c>
       <c r="D16" s="16">
-        <f t="shared" ref="D16:AE16" si="0">D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
-        <v>0.38934455560856757</v>
-      </c>
-      <c r="E16" s="16">
         <f t="shared" si="0"/>
         <v>1.8112948210918218</v>
       </c>
+      <c r="E16" s="16">
+        <f>E6*SIN(RADIANS(E9+5.15))*E13/1000</f>
+        <v>4.4750917512529496</v>
+      </c>
       <c r="F16" s="16">
-        <f>F6*SIN(RADIANS(F9+5.15))*F13/1000</f>
-        <v>4.4750917512529496</v>
+        <f t="shared" si="0"/>
+        <v>5.4446222516176634</v>
       </c>
       <c r="G16" s="16">
         <f t="shared" si="0"/>
-        <v>5.4446222516176634</v>
+        <v>5.9469453841091626</v>
       </c>
       <c r="H16" s="16">
         <f t="shared" si="0"/>
-        <v>5.9469453841091626</v>
+        <v>5.6590559428960212</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="0"/>
-        <v>5.6590559428960212</v>
+        <v>6.0927652115792634</v>
       </c>
       <c r="J16" s="16">
         <f t="shared" si="0"/>
-        <v>6.0927652115792634</v>
+        <v>6.0976142089621366</v>
       </c>
       <c r="K16" s="16">
         <f t="shared" si="0"/>
-        <v>6.0976142089621366</v>
+        <v>6.3279415846485803</v>
       </c>
       <c r="L16" s="16">
         <f t="shared" si="0"/>
-        <v>6.3279415846485803</v>
+        <v>7.0095037627925798</v>
       </c>
       <c r="M16" s="16">
         <f t="shared" si="0"/>
-        <v>7.0095037627925798</v>
+        <v>7.5711771242618884</v>
       </c>
       <c r="N16" s="16">
         <f t="shared" si="0"/>
-        <v>7.5711771242618884</v>
+        <v>7.937808715762241</v>
       </c>
       <c r="O16" s="16">
         <f t="shared" si="0"/>
-        <v>7.937808715762241</v>
+        <v>8.3306919291859725</v>
       </c>
       <c r="P16" s="16">
         <f t="shared" si="0"/>
-        <v>8.3306919291859725</v>
+        <v>9.369972199445602</v>
       </c>
       <c r="Q16" s="16">
         <f t="shared" si="0"/>
-        <v>9.369972199445602</v>
+        <v>7.0892341737595572</v>
       </c>
       <c r="R16" s="16">
         <f t="shared" si="0"/>
-        <v>7.0892341737595572</v>
+        <v>5.4793670426458965</v>
       </c>
       <c r="S16" s="16">
         <f t="shared" si="0"/>
-        <v>5.4793670426458965</v>
+        <v>4.957246848957868</v>
       </c>
       <c r="T16" s="16">
         <f t="shared" si="0"/>
-        <v>4.957246848957868</v>
+        <v>4.8935172428682936</v>
       </c>
       <c r="U16" s="16">
         <f t="shared" si="0"/>
-        <v>4.8935172428682936</v>
+        <v>4.5504713609212226</v>
       </c>
       <c r="V16" s="16">
         <f t="shared" si="0"/>
-        <v>4.5504713609212226</v>
+        <v>0.10037237370560359</v>
       </c>
       <c r="W16" s="16">
         <f t="shared" si="0"/>
-        <v>0.10037237370560359</v>
+        <v>0</v>
       </c>
       <c r="X16" s="16">
         <f t="shared" si="0"/>
@@ -23532,128 +25837,146 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
+      <c r="M17" s="3"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O24" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>101</v>
+      </c>
+      <c r="R24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O25">
+        <f>AVERAGE(C8:V8)</f>
+        <v>621.77425000000005</v>
+      </c>
+      <c r="Q25">
+        <f>MIN(C10:AB10)</f>
+        <v>366</v>
+      </c>
+      <c r="R25">
+        <f>MAX(C10:AC10)</f>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="29" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4765B8-342C-4A6E-9692-B7C6F1796DEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94363ADC-AC88-46D9-9481-31EBC409444D}">
   <dimension ref="A1:AK36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>71</v>
       </c>
@@ -23665,7 +25988,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
@@ -23682,7 +26005,7 @@
         <v>0.13763440860215059</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -23695,7 +26018,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="4" t="s">
         <v>0</v>
@@ -23794,7 +26117,7 @@
       <c r="AJ5" s="10"/>
       <c r="AK5" s="10"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
         <v>1</v>
@@ -23878,7 +26201,7 @@
         <v>0.95599999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="6" t="s">
         <v>2</v>
@@ -23962,7 +26285,7 @@
         <v>16.004999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
         <v>47</v>
@@ -24046,7 +26369,7 @@
         <v>621.33600000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -24141,7 +26464,7 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -24185,47 +26508,47 @@
       <c r="O10">
         <v>410</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10">
         <v>414</v>
       </c>
-      <c r="Q10" s="33">
+      <c r="Q10">
         <v>415</v>
       </c>
-      <c r="R10" s="33">
+      <c r="R10">
         <v>416</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10">
         <v>423</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10">
         <v>424</v>
       </c>
-      <c r="U10" s="33">
+      <c r="U10">
         <v>418</v>
       </c>
-      <c r="V10" s="33">
+      <c r="V10">
         <v>417</v>
       </c>
-      <c r="W10" s="33">
+      <c r="W10">
         <v>410</v>
       </c>
-      <c r="X10" s="33">
+      <c r="X10">
         <v>404</v>
       </c>
-      <c r="Y10" s="33">
+      <c r="Y10">
         <v>396</v>
       </c>
-      <c r="Z10" s="33">
+      <c r="Z10">
         <v>387</v>
       </c>
-      <c r="AA10" s="33">
+      <c r="AA10">
         <v>388</v>
       </c>
-      <c r="AB10" s="33">
+      <c r="AB10">
         <v>387</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -24268,14 +26591,14 @@
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -24368,7 +26691,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -24453,7 +26776,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
@@ -24494,7 +26817,7 @@
       <c r="AJ15" s="2"/>
       <c r="AK15" s="2"/>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
         <v>6</v>
@@ -24616,128 +26939,150 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="S17" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="T17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="P24" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>101</v>
+      </c>
+      <c r="R24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="P25">
+        <f>AVERAGE(C8:AB8)</f>
+        <v>622.24807692307695</v>
+      </c>
+      <c r="Q25">
+        <f>MIN(C10:AB10)</f>
+        <v>387</v>
+      </c>
+      <c r="R25">
+        <f>MAX(C10:AC10)</f>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="29" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
-  <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AJ22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -24748,7 +27093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -24757,7 +27102,7 @@
         <v>402.55</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -24765,7 +27110,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -24888,7 +27233,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -24977,7 +27322,7 @@
         <v>30.405999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -25066,7 +27411,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -25158,13 +27503,13 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -25260,7 +27605,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -25286,7 +27631,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -25376,7 +27721,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -25466,13 +27811,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -25607,6 +27952,24 @@
       <c r="AI15">
         <f t="shared" si="2"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M21" t="s">
+        <v>101</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M22">
+        <f>MIN(C10:AZ10)</f>
+        <v>406</v>
+      </c>
+      <c r="N22">
+        <f>MAX(C10:AZ10)</f>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -25619,24 +27982,24 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
   <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -25647,7 +28010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -25659,7 +28022,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -25670,7 +28033,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -25793,7 +28156,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -25858,7 +28221,7 @@
         <v>48.012999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -25923,7 +28286,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -25991,13 +28354,13 @@
         <v>95.1</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -26077,7 +28440,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -26103,7 +28466,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -26208,7 +28571,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -26274,13 +28637,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -26417,12 +28780,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="L16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="13:18" x14ac:dyDescent="0.3">
+      <c r="M21" t="s">
+        <v>101</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="13:18" x14ac:dyDescent="0.3">
+      <c r="M22">
+        <f>MIN(C10:AZ10)</f>
+        <v>404</v>
+      </c>
+      <c r="N22">
+        <f>MAX(C10:AZ10)</f>
+        <v>467</v>
+      </c>
+    </row>
+    <row r="29" spans="13:18" x14ac:dyDescent="0.3">
       <c r="R29">
         <f>485*1.03</f>
         <v>499.55</v>
@@ -26438,24 +28819,24 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
   <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -26466,7 +28847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -26475,7 +28856,7 @@
         <v>379.31</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -26483,7 +28864,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -26606,7 +28987,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -26641,7 +29022,7 @@
         <v>2.0994000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -26676,7 +29057,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -26714,13 +29095,13 @@
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -26780,7 +29161,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -26806,7 +29187,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -26911,7 +29292,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -26947,13 +29328,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -27090,13 +29471,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="10:18" x14ac:dyDescent="0.3">
       <c r="J18">
         <f>1-348/457</f>
         <v>0.23851203501094087</v>
       </c>
     </row>
-    <row r="29" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="10:18" x14ac:dyDescent="0.3">
+      <c r="M21" t="s">
+        <v>101</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="10:18" x14ac:dyDescent="0.3">
+      <c r="M22">
+        <f>MIN(C10:AZ10)</f>
+        <v>376</v>
+      </c>
+      <c r="N22">
+        <f>MAX(C10:AZ10)</f>
+        <v>428</v>
+      </c>
+    </row>
+    <row r="29" spans="10:18" x14ac:dyDescent="0.3">
       <c r="R29">
         <f>485*1.03</f>
         <v>499.55</v>
@@ -27112,22 +29511,22 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B26E4-CFF3-41E2-8721-B0918FFC9B0E}">
   <dimension ref="A1:AK36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="39.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>71</v>
       </c>
@@ -27139,24 +29538,24 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D3">
         <f>(C3/C2)</f>
-        <v>0.86221294363256784</v>
+        <v>0.84133611691022969</v>
       </c>
       <c r="E3">
         <f>1-D3</f>
-        <v>0.13778705636743216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+        <v>0.15866388308977031</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -27165,14 +29564,11 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="4" t="s">
         <v>0</v>
@@ -27271,7 +29667,7 @@
       <c r="AJ5" s="10"/>
       <c r="AK5" s="10"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
         <v>1</v>
@@ -27301,16 +29697,40 @@
         <v>65.655000000000001</v>
       </c>
       <c r="K6">
-        <v>76.481999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="L6">
-        <v>68.266999999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+        <v>61.6</v>
+      </c>
+      <c r="M6">
+        <v>60.4</v>
+      </c>
+      <c r="N6">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="O6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="P6">
+        <v>21</v>
+      </c>
+      <c r="Q6">
+        <v>44</v>
+      </c>
+      <c r="R6">
+        <v>55.9</v>
+      </c>
+      <c r="S6">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="T6">
+        <v>75.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="C7" s="16">
         <v>-68.718999999999994</v>
@@ -27337,13 +29757,37 @@
         <v>-24.202999999999999</v>
       </c>
       <c r="K7">
-        <v>-9.125</v>
+        <v>-25.6</v>
       </c>
       <c r="L7">
-        <v>-21.331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+        <v>-16</v>
+      </c>
+      <c r="M7">
+        <v>-20.6</v>
+      </c>
+      <c r="N7">
+        <v>-70.81</v>
+      </c>
+      <c r="O7">
+        <v>-63</v>
+      </c>
+      <c r="P7">
+        <v>-53.6</v>
+      </c>
+      <c r="Q7">
+        <v>-39.280999999999999</v>
+      </c>
+      <c r="R7">
+        <v>-29.6</v>
+      </c>
+      <c r="S7">
+        <v>-16.3</v>
+      </c>
+      <c r="T7">
+        <v>-10.199999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
         <v>47</v>
@@ -27373,13 +29817,37 @@
         <v>622.85</v>
       </c>
       <c r="K8">
-        <v>621.33600000000001</v>
+        <v>622.79999999999995</v>
       </c>
       <c r="L8">
-        <v>621.36500000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+        <v>623.6</v>
+      </c>
+      <c r="M8">
+        <v>622</v>
+      </c>
+      <c r="N8">
+        <v>626</v>
+      </c>
+      <c r="O8">
+        <v>624</v>
+      </c>
+      <c r="P8">
+        <v>622</v>
+      </c>
+      <c r="Q8">
+        <v>625.1</v>
+      </c>
+      <c r="R8">
+        <v>625.1</v>
+      </c>
+      <c r="S8">
+        <v>623.6</v>
+      </c>
+      <c r="T8">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -27411,19 +29879,35 @@
         <v>83</v>
       </c>
       <c r="K9" s="1">
-        <v>56</v>
+        <v>57.5</v>
       </c>
       <c r="L9" s="1">
-        <v>56</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
+        <v>88</v>
+      </c>
+      <c r="M9" s="1">
+        <v>89</v>
+      </c>
+      <c r="N9" s="1">
+        <v>84.5</v>
+      </c>
+      <c r="O9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="P9" s="1">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>89</v>
+      </c>
+      <c r="R9" s="1">
+        <v>90</v>
+      </c>
+      <c r="S9" s="1">
+        <v>88.5</v>
+      </c>
+      <c r="T9" s="1">
+        <v>26.5</v>
+      </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
@@ -27442,7 +29926,7 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -27472,13 +29956,37 @@
         <v>447</v>
       </c>
       <c r="K10">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="L10">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+        <v>452</v>
+      </c>
+      <c r="M10">
+        <v>449</v>
+      </c>
+      <c r="N10">
+        <v>403</v>
+      </c>
+      <c r="O10">
+        <v>407</v>
+      </c>
+      <c r="P10">
+        <v>415</v>
+      </c>
+      <c r="Q10">
+        <v>430</v>
+      </c>
+      <c r="R10">
+        <v>438</v>
+      </c>
+      <c r="S10">
+        <v>450</v>
+      </c>
+      <c r="T10">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -27521,44 +30029,44 @@
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="16">
-        <v>249.71</v>
-      </c>
-      <c r="D13">
-        <v>249.71</v>
-      </c>
-      <c r="E13">
-        <v>249.71</v>
-      </c>
-      <c r="F13">
-        <v>249.71</v>
-      </c>
-      <c r="G13">
-        <v>249.71</v>
-      </c>
-      <c r="H13">
-        <v>249.71</v>
-      </c>
-      <c r="I13">
-        <v>249.71</v>
-      </c>
-      <c r="J13">
-        <v>249.71</v>
-      </c>
-      <c r="K13">
-        <v>249.71</v>
+        <v>260.20999999999998</v>
+      </c>
+      <c r="D13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="E13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="F13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="G13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="H13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="I13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="J13" s="16">
+        <v>260.20999999999998</v>
+      </c>
+      <c r="K13" s="16">
+        <v>260.20999999999998</v>
       </c>
       <c r="L13">
         <v>249.71</v>
@@ -27621,7 +30129,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -27651,13 +30159,37 @@
         <v>77</v>
       </c>
       <c r="K14">
+        <v>75</v>
+      </c>
+      <c r="L14">
+        <v>74</v>
+      </c>
+      <c r="M14">
+        <v>75</v>
+      </c>
+      <c r="N14">
+        <v>55</v>
+      </c>
+      <c r="O14">
+        <v>65</v>
+      </c>
+      <c r="P14">
+        <v>75</v>
+      </c>
+      <c r="Q14">
+        <v>76</v>
+      </c>
+      <c r="R14">
+        <v>75</v>
+      </c>
+      <c r="S14">
+        <v>75</v>
+      </c>
+      <c r="T14">
         <v>67</v>
       </c>
-      <c r="L14">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
@@ -27698,213 +30230,1246 @@
       <c r="AJ15" s="2"/>
       <c r="AK15" s="2"/>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="16">
-        <f>-C6*SIN(RADIANS(C9+5.15))*C13/1000</f>
-        <v>-1.9089163300292105</v>
+        <f>-C6*SIN(RADIANS(C9+4.96))*C13/1000</f>
+        <v>-1.9888446022622024</v>
       </c>
       <c r="D16" s="16">
-        <f t="shared" ref="D16:AE16" si="0">-D6*SIN(RADIANS(D9+5.15))*D13/1000</f>
-        <v>-4.0809375058192954</v>
+        <f t="shared" ref="D16:K16" si="0">-D6*SIN(RADIANS(D9+4.96))*D13/1000</f>
+        <v>-4.2527956349925518</v>
       </c>
       <c r="E16" s="16">
         <f t="shared" si="0"/>
-        <v>-7.0574220518637798</v>
+        <v>-7.3539886035989408</v>
       </c>
       <c r="F16" s="16">
         <f t="shared" si="0"/>
-        <v>-10.09453321766197</v>
+        <v>-10.527409285407064</v>
       </c>
       <c r="G16" s="16">
         <f t="shared" si="0"/>
-        <v>-13.401234911810583</v>
+        <v>-13.966402193997661</v>
       </c>
       <c r="H16" s="16">
         <f t="shared" si="0"/>
-        <v>-14.847761858930939</v>
+        <v>-15.473036951197667</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="0"/>
-        <v>-15.781617917093591</v>
+        <v>-16.445267992387105</v>
       </c>
       <c r="J16" s="16">
         <f t="shared" si="0"/>
-        <v>-16.386164614410578</v>
+        <v>-17.07325998043143</v>
       </c>
       <c r="K16" s="16">
         <f t="shared" si="0"/>
-        <v>-16.727950101680829</v>
+        <v>-14.697192119709124</v>
       </c>
       <c r="L16" s="16">
-        <f t="shared" si="0"/>
-        <v>-14.931186025358189</v>
+        <f t="shared" ref="L16:AE16" si="1">-L6*SIN(RADIANS(L9+5.15))*L13/1000</f>
+        <v>-15.358895091501429</v>
       </c>
       <c r="M16" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>-15.042937875530633</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="1"/>
+        <v>-0.56433407059449248</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="1"/>
+        <v>-2.4445410159422072</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="1"/>
+        <v>-5.2402184740344895</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="1"/>
+        <v>-10.95843156495609</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="1"/>
+        <v>-13.902438921694182</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="1"/>
+        <v>-16.846155017276384</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="1"/>
+        <v>-9.9320795468220986</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N16" s="16">
-        <f t="shared" si="0"/>
+      <c r="V16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O16" s="16">
-        <f t="shared" si="0"/>
+      <c r="W16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P16" s="16">
-        <f t="shared" si="0"/>
+      <c r="X16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="16">
-        <f t="shared" si="0"/>
+      <c r="Y16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R16" s="16">
-        <f t="shared" si="0"/>
+      <c r="Z16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AA16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AB16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AC16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AD16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W16" s="16">
-        <f t="shared" si="0"/>
+      <c r="AE16" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="21" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="M21" t="s">
+        <v>93</v>
+      </c>
+      <c r="N21" t="s">
+        <v>101</v>
+      </c>
+      <c r="O21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="M22">
+        <f>AVERAGE(C8:T8)</f>
+        <v>623.16511111111129</v>
+      </c>
+      <c r="N22">
+        <f>MIN(C10:BA10)</f>
+        <v>403</v>
+      </c>
+      <c r="O22">
+        <f>MAX(C10:BA10)</f>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
-      <c r="B27" s="29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B27" s="30"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4491407B-6063-4D38-82E5-CAFE7B595AB6}">
+  <dimension ref="A1:AK36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2">
+        <v>406</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3">
+        <v>338</v>
+      </c>
+      <c r="D3">
+        <f>(C3/C2)</f>
+        <v>0.83251231527093594</v>
+      </c>
+      <c r="E3">
+        <f>1-D3</f>
+        <v>0.16748768472906406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" t="s">
+        <v>83</v>
+      </c>
+      <c r="O4" s="3"/>
+      <c r="Q4" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="D6">
+        <v>3.4</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>11.8</v>
+      </c>
+      <c r="G6">
+        <v>18.5</v>
+      </c>
+      <c r="H6">
+        <v>74.64</v>
+      </c>
+      <c r="I6">
+        <v>0.6</v>
+      </c>
+      <c r="J6">
+        <v>3.16</v>
+      </c>
+      <c r="K6">
+        <v>7.5</v>
+      </c>
+      <c r="L6">
+        <v>11.89</v>
+      </c>
+      <c r="M6">
+        <v>20.6</v>
+      </c>
+      <c r="N6">
+        <v>30.58</v>
+      </c>
+      <c r="O6">
+        <v>40.848999999999997</v>
+      </c>
+      <c r="P6">
+        <v>49.58</v>
+      </c>
+      <c r="Q6">
+        <v>66.7</v>
+      </c>
+      <c r="R6">
+        <v>73.463999999999999</v>
+      </c>
+      <c r="S6">
+        <v>79.912000000000006</v>
+      </c>
+      <c r="T6">
+        <v>82.4</v>
+      </c>
+      <c r="U6">
+        <v>81.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16">
+        <v>-113.5</v>
+      </c>
+      <c r="D7">
+        <v>-102</v>
+      </c>
+      <c r="E7">
+        <v>-94.207999999999998</v>
+      </c>
+      <c r="F7">
+        <v>-87.7</v>
+      </c>
+      <c r="G7">
+        <v>-80.5</v>
+      </c>
+      <c r="H7">
+        <v>-45</v>
+      </c>
+      <c r="I7">
+        <v>-112.5</v>
+      </c>
+      <c r="J7">
+        <v>-102.4</v>
+      </c>
+      <c r="K7">
+        <v>-92</v>
+      </c>
+      <c r="L7">
+        <v>-86</v>
+      </c>
+      <c r="M7">
+        <v>-77.694000000000003</v>
+      </c>
+      <c r="N7">
+        <v>-70.8</v>
+      </c>
+      <c r="O7">
+        <v>-65.129000000000005</v>
+      </c>
+      <c r="P7">
+        <v>-60.462000000000003</v>
+      </c>
+      <c r="Q7">
+        <v>-50.768999999999998</v>
+      </c>
+      <c r="R7">
+        <v>-45.74</v>
+      </c>
+      <c r="S7">
+        <v>-40.716999999999999</v>
+      </c>
+      <c r="T7">
+        <v>-34.972999999999999</v>
+      </c>
+      <c r="U7">
+        <v>-29.228999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16">
+        <v>624</v>
+      </c>
+      <c r="D8">
+        <v>623</v>
+      </c>
+      <c r="E8">
+        <v>624.36500000000001</v>
+      </c>
+      <c r="F8">
+        <v>624</v>
+      </c>
+      <c r="G8">
+        <v>623</v>
+      </c>
+      <c r="H8">
+        <v>622.79999999999995</v>
+      </c>
+      <c r="I8">
+        <v>625</v>
+      </c>
+      <c r="J8">
+        <v>624.5</v>
+      </c>
+      <c r="K8">
+        <v>624</v>
+      </c>
+      <c r="L8">
+        <v>622</v>
+      </c>
+      <c r="M8">
+        <v>622</v>
+      </c>
+      <c r="N8">
+        <v>625</v>
+      </c>
+      <c r="O8">
+        <v>624.36500000000001</v>
+      </c>
+      <c r="P8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="Q8">
+        <v>622.85</v>
+      </c>
+      <c r="R8">
+        <v>621.33600000000001</v>
+      </c>
+      <c r="S8">
+        <v>622.85</v>
+      </c>
+      <c r="T8">
+        <v>623.60699999999997</v>
+      </c>
+      <c r="U8">
+        <v>622.79999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="15">
+        <v>82</v>
+      </c>
+      <c r="D9" s="1">
+        <v>81</v>
+      </c>
+      <c r="E9" s="1">
+        <v>83</v>
+      </c>
+      <c r="F9" s="1">
+        <v>86</v>
+      </c>
+      <c r="G9" s="1">
+        <v>84</v>
+      </c>
+      <c r="H9" s="1">
+        <v>88</v>
+      </c>
+      <c r="I9" s="1">
+        <v>85</v>
+      </c>
+      <c r="J9" s="1">
+        <v>85.5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>85</v>
+      </c>
+      <c r="L9" s="1">
+        <v>85</v>
+      </c>
+      <c r="M9" s="1">
+        <v>88</v>
+      </c>
+      <c r="N9" s="1">
+        <v>88</v>
+      </c>
+      <c r="O9" s="1">
+        <v>89</v>
+      </c>
+      <c r="P9" s="1">
+        <v>90</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>90</v>
+      </c>
+      <c r="R9" s="1">
+        <v>89</v>
+      </c>
+      <c r="S9" s="1">
+        <v>90</v>
+      </c>
+      <c r="T9" s="1">
+        <v>89</v>
+      </c>
+      <c r="U9" s="1">
+        <v>90</v>
+      </c>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16">
+        <v>339</v>
+      </c>
+      <c r="D10">
+        <v>340</v>
+      </c>
+      <c r="E10">
+        <v>341</v>
+      </c>
+      <c r="F10">
+        <v>343</v>
+      </c>
+      <c r="G10">
+        <v>346</v>
+      </c>
+      <c r="H10">
+        <v>378</v>
+      </c>
+      <c r="I10">
+        <v>336</v>
+      </c>
+      <c r="J10">
+        <v>337</v>
+      </c>
+      <c r="K10">
+        <v>339</v>
+      </c>
+      <c r="L10">
+        <v>341</v>
+      </c>
+      <c r="M10">
+        <v>346</v>
+      </c>
+      <c r="N10">
+        <v>351</v>
+      </c>
+      <c r="O10">
+        <v>356</v>
+      </c>
+      <c r="P10">
+        <v>361</v>
+      </c>
+      <c r="Q10">
+        <v>370</v>
+      </c>
+      <c r="R10">
+        <v>374</v>
+      </c>
+      <c r="S10">
+        <v>378</v>
+      </c>
+      <c r="T10">
+        <v>381</v>
+      </c>
+      <c r="U10">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>245.83</v>
+      </c>
+      <c r="D13">
+        <v>245.83</v>
+      </c>
+      <c r="E13">
+        <v>245.83</v>
+      </c>
+      <c r="F13">
+        <v>245.83</v>
+      </c>
+      <c r="G13">
+        <v>245.83</v>
+      </c>
+      <c r="H13">
+        <v>245.83</v>
+      </c>
+      <c r="I13">
+        <v>245.83</v>
+      </c>
+      <c r="J13">
+        <v>245.83</v>
+      </c>
+      <c r="K13">
+        <v>245.83</v>
+      </c>
+      <c r="L13">
+        <v>245.83</v>
+      </c>
+      <c r="M13">
+        <v>245.83</v>
+      </c>
+      <c r="N13">
+        <v>245.83</v>
+      </c>
+      <c r="O13">
+        <v>245.83</v>
+      </c>
+      <c r="P13">
+        <v>245.83</v>
+      </c>
+      <c r="Q13">
+        <v>245.83</v>
+      </c>
+      <c r="R13">
+        <v>245.83</v>
+      </c>
+      <c r="S13">
+        <v>245.83</v>
+      </c>
+      <c r="T13">
+        <v>245.83</v>
+      </c>
+      <c r="U13">
+        <v>245.83</v>
+      </c>
+      <c r="V13">
+        <v>245.83</v>
+      </c>
+      <c r="W13">
+        <v>245.83</v>
+      </c>
+      <c r="X13">
+        <v>245.83</v>
+      </c>
+      <c r="Y13">
+        <v>245.83</v>
+      </c>
+      <c r="Z13">
+        <v>245.83</v>
+      </c>
+      <c r="AA13">
+        <v>245.83</v>
+      </c>
+      <c r="AB13">
+        <v>245.83</v>
+      </c>
+      <c r="AC13">
+        <v>245.83</v>
+      </c>
+      <c r="AD13">
+        <v>245.83</v>
+      </c>
+      <c r="AE13">
+        <v>245.83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>33</v>
+      </c>
+      <c r="F14">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>62</v>
+      </c>
+      <c r="H14">
+        <v>85</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
+      <c r="K14">
+        <v>35</v>
+      </c>
+      <c r="L14">
+        <v>44</v>
+      </c>
+      <c r="M14">
+        <v>50</v>
+      </c>
+      <c r="N14">
+        <v>76</v>
+      </c>
+      <c r="O14">
+        <v>82</v>
+      </c>
+      <c r="P14">
+        <v>85</v>
+      </c>
+      <c r="Q14">
+        <v>88</v>
+      </c>
+      <c r="R14">
+        <v>87</v>
+      </c>
+      <c r="S14">
+        <v>85</v>
+      </c>
+      <c r="T14">
+        <v>85</v>
+      </c>
+      <c r="U14">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="16">
+        <f>-C6*SIN(RADIANS(C9+5.25))*C13/1000</f>
+        <v>-4.9109379769919088E-2</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:AE16" si="0">-D6*SIN(RADIANS(D9+5.25))*D13/1000</f>
+        <v>-0.83403244093913598</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.7200073984477242</v>
+      </c>
+      <c r="F16" s="16">
+        <f t="shared" si="0"/>
+        <v>-2.900103689581238</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>-4.5474653742290858</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>-18.319240363209158</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>-0.14749659592534689</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>-0.77675624770615737</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.8437074490668364</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="0"/>
+        <v>-2.9228908759206247</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>-5.0559532620861303</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="0"/>
+        <v>-7.5053908133297975</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="0"/>
+        <v>-10.014296277159817</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="0"/>
+        <v>-12.137120802638771</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>-16.328074980556799</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>-18.009994411252876</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>-19.562355739823911</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>-20.200690671447745</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>-19.951096115672847</v>
+      </c>
+      <c r="V16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="H17" t="s">
+        <v>82</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="Q17" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" t="s">
+        <v>88</v>
+      </c>
+      <c r="T17" t="s">
+        <v>90</v>
+      </c>
+      <c r="U17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s">
+        <v>84</v>
+      </c>
+      <c r="S18" t="s">
+        <v>89</v>
+      </c>
+      <c r="T18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" t="s">
+        <v>101</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="M22">
+        <f>MIN(C10:AZ10)</f>
+        <v>336</v>
+      </c>
+      <c r="N22">
+        <f>MAX(C10:AZ10)</f>
+        <v>382</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="M24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="M25">
+        <f>AVERAGE(C8:U8)</f>
+        <v>623.42526315789462</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
     </row>
@@ -27917,25 +31482,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D1208C-7CDD-421F-9FF0-096EE144B4F3}">
-  <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AJ22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -27946,7 +31511,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -27955,19 +31520,19 @@
         <v>379.31</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C4">
-        <v>380</v>
+        <v>381.5</v>
       </c>
       <c r="D4">
         <f>1-C4/C2</f>
-        <v>0.16849015317286653</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+        <v>0.16520787746170673</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -28090,7 +31655,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -28182,7 +31747,7 @@
         <v>24.667000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -28274,7 +31839,7 @@
         <v>-123</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -28369,13 +31934,13 @@
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -28473,7 +32038,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -28499,7 +32064,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -28604,7 +32169,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -28697,13 +32262,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -28838,6 +32403,24 @@
       <c r="AI15">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="Q21" t="s">
+        <v>101</v>
+      </c>
+      <c r="S21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="Q22">
+        <f>MIN(C10:AE10)</f>
+        <v>381</v>
+      </c>
+      <c r="S22">
+        <f>MAX(C10:AG10)</f>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -28849,25 +32432,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CB8201-A5D3-4826-B613-98BAA3DB341B}">
-  <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AJ22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -28878,7 +32461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -28887,7 +32470,7 @@
         <v>403.38</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -28899,7 +32482,7 @@
         <v>0.18106995884773658</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -29022,7 +32605,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -29039,7 +32622,7 @@
         <v>13.111000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -29056,7 +32639,7 @@
         <v>-92</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -29076,13 +32659,13 @@
         <v>80.7</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -29130,7 +32713,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -29156,7 +32739,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -29261,7 +32844,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -29279,13 +32862,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -29420,6 +33003,24 @@
       <c r="AI15">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K21" t="s">
+        <v>101</v>
+      </c>
+      <c r="M21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K22">
+        <f>MIN(C10:F10)</f>
+        <v>438</v>
+      </c>
+      <c r="M22">
+        <f>MAX(C10:H10)</f>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -29432,24 +33033,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D539E524-5F19-4B4B-B21A-C95F2596B6A0}">
   <dimension ref="A1:AJ27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -29460,7 +33061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -29472,7 +33073,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -29493,7 +33094,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -29616,7 +33217,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -29702,7 +33303,7 @@
         <v>33.061999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -29785,7 +33386,7 @@
         <v>-66</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -29871,13 +33472,13 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -29969,7 +33570,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -29995,7 +33596,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -30100,7 +33701,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -30184,13 +33785,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -30327,7 +33928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="U16" t="s">
         <v>23</v>
       </c>
@@ -30335,22 +33936,40 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="17" spans="14:29" x14ac:dyDescent="0.3">
       <c r="AB17">
         <v>2.2241</v>
       </c>
     </row>
-    <row r="18" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="18" spans="14:29" x14ac:dyDescent="0.3">
       <c r="AC18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="21" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="N21" t="s">
+        <v>102</v>
+      </c>
+      <c r="O21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="N22">
+        <f>MIN(C10:AN10)</f>
+        <v>346</v>
+      </c>
+      <c r="O22">
+        <f>MAX(C10:AO10)</f>
+        <v>413.5</v>
+      </c>
+    </row>
+    <row r="24" spans="14:29" x14ac:dyDescent="0.3">
       <c r="Q24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="25" spans="14:29" x14ac:dyDescent="0.3">
       <c r="Q25" t="s">
         <v>42</v>
       </c>
@@ -30361,7 +33980,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="26" spans="14:29" x14ac:dyDescent="0.3">
       <c r="Q26" t="s">
         <v>43</v>
       </c>
@@ -30372,7 +33991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="27" spans="14:29" x14ac:dyDescent="0.3">
       <c r="R27">
         <v>505</v>
       </c>
@@ -30386,25 +34005,25 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E6C766-4925-4D35-B304-44784D2D9843}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -30415,7 +34034,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -30423,7 +34042,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -30434,7 +34053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -30484,7 +34103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -30531,7 +34150,7 @@
         <v>6.2092000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -30578,7 +34197,7 @@
         <v>-18.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -30628,7 +34247,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>3</v>
@@ -30676,7 +34295,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
@@ -30684,13 +34303,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -30741,7 +34360,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -30789,13 +34408,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -30860,9 +34479,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="L16" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L21" t="s">
+        <v>101</v>
+      </c>
+      <c r="M21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <f>MIN(C9:AL9)</f>
+        <v>340</v>
+      </c>
+      <c r="M22">
+        <f>MAX(C9:AM9)</f>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -30874,25 +34511,25 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B944D1C8-56B8-47D8-90D4-245D22EBCA01}">
-  <dimension ref="A1:AE15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -30903,7 +34540,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -30911,7 +34548,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -30919,7 +34556,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -31011,7 +34648,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -31067,7 +34704,7 @@
         <v>17.72</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -31123,7 +34760,7 @@
         <v>-119.5</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -31182,14 +34819,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
       <c r="D9">
         <v>340</v>
       </c>
@@ -31239,7 +34873,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
@@ -31247,13 +34881,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -31346,7 +34980,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -31403,13 +35037,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -31528,6 +35162,24 @@
       <c r="AE15">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M21" t="s">
+        <v>101</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M22">
+        <f>MIN(D9:AM9)</f>
+        <v>340</v>
+      </c>
+      <c r="N22">
+        <f>MAX(D9:AN9)</f>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -31539,26 +35191,26 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07511B1B-CFA9-4E3E-A27D-F86FFAE12463}">
-  <dimension ref="A1:AE16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -31569,7 +35221,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -31577,7 +35229,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -31588,7 +35240,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -31680,7 +35332,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -31703,7 +35355,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -31723,7 +35375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
@@ -31743,7 +35395,7 @@
         <v>628.9</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -31766,7 +35418,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -31788,7 +35440,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -31797,14 +35449,14 @@
       </c>
       <c r="C11" s="24"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="23"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -31876,7 +35528,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -31895,14 +35547,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="25"/>
     </row>
-    <row r="16" spans="1:31" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
       <c r="B16" s="27" t="s">
         <v>6</v>
@@ -32010,6 +35662,36 @@
       <c r="AE16" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:14" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="8:14" x14ac:dyDescent="0.3">
+      <c r="L21" t="s">
+        <v>93</v>
+      </c>
+      <c r="M21" t="s">
+        <v>101</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="8:14" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <f>AVERAGE(C8:AK8)</f>
+        <v>626.94000000000005</v>
+      </c>
+      <c r="M22">
+        <f>MIN(C10:AM10)</f>
+        <v>334</v>
+      </c>
+      <c r="N22">
+        <f>MAX(C10:AN10)</f>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -32021,27 +35703,27 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC7A6C4B-FDDD-4D0B-90C8-5B01A1705645}">
-  <dimension ref="A1:AE17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -32052,7 +35734,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -32060,7 +35742,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -32077,7 +35759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -32169,7 +35851,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -32213,7 +35895,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -32257,7 +35939,7 @@
         <v>-73</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
@@ -32301,7 +35983,7 @@
         <v>629.71799999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -32348,7 +36030,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -32393,7 +36075,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -32402,14 +36084,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -32481,7 +36163,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -32526,14 +36208,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -32654,12 +36336,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="14:16" x14ac:dyDescent="0.3">
       <c r="N17" s="3" t="s">
         <v>50</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="O19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N21" t="s">
+        <v>93</v>
+      </c>
+      <c r="O21" t="s">
+        <v>101</v>
+      </c>
+      <c r="P21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N22">
+        <f>AVERAGE(C8:AM8)</f>
+        <v>627.65099999999995</v>
+      </c>
+      <c r="O22">
+        <f>MIN(A10:AM10)</f>
+        <v>334</v>
+      </c>
+      <c r="P22">
+        <f>MAX(B10:AN10)</f>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -32671,28 +36383,28 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4D735A-7F76-4974-8609-056275EBAB78}">
-  <dimension ref="A1:AE21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -32703,7 +36415,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -32719,7 +36431,7 @@
         <v>0.14749999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -32737,7 +36449,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -32829,7 +36541,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -32867,7 +36579,7 @@
         <v>45.42</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -32905,7 +36617,7 @@
         <v>-52.89</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -32943,7 +36655,7 @@
         <v>623.61</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -32990,7 +36702,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -33035,7 +36747,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -33044,14 +36756,14 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -33144,7 +36856,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -33183,14 +36895,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -33311,13 +37023,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="21" t="s">
         <v>52</v>
+      </c>
+      <c r="N21" t="s">
+        <v>93</v>
+      </c>
+      <c r="O21" t="s">
+        <v>101</v>
+      </c>
+      <c r="P21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N22">
+        <f>AVERAGE(C8:M8)</f>
+        <v>624.85518181818179</v>
+      </c>
+      <c r="O22">
+        <f>MIN(A10:Z10)</f>
+        <v>337</v>
+      </c>
+      <c r="P22">
+        <f>MAX(B10:AA10)</f>
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FF203A-7CD3-4B49-94A4-E0C6A4A9F528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC3B179-5D81-457C-B34A-1F9A34C29E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="16" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="18" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId16"/>
     <sheet name="FlxTest10mm_4" sheetId="23" r:id="rId17"/>
     <sheet name="FlxTest10mm_5" sheetId="24" r:id="rId18"/>
+    <sheet name="FlxTest10mm_6" sheetId="26" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -253,10 +254,13 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{EDD4A2EB-AC41-41F5-AEBA-BA83D6D066BB}">
       <text>
-        <t>[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Recheck after test</t>
+    Recheck after test
+Reply:
+    Moe had it originally at 465
+</t>
       </text>
     </comment>
     <comment ref="C3" authorId="1" shapeId="0" xr:uid="{E30E01B8-EB61-46FD-9E73-DB8665781EAE}">
@@ -264,7 +268,9 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Recheck after test</t>
+    Recheck after test
+Reply:
+    Moe had it originally at 401</t>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{FBA43358-59F0-4FFB-BDC7-3AEDE0ADFC53}">
@@ -403,8 +409,62 @@
 </comments>
 </file>
 
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={F2916077-4F60-4815-AACB-36F540965802}</author>
+    <author>tc={D38AB9F1-0008-44E2-9AA2-442694BB58A1}</author>
+    <author>tc={8BAEE42B-9536-417D-B6B2-DB5320F80125}</author>
+    <author>tc={D29CCFA0-C50E-48A0-9F07-9CBB4F001241}</author>
+    <author>tc={E616D17E-2271-4A96-95EA-0FDB020E98C3}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{F2916077-4F60-4815-AACB-36F540965802}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{D38AB9F1-0008-44E2-9AA2-442694BB58A1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{8BAEE42B-9536-417D-B6B2-DB5320F80125}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Max contracted length normalized by resting length</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{D29CCFA0-C50E-48A0-9F07-9CBB4F001241}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kmax</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{E616D17E-2271-4A96-95EA-0FDB020E98C3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="108">
   <si>
     <t>Test #</t>
   </si>
@@ -720,6 +780,15 @@
   <si>
     <t>max length (test)</t>
   </si>
+  <si>
+    <t>Flex test 6</t>
+  </si>
+  <si>
+    <t>*pre-inflation length 462</t>
+  </si>
+  <si>
+    <t>*pretension 20.9 N relaxing to 19 N before inflation</t>
+  </si>
 </sst>
 </file>
 
@@ -772,7 +841,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -976,7 +1045,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -4115,56 +4184,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.60346456692913386"/>
-                  <c:y val="-0.28313193524076818"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="log"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
@@ -4768,56 +4787,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.60346456692913386"/>
-                  <c:y val="-0.28313193524076818"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="log"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
@@ -5319,56 +5288,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.35160629921259845"/>
-                  <c:y val="-0.12492964421114028"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:trendline>
             <c:spPr>
               <a:ln w="19050" cap="rnd">
@@ -7317,6 +7236,483 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1394438799"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.38444521414405664"/>
+                  <c:y val="-0.42743820243981429"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_6!$C$7:$AE$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>-86.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-78.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-59.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-53.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-45.743000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-40.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-33.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-25.28</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-32</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-40.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-44.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-50.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-56.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-66.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-71.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-76.257999999999996</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-80.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-21.331</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_6!$C$16:$X$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>-0.77403468088936644</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2.1699751461256667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.1634500137164219</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6.0859073063754314</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-8.3053257787199364</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-11.529780814291216</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-14.646218214568991</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-16.11181033876116</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-17.67596442949068</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-18.688151379143374</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-17.008511474983347</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-14.571619480029591</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-13.263206031719381</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-10.450799841685679</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-7.7085359024047326</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-4.0341781682833195</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-2.735286933111357</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-1.815235873792082</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1.1189810180910094</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-18.534438585205493</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9187-4579-870C-E12B422BB1CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1604021071"/>
+        <c:axId val="1604018671"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1604021071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604018671"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1604018671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604021071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -11230,6 +11626,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors20.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -17187,6 +17623,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style20.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -21754,6 +22706,49 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58E722E8-FDD3-4A7B-AD3B-C615A565B17C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>49770</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>8515</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>329917</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>40264</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8B8A4D0-7025-4D69-80BF-1D6FF57C0C25}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22493,8 +23488,15 @@
   <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{EDD4A2EB-AC41-41F5-AEBA-BA83D6D066BB}">
     <text>Recheck after test</text>
   </threadedComment>
+  <threadedComment ref="C2" dT="2026-08-15T11:49:42.01" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{9CFDF14D-575A-454E-B7D7-DA4387652C71}" parentId="{EDD4A2EB-AC41-41F5-AEBA-BA83D6D066BB}">
+    <text xml:space="preserve">Moe had it originally at 465
+</text>
+  </threadedComment>
   <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{E30E01B8-EB61-46FD-9E73-DB8665781EAE}">
     <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="C3" dT="2026-08-15T11:49:54.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{5A4E2F9F-8889-44AD-82E8-09E38A749055}" parentId="{E30E01B8-EB61-46FD-9E73-DB8665781EAE}">
+    <text>Moe had it originally at 401</text>
   </threadedComment>
   <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{FBA43358-59F0-4FFB-BDC7-3AEDE0ADFC53}">
     <text>Max contracted length normalized by resting length</text>
@@ -22548,6 +23550,26 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment8.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{F2916077-4F60-4815-AACB-36F540965802}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{D38AB9F1-0008-44E2-9AA2-442694BB58A1}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{8BAEE42B-9536-417D-B6B2-DB5320F80125}">
+    <text>Max contracted length normalized by resting length</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{D29CCFA0-C50E-48A0-9F07-9CBB4F001241}">
+    <text>Kmax</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{E616D17E-2271-4A96-95EA-0FDB020E98C3}">
+    <text>Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C83896A-0586-4C90-B5FD-474633C66A37}">
   <dimension ref="A1:AJ27"/>
@@ -25982,7 +27004,7 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
@@ -25994,15 +27016,15 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="D3">
         <f>(C3/C2)</f>
-        <v>0.86236559139784941</v>
+        <v>0.84682713347921224</v>
       </c>
       <c r="E3">
         <f>1-D3</f>
-        <v>0.13763440860215059</v>
+        <v>0.15317286652078776</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
@@ -26014,7 +27036,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O4" s="3"/>
     </row>
@@ -30421,7 +31443,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
-      <c r="B27" s="30"/>
+      <c r="B27" s="3"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
@@ -31480,6 +32502,1050 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90DACAB6-F80F-4BC7-AC78-635542748F6E}">
+  <dimension ref="A1:AK36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2">
+        <v>457</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3">
+        <v>387</v>
+      </c>
+      <c r="D3">
+        <f>(C3/C2)</f>
+        <v>0.84682713347921224</v>
+      </c>
+      <c r="E3">
+        <f>1-D3</f>
+        <v>0.15317286652078776</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4" s="3"/>
+      <c r="V4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>3.1</v>
+      </c>
+      <c r="D6">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E6">
+        <v>16.7</v>
+      </c>
+      <c r="F6">
+        <v>24.4</v>
+      </c>
+      <c r="G6">
+        <v>33.4</v>
+      </c>
+      <c r="H6">
+        <v>46.3</v>
+      </c>
+      <c r="I6">
+        <v>58.9</v>
+      </c>
+      <c r="J6">
+        <v>64.7</v>
+      </c>
+      <c r="K6">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="L6">
+        <v>75</v>
+      </c>
+      <c r="M6">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="N6">
+        <v>58.6</v>
+      </c>
+      <c r="O6">
+        <v>53.2</v>
+      </c>
+      <c r="P6">
+        <v>41.9</v>
+      </c>
+      <c r="Q6">
+        <v>31</v>
+      </c>
+      <c r="R6">
+        <v>16.2</v>
+      </c>
+      <c r="S6">
+        <v>11</v>
+      </c>
+      <c r="T6">
+        <v>7.3</v>
+      </c>
+      <c r="U6">
+        <v>4.5</v>
+      </c>
+      <c r="V6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16">
+        <v>-86.5</v>
+      </c>
+      <c r="D7">
+        <v>-78.7</v>
+      </c>
+      <c r="E7">
+        <v>-71</v>
+      </c>
+      <c r="F7">
+        <v>-66</v>
+      </c>
+      <c r="G7">
+        <v>-59.7</v>
+      </c>
+      <c r="H7">
+        <v>-53.6</v>
+      </c>
+      <c r="I7">
+        <v>-45.743000000000002</v>
+      </c>
+      <c r="J7">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="K7">
+        <v>-33.9</v>
+      </c>
+      <c r="L7">
+        <v>-25.28</v>
+      </c>
+      <c r="M7">
+        <v>-32</v>
+      </c>
+      <c r="N7">
+        <v>-40.5</v>
+      </c>
+      <c r="O7">
+        <v>-44.3</v>
+      </c>
+      <c r="P7">
+        <v>-50.7</v>
+      </c>
+      <c r="Q7">
+        <v>-56.5</v>
+      </c>
+      <c r="R7">
+        <v>-66.5</v>
+      </c>
+      <c r="S7">
+        <v>-71.900000000000006</v>
+      </c>
+      <c r="T7">
+        <v>-76.257999999999996</v>
+      </c>
+      <c r="U7">
+        <v>-80.900000000000006</v>
+      </c>
+      <c r="V7">
+        <v>-21.331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16">
+        <v>613.75</v>
+      </c>
+      <c r="D8">
+        <v>613</v>
+      </c>
+      <c r="E8">
+        <v>613</v>
+      </c>
+      <c r="F8">
+        <v>616</v>
+      </c>
+      <c r="G8">
+        <v>616.70000000000005</v>
+      </c>
+      <c r="H8">
+        <v>616</v>
+      </c>
+      <c r="I8">
+        <v>614.5</v>
+      </c>
+      <c r="J8">
+        <v>613</v>
+      </c>
+      <c r="K8">
+        <v>613.76400000000001</v>
+      </c>
+      <c r="L8">
+        <v>613</v>
+      </c>
+      <c r="M8">
+        <v>613</v>
+      </c>
+      <c r="N8">
+        <v>615</v>
+      </c>
+      <c r="O8">
+        <v>615</v>
+      </c>
+      <c r="P8">
+        <v>615</v>
+      </c>
+      <c r="Q8">
+        <v>613.70000000000005</v>
+      </c>
+      <c r="R8">
+        <v>613</v>
+      </c>
+      <c r="S8">
+        <v>615.20000000000005</v>
+      </c>
+      <c r="T8">
+        <v>614</v>
+      </c>
+      <c r="U8">
+        <v>613</v>
+      </c>
+      <c r="V8">
+        <v>615.20000000000005</v>
+      </c>
+      <c r="W8">
+        <v>613</v>
+      </c>
+      <c r="X8">
+        <v>613</v>
+      </c>
+      <c r="Y8">
+        <v>613</v>
+      </c>
+      <c r="Z8">
+        <v>613</v>
+      </c>
+      <c r="AA8">
+        <v>613</v>
+      </c>
+      <c r="AB8">
+        <v>613</v>
+      </c>
+      <c r="AC8">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="15">
+        <v>85.5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="E9" s="1">
+        <v>88</v>
+      </c>
+      <c r="F9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>90</v>
+      </c>
+      <c r="H9" s="1">
+        <v>89</v>
+      </c>
+      <c r="I9" s="1">
+        <v>90</v>
+      </c>
+      <c r="J9" s="1">
+        <v>89</v>
+      </c>
+      <c r="K9" s="1">
+        <v>88</v>
+      </c>
+      <c r="L9" s="1">
+        <v>88.5</v>
+      </c>
+      <c r="M9" s="1">
+        <v>90</v>
+      </c>
+      <c r="N9" s="1">
+        <v>90</v>
+      </c>
+      <c r="O9" s="1">
+        <v>88</v>
+      </c>
+      <c r="P9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>90</v>
+      </c>
+      <c r="R9" s="1">
+        <v>89</v>
+      </c>
+      <c r="S9" s="1">
+        <v>90</v>
+      </c>
+      <c r="T9" s="1">
+        <v>90</v>
+      </c>
+      <c r="U9" s="1">
+        <v>90</v>
+      </c>
+      <c r="V9" s="1">
+        <v>93</v>
+      </c>
+      <c r="W9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="X9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16">
+        <v>387</v>
+      </c>
+      <c r="D10" s="30">
+        <v>391</v>
+      </c>
+      <c r="E10" s="30">
+        <v>395</v>
+      </c>
+      <c r="F10" s="30">
+        <v>400</v>
+      </c>
+      <c r="G10" s="30">
+        <v>405</v>
+      </c>
+      <c r="H10" s="30">
+        <v>412</v>
+      </c>
+      <c r="I10" s="30">
+        <v>422</v>
+      </c>
+      <c r="J10" s="30">
+        <v>425</v>
+      </c>
+      <c r="K10" s="30">
+        <v>430</v>
+      </c>
+      <c r="L10" s="30">
+        <v>435</v>
+      </c>
+      <c r="M10" s="30">
+        <v>431</v>
+      </c>
+      <c r="N10" s="30">
+        <v>423</v>
+      </c>
+      <c r="O10" s="30">
+        <v>418</v>
+      </c>
+      <c r="P10" s="30">
+        <v>411</v>
+      </c>
+      <c r="Q10" s="30">
+        <v>405</v>
+      </c>
+      <c r="R10" s="30">
+        <v>395</v>
+      </c>
+      <c r="S10" s="30">
+        <v>390</v>
+      </c>
+      <c r="T10" s="30">
+        <v>387</v>
+      </c>
+      <c r="U10" s="30">
+        <v>385</v>
+      </c>
+      <c r="V10" s="30">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>249.71</v>
+      </c>
+      <c r="D13">
+        <v>249.71</v>
+      </c>
+      <c r="E13">
+        <v>249.71</v>
+      </c>
+      <c r="F13">
+        <v>249.71</v>
+      </c>
+      <c r="G13">
+        <v>249.71</v>
+      </c>
+      <c r="H13">
+        <v>249.71</v>
+      </c>
+      <c r="I13">
+        <v>249.71</v>
+      </c>
+      <c r="J13">
+        <v>249.71</v>
+      </c>
+      <c r="K13">
+        <v>249.71</v>
+      </c>
+      <c r="L13">
+        <v>249.71</v>
+      </c>
+      <c r="M13">
+        <v>249.71</v>
+      </c>
+      <c r="N13">
+        <v>249.71</v>
+      </c>
+      <c r="O13">
+        <v>249.71</v>
+      </c>
+      <c r="P13">
+        <v>249.71</v>
+      </c>
+      <c r="Q13">
+        <v>249.71</v>
+      </c>
+      <c r="R13">
+        <v>249.71</v>
+      </c>
+      <c r="S13">
+        <v>249.71</v>
+      </c>
+      <c r="T13">
+        <v>249.71</v>
+      </c>
+      <c r="U13">
+        <v>249.71</v>
+      </c>
+      <c r="V13">
+        <v>249.71</v>
+      </c>
+      <c r="W13">
+        <v>249.71</v>
+      </c>
+      <c r="X13">
+        <v>249.71</v>
+      </c>
+      <c r="Y13">
+        <v>249.71</v>
+      </c>
+      <c r="Z13">
+        <v>249.71</v>
+      </c>
+      <c r="AA13">
+        <v>249.71</v>
+      </c>
+      <c r="AB13">
+        <v>249.71</v>
+      </c>
+      <c r="AC13">
+        <v>249.71</v>
+      </c>
+      <c r="AD13">
+        <v>249.71</v>
+      </c>
+      <c r="AE13">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16">
+        <v>42</v>
+      </c>
+      <c r="D14">
+        <v>53</v>
+      </c>
+      <c r="E14">
+        <v>66</v>
+      </c>
+      <c r="F14">
+        <v>74</v>
+      </c>
+      <c r="G14">
+        <v>80</v>
+      </c>
+      <c r="H14">
+        <v>80</v>
+      </c>
+      <c r="I14">
+        <v>85</v>
+      </c>
+      <c r="J14">
+        <v>85</v>
+      </c>
+      <c r="K14">
+        <v>85</v>
+      </c>
+      <c r="L14">
+        <v>80</v>
+      </c>
+      <c r="M14">
+        <v>82</v>
+      </c>
+      <c r="N14">
+        <v>83</v>
+      </c>
+      <c r="O14">
+        <v>85</v>
+      </c>
+      <c r="P14">
+        <v>85</v>
+      </c>
+      <c r="Q14">
+        <v>80</v>
+      </c>
+      <c r="R14">
+        <v>70</v>
+      </c>
+      <c r="S14">
+        <v>65</v>
+      </c>
+      <c r="T14">
+        <v>55</v>
+      </c>
+      <c r="U14">
+        <v>40</v>
+      </c>
+      <c r="V14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="16">
+        <f>-C6*SIN(RADIANS(C9+5.25))*C13/1000</f>
+        <v>-0.77403468088936644</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:AE16" si="0">-D6*SIN(RADIANS(D9+5.25))*D13/1000</f>
+        <v>-2.1699751461256667</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>-4.1634500137164219</v>
+      </c>
+      <c r="F16" s="16">
+        <f t="shared" si="0"/>
+        <v>-6.0859073063754314</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>-8.3053257787199364</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>-11.529780814291216</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>-14.646218214568991</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>-16.11181033876116</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="0"/>
+        <v>-17.67596442949068</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="0"/>
+        <v>-18.688151379143374</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>-17.008511474983347</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="0"/>
+        <v>-14.571619480029591</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="0"/>
+        <v>-13.263206031719381</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="0"/>
+        <v>-10.450799841685679</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>-7.7085359024047326</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>-4.0341781682833195</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>-2.735286933111357</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.815235873792082</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.1189810180910094</v>
+      </c>
+      <c r="V16" s="16">
+        <f t="shared" si="0"/>
+        <v>-18.534438585205493</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="V17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="V18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="V19">
+        <f>462/C2</f>
+        <v>1.0109409190371992</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" t="s">
+        <v>101</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="M22">
+        <f>MIN(C10:AZ10)</f>
+        <v>385</v>
+      </c>
+      <c r="N22">
+        <f>MAX(C10:AZ10)</f>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="M24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="M25">
+        <f>AVERAGE(C8:U8)</f>
+        <v>614.19021052631581</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D1208C-7CDD-421F-9FF0-096EE144B4F3}">
   <dimension ref="A1:AJ22"/>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC3B179-5D81-457C-B34A-1F9A34C29E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F044C214-45A8-4FE3-AF4A-1935F7B4994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="18" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="19" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="FlxTest10mm_4" sheetId="23" r:id="rId17"/>
     <sheet name="FlxTest10mm_5" sheetId="24" r:id="rId18"/>
     <sheet name="FlxTest10mm_6" sheetId="26" r:id="rId19"/>
+    <sheet name="FlxTest10mm_7" sheetId="27" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -463,8 +464,80 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={9AA8AD60-DE11-48B5-880C-2CCB45861899}</author>
+    <author>tc={E755D6F7-2EEF-478D-A020-90D4294A3ECE}</author>
+    <author>tc={1C40D3B8-BABA-47B6-BDD9-D22111829239}</author>
+    <author>tc={9EA52FCB-FEBF-4E8B-B6D0-56B012E0978E}</author>
+    <author>tc={E990C728-1545-4F94-A65C-CF60D8224868}</author>
+    <author>tc={D96C6B4A-6774-4EBB-B219-C5959025303E}</author>
+    <author>tc={701EEFB9-267B-45F6-8252-91563326FAC1}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{9AA8AD60-DE11-48B5-880C-2CCB45861899}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{E755D6F7-2EEF-478D-A020-90D4294A3ECE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Recheck after test</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="2" shapeId="0" xr:uid="{1C40D3B8-BABA-47B6-BDD9-D22111829239}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Max contracted length normalized by resting length</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="3" shapeId="0" xr:uid="{9EA52FCB-FEBF-4E8B-B6D0-56B012E0978E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kmax</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{E990C728-1545-4F94-A65C-CF60D8224868}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="5" shapeId="0" xr:uid="{D96C6B4A-6774-4EBB-B219-C5959025303E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Originally read -106 but corrected by 3 degrees.</t>
+      </text>
+    </comment>
+    <comment ref="X18" authorId="6" shapeId="0" xr:uid="{701EEFB9-267B-45F6-8252-91563326FAC1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Actually 410?</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="118">
   <si>
     <t>Test #</t>
   </si>
@@ -789,6 +862,36 @@
   <si>
     <t>*pretension 20.9 N relaxing to 19 N before inflation</t>
   </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>*Winch not locked. Pneumatic fitting hitting femur to limit RoM.</t>
+  </si>
+  <si>
+    <t>*self interference again.</t>
+  </si>
+  <si>
+    <t>Deflection in bracket, see picture.</t>
+  </si>
+  <si>
+    <t>high deflection in bracket.</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>It might be worth redoing this test with a short tendon. Would like to see high force/deflection at -90 knee angle. This test is somewhat limited due to shorter resting length and inability to reach -120 knee angle due to fitting interference.</t>
+  </si>
+  <si>
+    <t>**22 N pretension</t>
+  </si>
+  <si>
+    <t>** 420 mm pre-inflation length</t>
+  </si>
+  <si>
+    <t>413 mm</t>
+  </si>
 </sst>
 </file>
 
@@ -1014,7 +1117,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1046,6 +1149,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -7578,6 +7688,516 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-9187-4579-870C-E12B422BB1CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1604021071"/>
+        <c:axId val="1604018671"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1604021071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604018671"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1604018671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1604021071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.38444521414405664"/>
+                  <c:y val="-0.42743820243981429"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_7!$C$7:$AE$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>-109</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-103.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-94.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-86.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-79.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-68.36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-73.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-82.72</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-96.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-105.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-108.568</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-104.9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-100.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-97</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-92.8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-88.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-83.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-78.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-74.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-70.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-62.256999999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-56</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_7!$C$16:$AE$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>-0.64909149703352276</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2.4970762294077464</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.8905426597375499</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-7.9869930549707391</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-11.452852453160894</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-14.69098116170135</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-17.317686944672865</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-14.194330592107978</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-9.0748251795974699</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-3.8144182760395964</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.9223094335223556</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.19944670724390048</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-2.0973842966034444</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-2.9964914752892953</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-3.8704681555820066</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-5.1939185571681117</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-6.6906354309609268</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-9.0373508433128933</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-11.8172174042011</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-13.955467186220737</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-16.579007539649229</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-20.930729544640581</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-23.408194309792101</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-19.274406804020305</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-14B6-4F0F-83B8-51F9FD99C85A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11666,6 +12286,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors21.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -18139,6 +18799,522 @@
 </file>
 
 <file path=xl/charts/style20.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style21.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -22792,6 +23968,49 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACAAE4F8-CB26-45EE-8AE1-A64A65EFA2CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>49770</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>8515</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>329917</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>40264</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB0B8133-CBE0-4468-8E05-E2BE925B2030}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23570,6 +24789,32 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment9.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-07-18T06:57:33.87" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{9AA8AD60-DE11-48B5-880C-2CCB45861899}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{E755D6F7-2EEF-478D-A020-90D4294A3ECE}">
+    <text>Recheck after test</text>
+  </threadedComment>
+  <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{1C40D3B8-BABA-47B6-BDD9-D22111829239}">
+    <text>Max contracted length normalized by resting length</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{9EA52FCB-FEBF-4E8B-B6D0-56B012E0978E}">
+    <text>Kmax</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{E990C728-1545-4F94-A65C-CF60D8224868}">
+    <text>Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</text>
+  </threadedComment>
+  <threadedComment ref="C7" dT="2026-08-15T15:17:40.28" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{D96C6B4A-6774-4EBB-B219-C5959025303E}">
+    <text>Originally read -106 but corrected by 3 degrees.</text>
+  </threadedComment>
+  <threadedComment ref="X18" dT="2026-08-15T17:06:13.47" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{701EEFB9-267B-45F6-8252-91563326FAC1}">
+    <text>Actually 410?</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C83896A-0586-4C90-B5FD-474633C66A37}">
   <dimension ref="A1:AJ27"/>
@@ -32387,9 +33632,6 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
       <c r="H18" t="s">
         <v>84</v>
       </c>
@@ -33433,9 +34675,6 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
       <c r="V18" t="s">
         <v>106</v>
       </c>
@@ -34493,6 +35732,1114 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B7509CB-A5F2-43C2-BF18-BBF73E7A3FA0}">
+  <dimension ref="A1:AK36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="F1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2">
+        <v>417</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3">
+        <v>341</v>
+      </c>
+      <c r="D3">
+        <f>(C3/C2)</f>
+        <v>0.81774580335731417</v>
+      </c>
+      <c r="E3">
+        <f>1-D3</f>
+        <v>0.18225419664268583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="3"/>
+      <c r="X4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="35">
+        <v>2.6</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F6">
+        <v>32</v>
+      </c>
+      <c r="G6">
+        <v>45.9</v>
+      </c>
+      <c r="H6">
+        <v>58.9</v>
+      </c>
+      <c r="I6">
+        <v>69.5</v>
+      </c>
+      <c r="J6">
+        <v>57</v>
+      </c>
+      <c r="K6">
+        <v>36.4</v>
+      </c>
+      <c r="L6">
+        <v>15.3</v>
+      </c>
+      <c r="M6">
+        <v>7.7</v>
+      </c>
+      <c r="N6" s="31">
+        <v>0.8</v>
+      </c>
+      <c r="O6">
+        <v>8.4</v>
+      </c>
+      <c r="P6">
+        <v>12</v>
+      </c>
+      <c r="Q6">
+        <v>15.5</v>
+      </c>
+      <c r="R6">
+        <v>20.8</v>
+      </c>
+      <c r="S6">
+        <v>26.8</v>
+      </c>
+      <c r="T6">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="U6">
+        <v>47.4</v>
+      </c>
+      <c r="V6">
+        <v>55.9</v>
+      </c>
+      <c r="W6">
+        <v>66.5</v>
+      </c>
+      <c r="X6">
+        <v>84</v>
+      </c>
+      <c r="Y6">
+        <v>94</v>
+      </c>
+      <c r="Z6">
+        <v>77.400000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="35">
+        <v>-109</v>
+      </c>
+      <c r="D7">
+        <v>-103.9</v>
+      </c>
+      <c r="E7">
+        <v>-94.2</v>
+      </c>
+      <c r="F7">
+        <v>-86.3</v>
+      </c>
+      <c r="G7">
+        <v>-79.099999999999994</v>
+      </c>
+      <c r="H7">
+        <v>-73</v>
+      </c>
+      <c r="I7">
+        <v>-68.36</v>
+      </c>
+      <c r="J7">
+        <v>-73.7</v>
+      </c>
+      <c r="K7">
+        <v>-82.72</v>
+      </c>
+      <c r="L7">
+        <v>-96.3</v>
+      </c>
+      <c r="M7">
+        <v>-105.3</v>
+      </c>
+      <c r="N7" s="31">
+        <v>-108.568</v>
+      </c>
+      <c r="O7">
+        <v>-104.9</v>
+      </c>
+      <c r="P7">
+        <v>-100.6</v>
+      </c>
+      <c r="Q7">
+        <v>-97</v>
+      </c>
+      <c r="R7">
+        <v>-92.8</v>
+      </c>
+      <c r="S7">
+        <v>-88.1</v>
+      </c>
+      <c r="T7">
+        <v>-83.4</v>
+      </c>
+      <c r="U7">
+        <v>-78.400000000000006</v>
+      </c>
+      <c r="V7">
+        <v>-74.8</v>
+      </c>
+      <c r="W7">
+        <v>-70.5</v>
+      </c>
+      <c r="X7">
+        <v>-62.256999999999998</v>
+      </c>
+      <c r="Y7">
+        <v>-56</v>
+      </c>
+      <c r="Z7">
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="35">
+        <v>613.75</v>
+      </c>
+      <c r="D8">
+        <v>615.20000000000005</v>
+      </c>
+      <c r="E8">
+        <v>617.5</v>
+      </c>
+      <c r="F8">
+        <v>616</v>
+      </c>
+      <c r="G8">
+        <v>616</v>
+      </c>
+      <c r="H8">
+        <v>614.5</v>
+      </c>
+      <c r="I8">
+        <v>614.5</v>
+      </c>
+      <c r="J8">
+        <v>613.70000000000005</v>
+      </c>
+      <c r="K8">
+        <v>617.5</v>
+      </c>
+      <c r="L8">
+        <v>616</v>
+      </c>
+      <c r="M8">
+        <v>615</v>
+      </c>
+      <c r="N8" s="31">
+        <v>614.5</v>
+      </c>
+      <c r="O8">
+        <v>616</v>
+      </c>
+      <c r="P8">
+        <v>617</v>
+      </c>
+      <c r="Q8">
+        <v>616.79999999999995</v>
+      </c>
+      <c r="R8">
+        <v>615.29999999999995</v>
+      </c>
+      <c r="S8">
+        <v>615.20000000000005</v>
+      </c>
+      <c r="T8">
+        <v>614.5</v>
+      </c>
+      <c r="U8">
+        <v>614.5</v>
+      </c>
+      <c r="V8">
+        <v>613.70000000000005</v>
+      </c>
+      <c r="W8">
+        <v>614</v>
+      </c>
+      <c r="X8">
+        <v>613</v>
+      </c>
+      <c r="Y8">
+        <v>616.70000000000005</v>
+      </c>
+      <c r="Z8">
+        <v>617.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="36">
+        <v>86</v>
+      </c>
+      <c r="D9" s="1">
+        <v>85</v>
+      </c>
+      <c r="E9" s="1">
+        <v>87</v>
+      </c>
+      <c r="F9" s="1">
+        <v>86.5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>87</v>
+      </c>
+      <c r="H9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="I9" s="1">
+        <v>88.5</v>
+      </c>
+      <c r="J9" s="1">
+        <v>89</v>
+      </c>
+      <c r="K9" s="1">
+        <v>88</v>
+      </c>
+      <c r="L9" s="1">
+        <v>88</v>
+      </c>
+      <c r="M9" s="1">
+        <v>86</v>
+      </c>
+      <c r="N9" s="32">
+        <v>88</v>
+      </c>
+      <c r="O9" s="1">
+        <v>84</v>
+      </c>
+      <c r="P9" s="1">
+        <v>85</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>85</v>
+      </c>
+      <c r="R9" s="1">
+        <v>85</v>
+      </c>
+      <c r="S9" s="1">
+        <v>86</v>
+      </c>
+      <c r="T9" s="1">
+        <v>86</v>
+      </c>
+      <c r="U9" s="1">
+        <v>88</v>
+      </c>
+      <c r="V9" s="1">
+        <v>86</v>
+      </c>
+      <c r="W9" s="1">
+        <v>88</v>
+      </c>
+      <c r="X9" s="1">
+        <v>88.5</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>89</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>89</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="35">
+        <v>350</v>
+      </c>
+      <c r="D10" s="30">
+        <v>351</v>
+      </c>
+      <c r="E10" s="30">
+        <v>355</v>
+      </c>
+      <c r="F10" s="30">
+        <v>360</v>
+      </c>
+      <c r="G10" s="30">
+        <v>365</v>
+      </c>
+      <c r="H10" s="30">
+        <v>371</v>
+      </c>
+      <c r="I10" s="30">
+        <v>376</v>
+      </c>
+      <c r="J10" s="30">
+        <v>370</v>
+      </c>
+      <c r="K10" s="30">
+        <v>361</v>
+      </c>
+      <c r="L10" s="30">
+        <v>352</v>
+      </c>
+      <c r="M10" s="30">
+        <v>350</v>
+      </c>
+      <c r="N10" s="33">
+        <v>350</v>
+      </c>
+      <c r="O10" s="30">
+        <v>348</v>
+      </c>
+      <c r="P10" s="30">
+        <v>350</v>
+      </c>
+      <c r="Q10" s="30">
+        <v>352</v>
+      </c>
+      <c r="R10" s="30">
+        <v>355</v>
+      </c>
+      <c r="S10" s="30">
+        <v>358</v>
+      </c>
+      <c r="T10" s="30">
+        <v>360</v>
+      </c>
+      <c r="U10" s="30">
+        <v>365</v>
+      </c>
+      <c r="V10" s="30">
+        <v>368</v>
+      </c>
+      <c r="W10" s="30">
+        <v>374</v>
+      </c>
+      <c r="X10" s="30">
+        <v>381</v>
+      </c>
+      <c r="Y10" s="30">
+        <v>386</v>
+      </c>
+      <c r="Z10" s="30">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="N12" s="31"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="31">
+        <v>249.71</v>
+      </c>
+      <c r="D13">
+        <v>249.71</v>
+      </c>
+      <c r="E13">
+        <v>249.71</v>
+      </c>
+      <c r="F13">
+        <v>249.71</v>
+      </c>
+      <c r="G13">
+        <v>249.71</v>
+      </c>
+      <c r="H13">
+        <v>249.71</v>
+      </c>
+      <c r="I13">
+        <v>249.71</v>
+      </c>
+      <c r="J13">
+        <v>249.71</v>
+      </c>
+      <c r="K13">
+        <v>249.71</v>
+      </c>
+      <c r="L13">
+        <v>249.71</v>
+      </c>
+      <c r="M13">
+        <v>249.71</v>
+      </c>
+      <c r="N13" s="31">
+        <v>249.71</v>
+      </c>
+      <c r="O13">
+        <v>249.71</v>
+      </c>
+      <c r="P13">
+        <v>249.71</v>
+      </c>
+      <c r="Q13">
+        <v>249.71</v>
+      </c>
+      <c r="R13">
+        <v>249.71</v>
+      </c>
+      <c r="S13">
+        <v>249.71</v>
+      </c>
+      <c r="T13">
+        <v>249.71</v>
+      </c>
+      <c r="U13">
+        <v>249.71</v>
+      </c>
+      <c r="V13">
+        <v>249.71</v>
+      </c>
+      <c r="W13">
+        <v>249.71</v>
+      </c>
+      <c r="X13">
+        <v>249.71</v>
+      </c>
+      <c r="Y13">
+        <v>249.71</v>
+      </c>
+      <c r="Z13">
+        <v>249.71</v>
+      </c>
+      <c r="AA13">
+        <v>249.71</v>
+      </c>
+      <c r="AB13">
+        <v>249.71</v>
+      </c>
+      <c r="AC13">
+        <v>249.71</v>
+      </c>
+      <c r="AD13">
+        <v>249.71</v>
+      </c>
+      <c r="AE13">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="35">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <v>35</v>
+      </c>
+      <c r="F14">
+        <v>65</v>
+      </c>
+      <c r="G14">
+        <v>65</v>
+      </c>
+      <c r="H14">
+        <v>78</v>
+      </c>
+      <c r="I14">
+        <v>80</v>
+      </c>
+      <c r="J14">
+        <v>75</v>
+      </c>
+      <c r="K14">
+        <v>67</v>
+      </c>
+      <c r="L14">
+        <v>40</v>
+      </c>
+      <c r="M14">
+        <v>21</v>
+      </c>
+      <c r="N14" s="31">
+        <v>7</v>
+      </c>
+      <c r="O14">
+        <v>25</v>
+      </c>
+      <c r="P14">
+        <v>34</v>
+      </c>
+      <c r="Q14">
+        <v>45</v>
+      </c>
+      <c r="R14">
+        <v>52</v>
+      </c>
+      <c r="S14">
+        <v>57</v>
+      </c>
+      <c r="T14">
+        <v>65</v>
+      </c>
+      <c r="U14">
+        <v>70</v>
+      </c>
+      <c r="V14">
+        <v>69</v>
+      </c>
+      <c r="W14">
+        <v>83</v>
+      </c>
+      <c r="X14">
+        <v>83</v>
+      </c>
+      <c r="Y14">
+        <v>98</v>
+      </c>
+      <c r="Z14">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="37"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="35">
+        <f>-C6*SIN(RADIANS(C9+5.25))*C13/1000</f>
+        <v>-0.64909149703352276</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:AE16" si="0">-D6*SIN(RADIANS(D9+5.25))*D13/1000</f>
+        <v>-2.4970762294077464</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>-4.8905426597375499</v>
+      </c>
+      <c r="F16" s="16">
+        <f t="shared" si="0"/>
+        <v>-7.9869930549707391</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>-11.452852453160894</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>-14.69098116170135</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>-17.317686944672865</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>-14.194330592107978</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="0"/>
+        <v>-9.0748251795974699</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="0"/>
+        <v>-3.8144182760395964</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.9223094335223556</v>
+      </c>
+      <c r="N16" s="35">
+        <f t="shared" si="0"/>
+        <v>-0.19944670724390048</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="0"/>
+        <v>-2.0973842966034444</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="0"/>
+        <v>-2.9964914752892953</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="0"/>
+        <v>-3.8704681555820066</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="0"/>
+        <v>-5.1939185571681117</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="0"/>
+        <v>-6.6906354309609268</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="0"/>
+        <v>-9.0373508433128933</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="0"/>
+        <v>-11.8172174042011</v>
+      </c>
+      <c r="V16" s="16">
+        <f t="shared" si="0"/>
+        <v>-13.955467186220737</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="0"/>
+        <v>-16.579007539649229</v>
+      </c>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>-20.930729544640581</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="0"/>
+        <v>-23.408194309792101</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="0"/>
+        <v>-19.274406804020305</v>
+      </c>
+      <c r="AA16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="X17" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y17">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="C18" t="s">
+        <v>109</v>
+      </c>
+      <c r="N18" t="s">
+        <v>110</v>
+      </c>
+      <c r="X18" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" t="s">
+        <v>111</v>
+      </c>
+      <c r="N19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" t="s">
+        <v>101</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="M22">
+        <f>MIN(C10:AZ10)</f>
+        <v>348</v>
+      </c>
+      <c r="N22">
+        <f>MAX(C10:AZ10)</f>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="M24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="M25">
+        <f>AVERAGE(C8:U8)</f>
+        <v>615.44473684210516</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="M28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F044C214-45A8-4FE3-AF4A-1935F7B4994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0054F3F2-613A-47F6-A79F-5F8B4D31CCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="19" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="18" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -897,7 +897,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -939,12 +939,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1117,7 +1111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1148,10 +1142,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -34234,61 +34226,61 @@
       <c r="C10" s="16">
         <v>387</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10">
         <v>391</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10">
         <v>395</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10">
         <v>400</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10">
         <v>405</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10">
         <v>412</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10">
         <v>422</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10">
         <v>425</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10">
         <v>430</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10">
         <v>435</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M10">
         <v>431</v>
       </c>
-      <c r="N10" s="30">
+      <c r="N10">
         <v>423</v>
       </c>
-      <c r="O10" s="30">
+      <c r="O10">
         <v>418</v>
       </c>
-      <c r="P10" s="30">
+      <c r="P10">
         <v>411</v>
       </c>
-      <c r="Q10" s="30">
+      <c r="Q10">
         <v>405</v>
       </c>
-      <c r="R10" s="30">
+      <c r="R10">
         <v>395</v>
       </c>
-      <c r="S10" s="30">
+      <c r="S10">
         <v>390</v>
       </c>
-      <c r="T10" s="30">
+      <c r="T10">
         <v>387</v>
       </c>
-      <c r="U10" s="30">
+      <c r="U10">
         <v>385</v>
       </c>
-      <c r="V10" s="30">
+      <c r="V10">
         <v>435</v>
       </c>
     </row>
@@ -35910,7 +35902,7 @@
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="33">
         <v>2.6</v>
       </c>
       <c r="D6">
@@ -35943,7 +35935,7 @@
       <c r="M6">
         <v>7.7</v>
       </c>
-      <c r="N6" s="31">
+      <c r="N6" s="30">
         <v>0.8</v>
       </c>
       <c r="O6">
@@ -35988,7 +35980,7 @@
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="33">
         <v>-109</v>
       </c>
       <c r="D7">
@@ -36021,7 +36013,7 @@
       <c r="M7">
         <v>-105.3</v>
       </c>
-      <c r="N7" s="31">
+      <c r="N7" s="30">
         <v>-108.568</v>
       </c>
       <c r="O7">
@@ -36066,7 +36058,7 @@
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="33">
         <v>613.75</v>
       </c>
       <c r="D8">
@@ -36099,7 +36091,7 @@
       <c r="M8">
         <v>615</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N8" s="30">
         <v>614.5</v>
       </c>
       <c r="O8">
@@ -36146,7 +36138,7 @@
       <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="34">
         <v>86</v>
       </c>
       <c r="D9" s="1">
@@ -36179,7 +36171,7 @@
       <c r="M9" s="1">
         <v>86</v>
       </c>
-      <c r="N9" s="32">
+      <c r="N9" s="31">
         <v>88</v>
       </c>
       <c r="O9" s="1">
@@ -36245,76 +36237,76 @@
       <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="33">
         <v>350</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10">
         <v>351</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10">
         <v>355</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10">
         <v>360</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10">
         <v>365</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10">
         <v>371</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10">
         <v>376</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10">
         <v>370</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10">
         <v>361</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10">
         <v>352</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M10">
         <v>350</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10" s="30">
         <v>350</v>
       </c>
-      <c r="O10" s="30">
+      <c r="O10">
         <v>348</v>
       </c>
-      <c r="P10" s="30">
+      <c r="P10">
         <v>350</v>
       </c>
-      <c r="Q10" s="30">
+      <c r="Q10">
         <v>352</v>
       </c>
-      <c r="R10" s="30">
+      <c r="R10">
         <v>355</v>
       </c>
-      <c r="S10" s="30">
+      <c r="S10">
         <v>358</v>
       </c>
-      <c r="T10" s="30">
+      <c r="T10">
         <v>360</v>
       </c>
-      <c r="U10" s="30">
+      <c r="U10">
         <v>365</v>
       </c>
-      <c r="V10" s="30">
+      <c r="V10">
         <v>368</v>
       </c>
-      <c r="W10" s="30">
+      <c r="W10">
         <v>374</v>
       </c>
-      <c r="X10" s="30">
+      <c r="X10">
         <v>381</v>
       </c>
-      <c r="Y10" s="30">
+      <c r="Y10">
         <v>386</v>
       </c>
-      <c r="Z10" s="30">
+      <c r="Z10">
         <v>379</v>
       </c>
     </row>
@@ -36325,7 +36317,7 @@
       <c r="B11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="36"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
@@ -36338,7 +36330,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="32"/>
+      <c r="N11" s="31"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -36368,15 +36360,15 @@
       <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="N12" s="31"/>
+      <c r="C12" s="33"/>
+      <c r="N12" s="30"/>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>249.71</v>
       </c>
       <c r="D13">
@@ -36409,7 +36401,7 @@
       <c r="M13">
         <v>249.71</v>
       </c>
-      <c r="N13" s="31">
+      <c r="N13" s="30">
         <v>249.71</v>
       </c>
       <c r="O13">
@@ -36469,7 +36461,7 @@
       <c r="B14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="33">
         <v>10</v>
       </c>
       <c r="D14">
@@ -36502,7 +36494,7 @@
       <c r="M14">
         <v>21</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="30">
         <v>7</v>
       </c>
       <c r="O14">
@@ -36547,7 +36539,7 @@
       <c r="B15" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="37"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -36558,7 +36550,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-      <c r="N15" s="34"/>
+      <c r="N15" s="32"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
@@ -36588,7 +36580,7 @@
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="33">
         <f>-C6*SIN(RADIANS(C9+5.25))*C13/1000</f>
         <v>-0.64909149703352276</v>
       </c>
@@ -36632,7 +36624,7 @@
         <f t="shared" si="0"/>
         <v>-1.9223094335223556</v>
       </c>
-      <c r="N16" s="35">
+      <c r="N16" s="33">
         <f t="shared" si="0"/>
         <v>-0.19944670724390048</v>
       </c>

--- a/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_10mm_pinned.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0054F3F2-613A-47F6-A79F-5F8B4D31CCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10268781-4083-43C9-B151-833620A4857D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="18" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="0" yWindow="1044" windowWidth="21600" windowHeight="11292" firstSheet="15" activeTab="18" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -417,7 +417,6 @@
     <author>tc={D38AB9F1-0008-44E2-9AA2-442694BB58A1}</author>
     <author>tc={8BAEE42B-9536-417D-B6B2-DB5320F80125}</author>
     <author>tc={D29CCFA0-C50E-48A0-9F07-9CBB4F001241}</author>
-    <author>tc={E616D17E-2271-4A96-95EA-0FDB020E98C3}</author>
   </authors>
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{F2916077-4F60-4815-AACB-36F540965802}">
@@ -433,7 +432,9 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Recheck after test</t>
+    Recheck after test
+Reply:
+    Was 387 then reduced to 384 and then 381 after a while.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="2" shapeId="0" xr:uid="{8BAEE42B-9536-417D-B6B2-DB5320F80125}">
@@ -450,14 +451,6 @@
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Kmax</t>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="4" shapeId="0" xr:uid="{E616D17E-2271-4A96-95EA-0FDB020E98C3}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</t>
       </text>
     </comment>
   </commentList>
@@ -24769,14 +24762,14 @@
   <threadedComment ref="C3" dT="2026-07-18T06:57:43.54" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{D38AB9F1-0008-44E2-9AA2-442694BB58A1}">
     <text>Recheck after test</text>
   </threadedComment>
+  <threadedComment ref="C3" dT="2026-08-16T20:19:16.56" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{2B101A1F-792E-4EA0-B36B-F4124522D90F}" parentId="{D38AB9F1-0008-44E2-9AA2-442694BB58A1}">
+    <text>Was 387 then reduced to 384 and then 381 after a while.</text>
+  </threadedComment>
   <threadedComment ref="D3" dT="2026-07-17T08:55:32.82" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{8BAEE42B-9536-417D-B6B2-DB5320F80125}">
     <text>Max contracted length normalized by resting length</text>
   </threadedComment>
   <threadedComment ref="E3" dT="2026-07-17T08:54:37.64" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{D29CCFA0-C50E-48A0-9F07-9CBB4F001241}">
     <text>Kmax</text>
-  </threadedComment>
-  <threadedComment ref="C4" dT="2026-07-18T06:57:17.11" personId="{10A700E7-E0AC-4B04-B751-E14560120F23}" id="{E616D17E-2271-4A96-95EA-0FDB020E98C3}">
-    <text>Initially measured 30 mm but noticed it was actually 35 mm around data reading 6</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -33774,15 +33767,15 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D3">
         <f>(C3/C2)</f>
-        <v>0.84682713347921224</v>
+        <v>0.83369803063457326</v>
       </c>
       <c r="E3">
         <f>1-D3</f>
-        <v>0.15317286652078776</v>
+        <v>0.16630196936542674</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
